--- a/results/cross_validation/global_ind/metrics_summary.xlsx
+++ b/results/cross_validation/global_ind/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7453626141229988</v>
+        <v>0.7456102071640792</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5390301434905529</v>
+        <v>0.5396718421211117</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3683567401502492</v>
+        <v>-0.3795260019227649</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.31242089595299</v>
+        <v>-3.232143957129213</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.91252739026035</v>
+        <v>-11.86660285347648</v>
       </c>
       <c r="G2" t="n">
-        <v>-18.2914863493837</v>
+        <v>-18.15854850863077</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.433399769688957</v>
+        <v>-5.391923211979005</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09163216597143546</v>
+        <v>0.09115453133246176</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1888727812252955</v>
+        <v>0.1887987623139842</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0193169631225194</v>
+        <v>0.01920172180727735</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04496633749182512</v>
+        <v>0.04463545761255151</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08738361381075242</v>
+        <v>0.08723102244700905</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05401743362329221</v>
+        <v>0.05385080423490637</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08103154920752002</v>
+        <v>0.08081204995803169</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01088708020159934</v>
+        <v>0.0108764943039853</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06479240884752697</v>
+        <v>0.06470221379585288</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001044153779208879</v>
+        <v>0.001052676722494461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002540497752762184</v>
+        <v>0.002493205666112705</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008761062075055078</v>
+        <v>0.008729902588970649</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00349135903737538</v>
+        <v>0.003467300044547346</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01525276028225464</v>
+        <v>0.01522029885366055</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1043411721306567</v>
+        <v>0.1042904324661917</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2545435303588111</v>
+        <v>0.2543662984670982</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03231336842869958</v>
+        <v>0.03244497992747817</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05040335061047216</v>
+        <v>0.049932010435318</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09360054527114187</v>
+        <v>0.09343394773298755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05908772323736446</v>
+        <v>0.05888378422407434</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09904828167285763</v>
+        <v>0.09889190887552467</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56.62858874498973</v>
+        <v>55.000969110065</v>
       </c>
       <c r="C6" t="n">
-        <v>42.25707506318089</v>
+        <v>42.27212509827788</v>
       </c>
       <c r="D6" t="n">
-        <v>35.31335449040573</v>
+        <v>34.97600521322535</v>
       </c>
       <c r="E6" t="n">
-        <v>107.4822923093647</v>
+        <v>106.9105328964537</v>
       </c>
       <c r="F6" t="n">
-        <v>5713.352802438526</v>
+        <v>5702.477411417667</v>
       </c>
       <c r="G6" t="n">
-        <v>794.9538868757112</v>
+        <v>791.7282866366028</v>
       </c>
       <c r="H6" t="n">
-        <v>1124.99799998703</v>
+        <v>1122.227555062049</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08401217190421992</v>
+        <v>0.08393048386356596</v>
       </c>
       <c r="C7" t="n">
-        <v>0.183645643146103</v>
+        <v>0.1833899970207635</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8224758593810421</v>
+        <v>0.8291893485651513</v>
       </c>
       <c r="E7" t="n">
-        <v>2.591009234425662</v>
+        <v>2.542776862210086</v>
       </c>
       <c r="F7" t="n">
-        <v>7.759781921061289</v>
+        <v>7.732183575710448</v>
       </c>
       <c r="G7" t="n">
-        <v>11.57977971228255</v>
+        <v>11.49998332524083</v>
       </c>
       <c r="H7" t="n">
-        <v>3.836784090366811</v>
+        <v>3.811908932101807</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.68160645841393</v>
+        <v>-30.69036173765498</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.419400979405459</v>
+        <v>-6.427759170448624</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.18729101365716</v>
+        <v>-31.13851459486666</v>
       </c>
       <c r="E8" t="n">
-        <v>-25.8523715089763</v>
+        <v>-25.96511588243321</v>
       </c>
       <c r="F8" t="n">
-        <v>-46.84925767926012</v>
+        <v>-46.89201280863669</v>
       </c>
       <c r="G8" t="n">
-        <v>-63.54703472451041</v>
+        <v>-63.63692794943661</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.08949372737056</v>
+        <v>-34.12511535724613</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-29.69548357173283</v>
+        <v>-29.70423885097388</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.460603633265185</v>
+        <v>-7.46896182430835</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.22849366751689</v>
+        <v>-32.17971724872638</v>
       </c>
       <c r="E9" t="n">
-        <v>-26.89357416283602</v>
+        <v>-27.00631853629294</v>
       </c>
       <c r="F9" t="n">
-        <v>-44.42472443032012</v>
+        <v>-44.46747955969668</v>
       </c>
       <c r="G9" t="n">
-        <v>-60.72228793720273</v>
+        <v>-60.81218116212893</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.57086123381229</v>
+        <v>-33.60648286368786</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9355123638449284</v>
+        <v>0.9355643174542618</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9329833958172252</v>
+        <v>0.9329971747091542</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5030474678699266</v>
+        <v>0.4997862839986079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5614450680682554</v>
+        <v>0.5677068485949638</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7018916770275101</v>
+        <v>-0.7005851412101622</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.515119499044793</v>
+        <v>-1.51338571687679</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1193295199213387</v>
+        <v>0.120347294445006</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0413564117838651</v>
+        <v>0.04132844785361608</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08669499534190273</v>
+        <v>0.08669302706395231</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01893864680878754</v>
+        <v>0.01899601823993391</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01461148467510495</v>
+        <v>0.01447581613749631</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02773178948713899</v>
+        <v>0.02771644731603462</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01688021666065197</v>
+        <v>0.01687544767935921</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03436892412624188</v>
+        <v>0.03434753404839874</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002757183767080265</v>
+        <v>0.002754962478522706</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009419633749293192</v>
+        <v>0.009417697033504254</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003792102229525772</v>
+        <v>0.0003816987388227578</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002583578565072223</v>
+        <v>0.0002546689681217399</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001154721936056003</v>
+        <v>0.001153835460383727</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004551844805545327</v>
+        <v>0.0004548707019305599</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002404048668740632</v>
+        <v>0.002402955563547624</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0525088922667415</v>
+        <v>0.05248773645836431</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09705479766241951</v>
+        <v>0.09704481971493509</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01947332079930327</v>
+        <v>0.01953711183421843</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01607351413061943</v>
+        <v>0.01595835104645025</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03398119974421156</v>
+        <v>0.0339681536204682</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02133505286036416</v>
+        <v>0.0213276979988596</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04007112957727656</v>
+        <v>0.04005397844554932</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.20804542030383</v>
+        <v>44.19678525633145</v>
       </c>
       <c r="C6" t="n">
-        <v>47.23080082031843</v>
+        <v>47.2291415774292</v>
       </c>
       <c r="D6" t="n">
-        <v>37.97366025560927</v>
+        <v>38.08633997549875</v>
       </c>
       <c r="E6" t="n">
-        <v>42.68366694588477</v>
+        <v>42.18856361151303</v>
       </c>
       <c r="F6" t="n">
-        <v>833.3714219426215</v>
+        <v>832.5198143979144</v>
       </c>
       <c r="G6" t="n">
-        <v>176.7304972399348</v>
+        <v>176.4999176505941</v>
       </c>
       <c r="H6" t="n">
-        <v>197.0330154374454</v>
+        <v>196.7867604115469</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02127631948347766</v>
+        <v>0.02125917849868735</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02669872487933767</v>
+        <v>0.02669323551070672</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1493512067950888</v>
+        <v>0.1503313039175936</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1317473300790784</v>
+        <v>0.1298662136991961</v>
       </c>
       <c r="F7" t="n">
-        <v>1.022751616926985</v>
+        <v>1.021966454370635</v>
       </c>
       <c r="G7" t="n">
-        <v>1.509708957699653</v>
+        <v>1.508668249108777</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4769223593106033</v>
+        <v>0.4764641058509326</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-39.04190944992001</v>
+        <v>-39.049163102929</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.98975442760327</v>
+        <v>-13.99098817933897</v>
       </c>
       <c r="D8" t="n">
-        <v>-33.26451897210205</v>
+        <v>-33.22527341394701</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.5669893602164</v>
+        <v>-35.65327612227669</v>
       </c>
       <c r="F8" t="n">
-        <v>-67.16674854395552</v>
+        <v>-67.17596443662215</v>
       </c>
       <c r="G8" t="n">
-        <v>-86.0325010024402</v>
+        <v>-86.04146556272576</v>
       </c>
       <c r="H8" t="n">
-        <v>-45.8437369593729</v>
+        <v>-45.85602180297326</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-37.66133740856647</v>
+        <v>-37.66859106157546</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.44743814300689</v>
+        <v>-15.44867189474258</v>
       </c>
       <c r="D9" t="n">
-        <v>-34.72220268750567</v>
+        <v>-34.68295712935063</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.02467307562002</v>
+        <v>-37.1109598376803</v>
       </c>
       <c r="F9" t="n">
-        <v>-63.77240199543952</v>
+        <v>-63.78161788810615</v>
       </c>
       <c r="G9" t="n">
-        <v>-82.07785550020944</v>
+        <v>-82.086820060495</v>
       </c>
       <c r="H9" t="n">
-        <v>-45.11765146839133</v>
+        <v>-45.12993631199168</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9385254398229943</v>
+        <v>0.9392324051479917</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9425893741015557</v>
+        <v>0.9428230564483274</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5156252250957921</v>
+        <v>0.5067965339630909</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6555488402892704</v>
+        <v>0.6716623528050547</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7242452145166649</v>
+        <v>-0.7405235809919586</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.521135589930235</v>
+        <v>-1.502163735331327</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1344846791437856</v>
+        <v>0.1363045053401966</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04158424401283493</v>
+        <v>0.04137178690394046</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07660979208287302</v>
+        <v>0.07648556911680708</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01869761166543711</v>
+        <v>0.01883194736714325</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01196212702919046</v>
+        <v>0.0114618571857519</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02742566468960839</v>
+        <v>0.02759915942141217</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01640414050501717</v>
+        <v>0.01621590941466977</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03211392999749351</v>
+        <v>0.03199437156828744</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002628359008242374</v>
+        <v>0.002598132542609737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00806944899514961</v>
+        <v>0.008036603372081917</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00036961249718706</v>
+        <v>0.0003763494181530543</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002029202200561306</v>
+        <v>0.0001934275607533542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001169888659317886</v>
+        <v>0.001180933420336408</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004562732682664876</v>
+        <v>0.0004528397559486675</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002149417108036591</v>
+        <v>0.002139714344980523</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05126752391370559</v>
+        <v>0.0509718799203025</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08983011185092452</v>
+        <v>0.0896471046497427</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0192253087670149</v>
+        <v>0.01939972727006888</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01424500684647539</v>
+        <v>0.01390782372455713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03420363517694992</v>
+        <v>0.03436471184713191</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02136055402527022</v>
+        <v>0.02128003185967229</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03835535676339009</v>
+        <v>0.03826187987857923</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.33193237221295</v>
+        <v>43.17387670244013</v>
       </c>
       <c r="C6" t="n">
-        <v>47.88265094262937</v>
+        <v>47.883709733737</v>
       </c>
       <c r="D6" t="n">
-        <v>37.66528457251989</v>
+        <v>38.14949198418682</v>
       </c>
       <c r="E6" t="n">
-        <v>34.9919785528948</v>
+        <v>33.09551778083877</v>
       </c>
       <c r="F6" t="n">
-        <v>759.9416872389179</v>
+        <v>783.5916712224741</v>
       </c>
       <c r="G6" t="n">
-        <v>176.0578761905909</v>
+        <v>174.8170289591872</v>
       </c>
       <c r="H6" t="n">
-        <v>183.311901644961</v>
+        <v>186.7852160638107</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02028221935887137</v>
+        <v>0.02004897123542932</v>
       </c>
       <c r="C7" t="n">
-        <v>0.022871802066138</v>
+        <v>0.02277870542595912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1455711612192933</v>
+        <v>0.1482244844037799</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1034773920672582</v>
+        <v>0.09863669345101095</v>
       </c>
       <c r="F7" t="n">
-        <v>1.036184972833044</v>
+        <v>1.045967455383646</v>
       </c>
       <c r="G7" t="n">
-        <v>1.513320136533714</v>
+        <v>1.501932216857125</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4736179473463865</v>
+        <v>0.4729314211261584</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-35.47256020892719</v>
+        <v>-33.57666110377835</v>
       </c>
       <c r="C8" t="n">
-        <v>-10.91802046322179</v>
+        <v>-8.942492507285181</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.41833243619698</v>
+        <v>-27.30995525506653</v>
       </c>
       <c r="E8" t="n">
-        <v>-33.01618596491194</v>
+        <v>-31.3036448717052</v>
       </c>
       <c r="F8" t="n">
-        <v>-63.01016037212307</v>
+        <v>-60.89740142828575</v>
       </c>
       <c r="G8" t="n">
-        <v>-82.00144252056046</v>
+        <v>-80.09963905096384</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.30611699432357</v>
+        <v>-40.35496570284747</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-33.69753901290122</v>
+        <v>-31.60441533041615</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.79218524016929</v>
+        <v>-11.02489781500463</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.29249721314449</v>
+        <v>-29.39236056278598</v>
       </c>
       <c r="E9" t="n">
-        <v>-34.89035074185945</v>
+        <v>-33.38605017942464</v>
       </c>
       <c r="F9" t="n">
-        <v>-58.64600052403107</v>
+        <v>-56.04833493040574</v>
       </c>
       <c r="G9" t="n">
-        <v>-76.91689830340663</v>
+        <v>-74.45014547634848</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.37257850591869</v>
+        <v>-39.31770071573094</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9336969435163562</v>
+        <v>0.9358131128763757</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9434883298401361</v>
+        <v>0.943774706654231</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1863465045225678</v>
+        <v>0.2057394787563328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06668576086833367</v>
+        <v>-0.03138328285661385</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.06449221183419862</v>
+        <v>-0.1112198767222419</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.261614239708514</v>
+        <v>-1.192569838362807</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1340185145341136</v>
+        <v>0.1250257167242129</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04617249788653872</v>
+        <v>0.04556751026500342</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0808131342371689</v>
+        <v>0.08055568433030515</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02223138199251444</v>
+        <v>0.02201751105135504</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01991163594221619</v>
+        <v>0.0208802235517236</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01691018480672899</v>
+        <v>0.01742292196777944</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01569061850176814</v>
+        <v>0.01583356006243482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03362157556115589</v>
+        <v>0.03371290187143358</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002834802482213976</v>
+        <v>0.002744325172830081</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007943094729404397</v>
+        <v>0.007902842545099346</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006208756440049316</v>
+        <v>0.0006060774216246606</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005498263700002239</v>
+        <v>0.0006075999944237064</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007222507309704963</v>
+        <v>0.0007539551340151945</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000409305284821427</v>
+        <v>0.0003968096797522921</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002180025873569242</v>
+        <v>0.002168601657957547</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05324286320450823</v>
+        <v>0.05238630711197422</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08912404125377393</v>
+        <v>0.0888979333004955</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02491737634673706</v>
+        <v>0.02461863971921805</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02344837670288125</v>
+        <v>0.02464954349321111</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02687472290034813</v>
+        <v>0.02745824346194043</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02023129468969861</v>
+        <v>0.01992008232292959</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03963977918299121</v>
+        <v>0.03965512490162815</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.23337188276405</v>
+        <v>43.4944801493773</v>
       </c>
       <c r="C6" t="n">
-        <v>47.96661040478878</v>
+        <v>48.03569023029152</v>
       </c>
       <c r="D6" t="n">
-        <v>43.51744513075124</v>
+        <v>43.15843694188957</v>
       </c>
       <c r="E6" t="n">
-        <v>56.86849576688216</v>
+        <v>61.20307556639113</v>
       </c>
       <c r="F6" t="n">
-        <v>302.5312476143407</v>
+        <v>314.5882183906316</v>
       </c>
       <c r="G6" t="n">
-        <v>118.2133552369122</v>
+        <v>123.4067548840012</v>
       </c>
       <c r="H6" t="n">
-        <v>102.2217543394065</v>
+        <v>105.6477760270971</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02187527868264291</v>
+        <v>0.02117709375806835</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02251366735854226</v>
+        <v>0.02239957778530024</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2445306615940331</v>
+        <v>0.2387024105682374</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2803791501985001</v>
+        <v>0.6196806097061616</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6397064781238779</v>
+        <v>0.6677874632209665</v>
       </c>
       <c r="G7" t="n">
-        <v>1.357541571223859</v>
+        <v>1.316097436569337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4277578011969091</v>
+        <v>0.4809740986013453</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.79204713865669</v>
+        <v>-21.08398065629341</v>
       </c>
       <c r="C8" t="n">
-        <v>4.987286108482635</v>
+        <v>2.95680338964803</v>
       </c>
       <c r="D8" t="n">
-        <v>-10.30627848370119</v>
+        <v>-12.45101692959305</v>
       </c>
       <c r="E8" t="n">
-        <v>-11.03544812292384</v>
+        <v>-12.43596277852138</v>
       </c>
       <c r="F8" t="n">
-        <v>-52.79765847853247</v>
+        <v>-54.28213234822452</v>
       </c>
       <c r="G8" t="n">
-        <v>-67.41364041505176</v>
+        <v>-69.81669924808294</v>
       </c>
       <c r="H8" t="n">
-        <v>-25.89296442173055</v>
+        <v>-27.85216476184454</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-15.43922932394096</v>
+        <v>-17.9283874189139</v>
       </c>
       <c r="C9" t="n">
-        <v>1.447197085359569</v>
+        <v>-0.3750451027030905</v>
       </c>
       <c r="D9" t="n">
-        <v>-13.84636750682426</v>
+        <v>-15.78286542194417</v>
       </c>
       <c r="E9" t="n">
-        <v>-14.5755371460469</v>
+        <v>-15.7678112708725</v>
       </c>
       <c r="F9" t="n">
-        <v>-44.55424543213646</v>
+        <v>-46.52362595161652</v>
       </c>
       <c r="G9" t="n">
-        <v>-57.80950133820564</v>
+        <v>-60.77750952869835</v>
       </c>
       <c r="H9" t="n">
-        <v>-24.12961394363244</v>
+        <v>-26.19254078245809</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.448280832341596</v>
+        <v>0.4162374192462812</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4491807539171339</v>
+        <v>0.2817603367638428</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.71370542874145</v>
+        <v>-1.265173408132207</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.334432470725763</v>
+        <v>-3.983967496021629</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.546987671516842</v>
+        <v>-0.4280669799352117</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.16693341150667</v>
+        <v>-7.31777423988183</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.310766232705333</v>
+        <v>-2.049497394660126</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1144332706032529</v>
+        <v>0.1243274640754534</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2028322889978678</v>
+        <v>0.2300398139027217</v>
       </c>
       <c r="D3" t="n">
-        <v>0.051020064726274</v>
+        <v>0.0323135403454342</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03937048468429454</v>
+        <v>0.04321077671551604</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03805915526035029</v>
+        <v>0.02988180235585568</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04349829588165374</v>
+        <v>0.03595384687526545</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08153559335894887</v>
+        <v>0.0826212073783744</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02358888034594448</v>
+        <v>0.02495890386821777</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07742134391070803</v>
+        <v>0.1009534078069451</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003596893407312308</v>
+        <v>0.001728488854744849</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002553465029749795</v>
+        <v>0.002936113734947625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001728113824671557</v>
+        <v>0.0009689337401124044</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002382941942793966</v>
+        <v>0.001505344675745387</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01854527307686336</v>
+        <v>0.02217519878011886</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1535867193019777</v>
+        <v>0.1579838721775668</v>
       </c>
       <c r="C5" t="n">
-        <v>0.278246911772095</v>
+        <v>0.3177316600638739</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05997410614016942</v>
+        <v>0.04157509897456468</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05053182195161575</v>
+        <v>0.05418591823479256</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04157058845712382</v>
+        <v>0.0311277005272218</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04881538633252804</v>
+        <v>0.03879877157521081</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1054542556592516</v>
+        <v>0.1069005035922051</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.71875056638737</v>
+        <v>64.44883879792251</v>
       </c>
       <c r="C6" t="n">
-        <v>55.6807416309262</v>
+        <v>64.13716768228836</v>
       </c>
       <c r="D6" t="n">
-        <v>111.8739470907354</v>
+        <v>52.93980662439227</v>
       </c>
       <c r="E6" t="n">
-        <v>176.112932285789</v>
+        <v>84.0129510172343</v>
       </c>
       <c r="F6" t="n">
-        <v>2344.053784687562</v>
+        <v>1852.151759251489</v>
       </c>
       <c r="G6" t="n">
-        <v>761.4118486205995</v>
+        <v>598.3684736076568</v>
       </c>
       <c r="H6" t="n">
-        <v>584.6420008136666</v>
+        <v>452.6764994968304</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1820279665396824</v>
+        <v>0.1926000069338681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2194407145623555</v>
+        <v>0.2861392844357087</v>
       </c>
       <c r="D7" t="n">
-        <v>2.833258908015108</v>
+        <v>1.361523929275967</v>
       </c>
       <c r="E7" t="n">
-        <v>2.604234333477108</v>
+        <v>2.994491056841905</v>
       </c>
       <c r="F7" t="n">
-        <v>1.530611962264646</v>
+        <v>0.8581966951972845</v>
       </c>
       <c r="G7" t="n">
-        <v>7.903496165623917</v>
+        <v>4.992772026475143</v>
       </c>
       <c r="H7" t="n">
-        <v>2.545511675080469</v>
+        <v>1.780953833193313</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-31.72281864792001</v>
+        <v>-25.21472186783235</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.35095665168784</v>
+        <v>-5.758577064511982</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.76610849089479</v>
+        <v>-30.16304647934857</v>
       </c>
       <c r="E8" t="n">
-        <v>-33.8218240419812</v>
+        <v>-26.98401058551392</v>
       </c>
       <c r="F8" t="n">
-        <v>-74.32869688012785</v>
+        <v>-75.27177193682158</v>
       </c>
       <c r="G8" t="n">
-        <v>-76.5124527750759</v>
+        <v>-76.48353402545739</v>
       </c>
       <c r="H8" t="n">
-        <v>-43.58380958128127</v>
+        <v>-39.97927699324763</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-31.52559407058379</v>
+        <v>-24.42582355848747</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.55919718245978</v>
+        <v>-6.591539187599762</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.97434902166674</v>
+        <v>-30.99600860243635</v>
       </c>
       <c r="E9" t="n">
-        <v>-34.03006457275315</v>
+        <v>-27.8169727086017</v>
       </c>
       <c r="F9" t="n">
-        <v>-73.84379023033985</v>
+        <v>-73.33214533766957</v>
       </c>
       <c r="G9" t="n">
-        <v>-75.94750341761436</v>
+        <v>-74.22373659561124</v>
       </c>
       <c r="H9" t="n">
-        <v>-43.48008308256961</v>
+        <v>-39.56437099840102</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9282439994464955</v>
+        <v>0.9271647436627009</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9425693805273799</v>
+        <v>0.9451837350311079</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7166031026568207</v>
+        <v>0.4009486773044051</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7547803742105714</v>
+        <v>0.7518781430271312</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3815894917686955</v>
+        <v>-0.4359809968875115</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.660066707620458</v>
+        <v>-1.744756703890023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2167567762420191</v>
+        <v>0.1407395997079683</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04772571528319081</v>
+        <v>0.04653925875319775</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07203745105178271</v>
+        <v>0.07103195556293429</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01290635808684235</v>
+        <v>0.0206468769891227</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009617602215986164</v>
+        <v>0.008509364270772856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0219142640456308</v>
+        <v>0.02220954862413657</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01744304055619234</v>
+        <v>0.0173390692904988</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03027407187327086</v>
+        <v>0.03104601224844383</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003067944364420093</v>
+        <v>0.003114088194540495</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008072259226261322</v>
+        <v>0.00770479414479034</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000216252043560263</v>
+        <v>0.0004571188814870025</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001444617590170443</v>
+        <v>0.000146171497462669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009373990802729508</v>
+        <v>0.0009743033468273867</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004814169199548875</v>
+        <v>0.0004967440533077035</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002153288898914427</v>
+        <v>0.002148870019735933</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05538902747313851</v>
+        <v>0.05580401593559818</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08984575241079192</v>
+        <v>0.08777695679841231</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01470551065282206</v>
+        <v>0.02138033866633086</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01201922455972282</v>
+        <v>0.01209014050632452</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03061697372819448</v>
+        <v>0.03121383261996813</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02194121509750286</v>
+        <v>0.02228775568126373</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0374196173203621</v>
+        <v>0.03842550670131629</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.81558969588245</v>
+        <v>43.02962451016955</v>
       </c>
       <c r="C6" t="n">
-        <v>49.68996211065122</v>
+        <v>50.0472591156189</v>
       </c>
       <c r="D6" t="n">
-        <v>26.46816461022251</v>
+        <v>41.37646466153178</v>
       </c>
       <c r="E6" t="n">
-        <v>29.13846783755145</v>
+        <v>24.30424047984752</v>
       </c>
       <c r="F6" t="n">
-        <v>381.7001799426002</v>
+        <v>380.9520231500121</v>
       </c>
       <c r="G6" t="n">
-        <v>200.1785313575592</v>
+        <v>200.0102884352038</v>
       </c>
       <c r="H6" t="n">
-        <v>121.3318159257445</v>
+        <v>123.2866500587306</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02367436122114542</v>
+        <v>0.02403043863736809</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02287976730016895</v>
+        <v>0.02183823539202088</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08517044563344599</v>
+        <v>0.1800353800257194</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07366701096814052</v>
+        <v>0.07453887714008453</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8302660537735995</v>
+        <v>0.8629526228180653</v>
       </c>
       <c r="G7" t="n">
-        <v>1.596714008260212</v>
+        <v>1.647549464008645</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4387286078594521</v>
+        <v>0.4684908363369839</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-38.08072776814659</v>
+        <v>-37.94636995622662</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.91593129315263</v>
+        <v>-15.1954751659661</v>
       </c>
       <c r="D8" t="n">
-        <v>-36.63439577324368</v>
+        <v>-32.14340239812598</v>
       </c>
       <c r="E8" t="n">
-        <v>-39.05497437350029</v>
+        <v>-38.98437991270387</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.66881744347589</v>
+        <v>-69.20545430115007</v>
       </c>
       <c r="G8" t="n">
-        <v>-85.30409951592222</v>
+        <v>-84.89666342141793</v>
       </c>
       <c r="H8" t="n">
-        <v>-47.27649102790688</v>
+        <v>-46.3952908592651</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-36.70015572679305</v>
+        <v>-36.56579791487308</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.37361500855624</v>
+        <v>-16.65315888136972</v>
       </c>
       <c r="D9" t="n">
-        <v>-38.0920794886473</v>
+        <v>-33.60108611352959</v>
       </c>
       <c r="E9" t="n">
-        <v>-40.5126580889039</v>
+        <v>-40.44206362810749</v>
       </c>
       <c r="F9" t="n">
-        <v>-66.27447089495989</v>
+        <v>-65.81110775263407</v>
       </c>
       <c r="G9" t="n">
-        <v>-81.34945401369146</v>
+        <v>-80.94201791918717</v>
       </c>
       <c r="H9" t="n">
-        <v>-46.5504055369253</v>
+        <v>-45.66920536828351</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5204749795915369</v>
+        <v>0.4956584956651561</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4833528572086732</v>
+        <v>0.4465422460389288</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1066580322499653</v>
+        <v>-0.2556606856119352</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7388993966432549</v>
+        <v>-1.03133615224063</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5197305843865432</v>
+        <v>0.6120746889689053</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.723395645732912</v>
+        <v>-1.880284362880962</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1386797648232414</v>
+        <v>-0.2688342950100895</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07959923178231747</v>
+        <v>0.08228677411251198</v>
       </c>
       <c r="C3" t="n">
-        <v>0.185879000282654</v>
+        <v>0.2080917606389486</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02228223194860497</v>
+        <v>0.02440999665061739</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02954674234512354</v>
+        <v>0.03158802472897491</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01603955057628793</v>
+        <v>0.0141545821709507</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01950257437179831</v>
+        <v>0.01964857561168319</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05880822188446438</v>
+        <v>0.06336328565228114</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02050220291839723</v>
+        <v>0.02156323741613086</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07261822531980737</v>
+        <v>0.07779220391115706</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006816836314553999</v>
+        <v>0.0009581586525029658</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001024406039215116</v>
+        <v>0.001196683963458876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003258595343707599</v>
+        <v>0.0002632046870229287</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004928781446838658</v>
+        <v>0.000521271749539231</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01594087593132162</v>
+        <v>0.01704912672996865</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.143185903350844</v>
+        <v>0.1468442624556059</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2694776898368534</v>
+        <v>0.2789125381031786</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02610907182293924</v>
+        <v>0.03095413788983576</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03200634373393994</v>
+        <v>0.03459312017524404</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01805157983032953</v>
+        <v>0.01622358428408867</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02220085909787875</v>
+        <v>0.02283137642673413</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08517190794546414</v>
+        <v>0.08839316988911451</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.98563933142902</v>
+        <v>37.11232068680539</v>
       </c>
       <c r="C6" t="n">
-        <v>40.71617483647502</v>
+        <v>52.61839931689375</v>
       </c>
       <c r="D6" t="n">
-        <v>40.25916753447245</v>
+        <v>37.32888307127421</v>
       </c>
       <c r="E6" t="n">
-        <v>63.59632572616903</v>
+        <v>61.98757982354242</v>
       </c>
       <c r="F6" t="n">
-        <v>845.4264486569425</v>
+        <v>673.1618134103027</v>
       </c>
       <c r="G6" t="n">
-        <v>231.7647463158937</v>
+        <v>220.21239874734</v>
       </c>
       <c r="H6" t="n">
-        <v>209.6247504002303</v>
+        <v>180.4035658426931</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.158209048165417</v>
+        <v>0.1663967174917448</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2058269005612632</v>
+        <v>0.2204918689261313</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2684797688670292</v>
+        <v>0.7547378334806655</v>
       </c>
       <c r="E7" t="n">
-        <v>1.044773806440854</v>
+        <v>1.220477048893221</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1443089263580966</v>
+        <v>0.1165618365902445</v>
       </c>
       <c r="G7" t="n">
-        <v>1.634727416842305</v>
+        <v>1.728900398177932</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5760543112058275</v>
+        <v>0.7012609505933232</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-16.98500645259404</v>
+        <v>-14.53088847189727</v>
       </c>
       <c r="C8" t="n">
-        <v>2.264763892841358</v>
+        <v>4.677715642302232</v>
       </c>
       <c r="D8" t="n">
-        <v>-25.74566934746716</v>
+        <v>-21.70298311398543</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.30185384972889</v>
+        <v>-20.36920546666367</v>
       </c>
       <c r="F8" t="n">
-        <v>-78.34852974737625</v>
+        <v>-78.91094261000553</v>
       </c>
       <c r="G8" t="n">
-        <v>-80.99823161150024</v>
+        <v>-78.27010777983128</v>
       </c>
       <c r="H8" t="n">
-        <v>-37.1857545193042</v>
+        <v>-34.85106863334682</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-15.20998525656806</v>
+        <v>-12.55864269853507</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3905991158938527</v>
+        <v>2.595310334582781</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.61983412441467</v>
+        <v>-23.78538842170488</v>
       </c>
       <c r="E9" t="n">
-        <v>-25.17601862667639</v>
+        <v>-22.45161077438312</v>
       </c>
       <c r="F9" t="n">
-        <v>-73.98436989928425</v>
+        <v>-74.06187611212553</v>
       </c>
       <c r="G9" t="n">
-        <v>-75.91368739434641</v>
+        <v>-72.62061420521592</v>
       </c>
       <c r="H9" t="n">
-        <v>-36.25221603089932</v>
+        <v>-33.81380364623029</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global_ind/metrics_summary.xlsx
+++ b/results/cross_validation/global_ind/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7456102071640792</v>
+        <v>0.7824659118456879</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5396718421211117</v>
+        <v>0.5094093324748276</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3795260019227649</v>
+        <v>-0.1585806370570255</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.232143957129213</v>
+        <v>-2.426337250544142</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.86660285347648</v>
+        <v>-13.10425060541587</v>
       </c>
       <c r="G2" t="n">
-        <v>-18.15854850863077</v>
+        <v>-26.85398314701063</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.391923211979005</v>
+        <v>-6.875212732617858</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09115453133246176</v>
+        <v>0.08879918632510617</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1887987623139842</v>
+        <v>0.1934150974688515</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01920172180727735</v>
+        <v>0.02048626366742287</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04463545761255151</v>
+        <v>0.04007148314460696</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08723102244700905</v>
+        <v>0.09075855340228256</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05385080423490637</v>
+        <v>0.06381530523248177</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08081204995803169</v>
+        <v>0.08289098154012532</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0108764943039853</v>
+        <v>0.009300720144298657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06470221379585288</v>
+        <v>0.06895581216073432</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001052676722494461</v>
+        <v>0.0008840796520419748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002493205666112705</v>
+        <v>0.002018494842983918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008729902588970649</v>
+        <v>0.009569637670777722</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003467300044547346</v>
+        <v>0.005040993421967398</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01522029885366055</v>
+        <v>0.015961622982134</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1042904324661917</v>
+        <v>0.09644024131190598</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2543662984670982</v>
+        <v>0.2625943871462875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03244497992747817</v>
+        <v>0.02973347695850546</v>
       </c>
       <c r="E5" t="n">
-        <v>0.049932010435318</v>
+        <v>0.04492766233606994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09343394773298755</v>
+        <v>0.09782452489420904</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05888378422407434</v>
+        <v>0.07099995367581163</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09889190887552467</v>
+        <v>0.1004200410537983</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55.000969110065</v>
+        <v>64.73390094308097</v>
       </c>
       <c r="C6" t="n">
-        <v>42.27212509827788</v>
+        <v>199729669.8538492</v>
       </c>
       <c r="D6" t="n">
-        <v>34.97600521322535</v>
+        <v>40.76865592961261</v>
       </c>
       <c r="E6" t="n">
-        <v>106.9105328964537</v>
+        <v>195604688.7036716</v>
       </c>
       <c r="F6" t="n">
-        <v>5702.477411417667</v>
+        <v>104913387.589027</v>
       </c>
       <c r="G6" t="n">
-        <v>791.7282866366028</v>
+        <v>981.4755299282332</v>
       </c>
       <c r="H6" t="n">
-        <v>1122.227555062049</v>
+        <v>83374805.52077244</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08393048386356596</v>
+        <v>0.07227073054730269</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1833899970207635</v>
+        <v>0.1959462687700658</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8291893485651513</v>
+        <v>0.6973860937470742</v>
       </c>
       <c r="E7" t="n">
-        <v>2.542776862210086</v>
+        <v>2.059628243106662</v>
       </c>
       <c r="F7" t="n">
-        <v>7.732183575710448</v>
+        <v>8.476947855988609</v>
       </c>
       <c r="G7" t="n">
-        <v>11.49998332524083</v>
+        <v>16.72044727899714</v>
       </c>
       <c r="H7" t="n">
-        <v>3.811908932101807</v>
+        <v>4.703771078526142</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.69036173765498</v>
+        <v>-40.09897102255025</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.427759170448624</v>
+        <v>-14.04573629799032</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.13851459486666</v>
+        <v>-40.18578037159529</v>
       </c>
       <c r="E8" t="n">
-        <v>-25.96511588243321</v>
+        <v>-35.23241903529991</v>
       </c>
       <c r="F8" t="n">
-        <v>-46.89201280863669</v>
+        <v>-53.78991922212141</v>
       </c>
       <c r="G8" t="n">
-        <v>-63.63692794943661</v>
+        <v>-66.77197741425418</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.12511535724613</v>
+        <v>-41.6874672273019</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-29.70423885097388</v>
+        <v>-39.90174644521403</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.46896182430835</v>
+        <v>-14.25397682876226</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.17971724872638</v>
+        <v>-40.39402090236724</v>
       </c>
       <c r="E9" t="n">
-        <v>-27.00631853629294</v>
+        <v>-35.44065956607186</v>
       </c>
       <c r="F9" t="n">
-        <v>-44.46747955969668</v>
+        <v>-53.30501257233341</v>
       </c>
       <c r="G9" t="n">
-        <v>-60.81218116212893</v>
+        <v>-66.20702805679264</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.60648286368786</v>
+        <v>-41.58374072859024</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9355643174542618</v>
+        <v>0.9261987934798601</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9329971747091542</v>
+        <v>0.9262391443112855</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4997862839986079</v>
+        <v>0.7246641793956985</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5677068485949638</v>
+        <v>0.707502210414482</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7005851412101622</v>
+        <v>-0.3502468801472898</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.51338571687679</v>
+        <v>-1.750042046232926</v>
       </c>
       <c r="H2" t="n">
-        <v>0.120347294445006</v>
+        <v>0.1973859002035184</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04132844785361608</v>
+        <v>0.04704892059786654</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08669302706395231</v>
+        <v>0.08990934521939349</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01899601823993391</v>
+        <v>0.01319883098359961</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01447581613749631</v>
+        <v>0.01054873012113107</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02771644731603462</v>
+        <v>0.02219347153061002</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01687544767935921</v>
+        <v>0.01807381062831841</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03434753404839874</v>
+        <v>0.03349551818015319</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002754962478522706</v>
+        <v>0.003155387617542021</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009417697033504254</v>
+        <v>0.01036758349958839</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003816987388227578</v>
+        <v>0.000210100867120362</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002546689681217399</v>
+        <v>0.0001723138257241899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001153835460383727</v>
+        <v>0.000916133282837866</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004548707019305599</v>
+        <v>0.0004977005906848822</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002402955563547624</v>
+        <v>0.002553203280582951</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05248773645836431</v>
+        <v>0.05617283700813072</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09704481971493509</v>
+        <v>0.101821331260146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01953711183421843</v>
+        <v>0.01449485657467372</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01595835104645025</v>
+        <v>0.01312683608963675</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0339681536204682</v>
+        <v>0.0302676937152117</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0213276979988596</v>
+        <v>0.02230920416968929</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04005397844554932</v>
+        <v>0.03969879313624803</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.19678525633145</v>
+        <v>49.07413259799511</v>
       </c>
       <c r="C6" t="n">
-        <v>47.2291415774292</v>
+        <v>119061148.570011</v>
       </c>
       <c r="D6" t="n">
-        <v>38.08633997549875</v>
+        <v>26.18933101133058</v>
       </c>
       <c r="E6" t="n">
-        <v>42.18856361151303</v>
+        <v>38882905.13824324</v>
       </c>
       <c r="F6" t="n">
-        <v>832.5198143979144</v>
+        <v>12017048.46166951</v>
       </c>
       <c r="G6" t="n">
-        <v>176.4999176505941</v>
+        <v>216.1059097492752</v>
       </c>
       <c r="H6" t="n">
-        <v>196.7867604115469</v>
+        <v>28326898.92321618</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02125917849868735</v>
+        <v>0.02584913328832138</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02669323551070672</v>
+        <v>0.03088556515632622</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1503313039175936</v>
+        <v>0.08424781678827471</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1298662136991961</v>
+        <v>0.08936995655366234</v>
       </c>
       <c r="F7" t="n">
-        <v>1.021966454370635</v>
+        <v>0.814430714684347</v>
       </c>
       <c r="G7" t="n">
-        <v>1.508668249108777</v>
+        <v>1.653722008566715</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4764641058509326</v>
+        <v>0.4497508658396077</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-39.049163102929</v>
+        <v>-45.82779539124397</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.99098817933897</v>
+        <v>-21.41442787140553</v>
       </c>
       <c r="D8" t="n">
-        <v>-33.22527341394701</v>
+        <v>-44.80753693765547</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.65327612227669</v>
+        <v>-45.99715905293696</v>
       </c>
       <c r="F8" t="n">
-        <v>-67.17596443662215</v>
+        <v>-77.94418438312198</v>
       </c>
       <c r="G8" t="n">
-        <v>-86.04146556272576</v>
+        <v>-92.87165450852677</v>
       </c>
       <c r="H8" t="n">
-        <v>-45.85602180297326</v>
+        <v>-54.81045969081512</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-37.66859106157546</v>
+        <v>-45.23612165923532</v>
       </c>
       <c r="C9" t="n">
-        <v>-15.44867189474258</v>
+        <v>-22.03914946372137</v>
       </c>
       <c r="D9" t="n">
-        <v>-34.68295712935063</v>
+        <v>-45.43225852997131</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.1109598376803</v>
+        <v>-46.62188064525279</v>
       </c>
       <c r="F9" t="n">
-        <v>-63.78161788810615</v>
+        <v>-76.48946443375797</v>
       </c>
       <c r="G9" t="n">
-        <v>-82.086820060495</v>
+        <v>-91.17680643614216</v>
       </c>
       <c r="H9" t="n">
-        <v>-45.12993631199168</v>
+        <v>-54.49928019468015</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9392324051479917</v>
+        <v>0.93205460833799</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9428230564483274</v>
+        <v>0.9352803955330585</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5067965339630909</v>
+        <v>0.6114646215201138</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6716623528050547</v>
+        <v>0.6682839361321029</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7405235809919586</v>
+        <v>-0.1681270518406408</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.502163735331327</v>
+        <v>-1.013013264634492</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1363045053401966</v>
+        <v>0.327657207508022</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04137178690394046</v>
+        <v>0.04270291016760745</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07648556911680708</v>
+        <v>0.08321359295909064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01883194736714325</v>
+        <v>0.01671975596259745</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0114618571857519</v>
+        <v>0.01006887919111687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02759915942141217</v>
+        <v>0.01995266357936643</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01621590941466977</v>
+        <v>0.01445023460367513</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03199437156828744</v>
+        <v>0.03118467274390899</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002598132542609737</v>
+        <v>0.002905020901803853</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008036603372081917</v>
+        <v>0.009096774937143394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003763494181530543</v>
+        <v>0.0002964802027807304</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001934275607533542</v>
+        <v>0.0001954177640119749</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001180933420336408</v>
+        <v>0.0007925662236358935</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004528397559486675</v>
+        <v>0.0003643136628538049</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002139714344980523</v>
+        <v>0.002275095615371609</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0509718799203025</v>
+        <v>0.05389824581379113</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0896471046497427</v>
+        <v>0.0953770147212807</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01939972727006888</v>
+        <v>0.01721860048844651</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01390782372455713</v>
+        <v>0.01397919039186372</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03436471184713191</v>
+        <v>0.02815255270194682</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02128003185967229</v>
+        <v>0.01908700245857911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03826187987857923</v>
+        <v>0.03795210109598467</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.17387670244013</v>
+        <v>44.14342649723626</v>
       </c>
       <c r="C6" t="n">
-        <v>47.883709733737</v>
+        <v>114598081.5985517</v>
       </c>
       <c r="D6" t="n">
-        <v>38.14949198418682</v>
+        <v>33.07957751816367</v>
       </c>
       <c r="E6" t="n">
-        <v>33.09551778083877</v>
+        <v>19793230.46929319</v>
       </c>
       <c r="F6" t="n">
-        <v>783.5916712224741</v>
+        <v>8102515.912503227</v>
       </c>
       <c r="G6" t="n">
-        <v>174.8170289591872</v>
+        <v>155.0776223519975</v>
       </c>
       <c r="H6" t="n">
-        <v>186.7852160638107</v>
+        <v>23749010.04682909</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02004897123542932</v>
+        <v>0.02441713212986569</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02277870542595912</v>
+        <v>0.02778362379608282</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1482244844037799</v>
+        <v>0.1187681496859124</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09863669345101095</v>
+        <v>0.1016516115951775</v>
       </c>
       <c r="F7" t="n">
-        <v>1.045967455383646</v>
+        <v>0.7059858238174749</v>
       </c>
       <c r="G7" t="n">
-        <v>1.501932216857125</v>
+        <v>1.212317997908691</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4729314211261584</v>
+        <v>0.3651540564888673</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-33.57666110377835</v>
+        <v>-44.5718322423185</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.942492507285181</v>
+        <v>-20.19901198471876</v>
       </c>
       <c r="D8" t="n">
-        <v>-27.30995525506653</v>
+        <v>-40.74118066879929</v>
       </c>
       <c r="E8" t="n">
-        <v>-31.3036448717052</v>
+        <v>-43.24222546884742</v>
       </c>
       <c r="F8" t="n">
-        <v>-60.89740142828575</v>
+        <v>-77.68281391307833</v>
       </c>
       <c r="G8" t="n">
-        <v>-80.09963905096384</v>
+        <v>-94.9274395532578</v>
       </c>
       <c r="H8" t="n">
-        <v>-40.35496570284747</v>
+        <v>-53.56075063850335</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-31.60441533041615</v>
+        <v>-43.78293393297362</v>
       </c>
       <c r="C9" t="n">
-        <v>-11.02489781500463</v>
+        <v>-21.03197410780654</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.39236056278598</v>
+        <v>-41.57414279188707</v>
       </c>
       <c r="E9" t="n">
-        <v>-33.38605017942464</v>
+        <v>-44.0751875919352</v>
       </c>
       <c r="F9" t="n">
-        <v>-56.04833493040574</v>
+        <v>-75.74318731392633</v>
       </c>
       <c r="G9" t="n">
-        <v>-74.45014547634848</v>
+        <v>-92.66764212341165</v>
       </c>
       <c r="H9" t="n">
-        <v>-39.31770071573094</v>
+        <v>-53.14584464365674</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9358131128763757</v>
+        <v>0.9323208969051008</v>
       </c>
       <c r="C2" t="n">
-        <v>0.943774706654231</v>
+        <v>0.9337066933935512</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2057394787563328</v>
+        <v>0.6129539214285118</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03138328285661385</v>
+        <v>0.66095927857297</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1112198767222419</v>
+        <v>-0.1821857810364818</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.192569838362807</v>
+        <v>-1.059799789741832</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1250257167242129</v>
+        <v>0.3163258699203034</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04556751026500342</v>
+        <v>0.04253358898377054</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08055568433030515</v>
+        <v>0.08493333960219897</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02201751105135504</v>
+        <v>0.01668361393389615</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0208802235517236</v>
+        <v>0.0102432700111141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01742292196777944</v>
+        <v>0.02001576446133205</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01583356006243482</v>
+        <v>0.01473915403606692</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03371290187143358</v>
+        <v>0.03152478850472979</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002744325172830081</v>
+        <v>0.002893635672659596</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007902842545099346</v>
+        <v>0.00931796933873329</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006060774216246606</v>
+        <v>0.0002953437607388997</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006075999944237064</v>
+        <v>0.0001997328043680826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007539551340151945</v>
+        <v>0.0008021049753412923</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003968096797522921</v>
+        <v>0.0003727810538211223</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002168601657957547</v>
+        <v>0.002313594600943714</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05238630711197422</v>
+        <v>0.05379252431945908</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0888979333004955</v>
+        <v>0.09652962933075673</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02461863971921805</v>
+        <v>0.01718556838568046</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02464954349321111</v>
+        <v>0.01413268567428295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02745824346194043</v>
+        <v>0.02832145786045083</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01992008232292959</v>
+        <v>0.01930753878206962</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03965512490162815</v>
+        <v>0.03821156739211661</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.4944801493773</v>
+        <v>44.0814627972389</v>
       </c>
       <c r="C6" t="n">
-        <v>48.03569023029152</v>
+        <v>115786675.8189136</v>
       </c>
       <c r="D6" t="n">
-        <v>43.15843694188957</v>
+        <v>32.898638136607</v>
       </c>
       <c r="E6" t="n">
-        <v>61.20307556639113</v>
+        <v>20557370.2816632</v>
       </c>
       <c r="F6" t="n">
-        <v>314.5882183906316</v>
+        <v>8794327.763580078</v>
       </c>
       <c r="G6" t="n">
-        <v>123.4067548840012</v>
+        <v>159.8589765614173</v>
       </c>
       <c r="H6" t="n">
-        <v>105.6477760270971</v>
+        <v>24189768.45053907</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02117709375806835</v>
+        <v>0.02432927589933149</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02239957778530024</v>
+        <v>0.02841057051904795</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2387024105682374</v>
+        <v>0.1183205642039637</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6196806097061616</v>
+        <v>0.1038520293911667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6677874632209665</v>
+        <v>0.714434415587367</v>
       </c>
       <c r="G7" t="n">
-        <v>1.316097436569337</v>
+        <v>1.240401767320449</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4809740986013453</v>
+        <v>0.3716247704868876</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.08398065629341</v>
+        <v>-44.60717394350542</v>
       </c>
       <c r="C8" t="n">
-        <v>2.95680338964803</v>
+        <v>-20.05486333680733</v>
       </c>
       <c r="D8" t="n">
-        <v>-12.45101692959305</v>
+        <v>-40.76422353644959</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.43596277852138</v>
+        <v>-43.11118037674167</v>
       </c>
       <c r="F8" t="n">
-        <v>-54.28213234822452</v>
+        <v>-77.53925280059937</v>
       </c>
       <c r="G8" t="n">
-        <v>-69.81669924808294</v>
+        <v>-94.62875087061423</v>
       </c>
       <c r="H8" t="n">
-        <v>-27.85216476184454</v>
+        <v>-53.45090747745294</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.9283874189139</v>
+        <v>-43.81827563416054</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3750451027030905</v>
+        <v>-20.88782545989511</v>
       </c>
       <c r="D9" t="n">
-        <v>-15.78286542194417</v>
+        <v>-41.59718565953737</v>
       </c>
       <c r="E9" t="n">
-        <v>-15.7678112708725</v>
+        <v>-43.94414249982945</v>
       </c>
       <c r="F9" t="n">
-        <v>-46.52362595161652</v>
+        <v>-75.59962620144736</v>
       </c>
       <c r="G9" t="n">
-        <v>-60.77750952869835</v>
+        <v>-92.36895344076808</v>
       </c>
       <c r="H9" t="n">
-        <v>-26.19254078245809</v>
+        <v>-53.03600148260632</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4162374192462812</v>
+        <v>0.3413256614529303</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2817603367638428</v>
+        <v>0.4043258201244568</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.265173408132207</v>
+        <v>-3.716872459481684</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.983967496021629</v>
+        <v>-1.63000463767415</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4280669799352117</v>
+        <v>-1.522317341546145</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.31777423988183</v>
+        <v>-3.725451833897227</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.049497394660126</v>
+        <v>-1.64149913183697</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1243274640754534</v>
+        <v>0.1226779301719572</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2300398139027217</v>
+        <v>0.2082971632956492</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0323135403454342</v>
+        <v>0.05045185157370972</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04321077671551604</v>
+        <v>0.03011463193908429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02988180235585568</v>
+        <v>0.03863281183736978</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03595384687526545</v>
+        <v>0.02680369460643026</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0826212073783744</v>
+        <v>0.07949634723736676</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02495890386821777</v>
+        <v>0.02816177336175296</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1009534078069451</v>
+        <v>0.0837260053553502</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001728488854744849</v>
+        <v>0.003599310077628795</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002936113734947625</v>
+        <v>0.001549366104380409</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009689337401124044</v>
+        <v>0.001711375082916304</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001505344675745387</v>
+        <v>0.0008552088038818331</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02217519878011886</v>
+        <v>0.01993383979765175</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1579838721775668</v>
+        <v>0.1678146994805668</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3177316600638739</v>
+        <v>0.2893544631681879</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04157509897456468</v>
+        <v>0.05999425037142139</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05418591823479256</v>
+        <v>0.0393619880643802</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0311277005272218</v>
+        <v>0.04136876941505879</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03879877157521081</v>
+        <v>0.029243953287506</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1069005035922051</v>
+        <v>0.1045230206311868</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.44883879792251</v>
+        <v>61.85794523621493</v>
       </c>
       <c r="C6" t="n">
-        <v>64.13716768228836</v>
+        <v>93878892.53670304</v>
       </c>
       <c r="D6" t="n">
-        <v>52.93980662439227</v>
+        <v>111.0482101422981</v>
       </c>
       <c r="E6" t="n">
-        <v>84.0129510172343</v>
+        <v>119890323.1232264</v>
       </c>
       <c r="F6" t="n">
-        <v>1852.151759251489</v>
+        <v>47315072.79105236</v>
       </c>
       <c r="G6" t="n">
-        <v>598.3684736076568</v>
+        <v>408.8521821716963</v>
       </c>
       <c r="H6" t="n">
-        <v>452.6764994968304</v>
+        <v>43514145.03488656</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1926000069338681</v>
+        <v>0.217815542917348</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2861392844357087</v>
+        <v>0.2378104577114081</v>
       </c>
       <c r="D7" t="n">
-        <v>1.361523929275967</v>
+        <v>2.836162509797691</v>
       </c>
       <c r="E7" t="n">
-        <v>2.994491056841905</v>
+        <v>1.581171895150623</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8581966951972845</v>
+        <v>1.51678633004377</v>
       </c>
       <c r="G7" t="n">
-        <v>4.992772026475143</v>
+        <v>2.837468392663771</v>
       </c>
       <c r="H7" t="n">
-        <v>1.780953833193313</v>
+        <v>1.537869188047435</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-25.21472186783235</v>
+        <v>-30.12810797662934</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.758577064511982</v>
+        <v>-12.88123391527929</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.16304647934857</v>
+        <v>-31.76207858193673</v>
       </c>
       <c r="E8" t="n">
-        <v>-26.98401058551392</v>
+        <v>-36.81945637969483</v>
       </c>
       <c r="F8" t="n">
-        <v>-75.27177193682158</v>
+        <v>-74.44549707472297</v>
       </c>
       <c r="G8" t="n">
-        <v>-76.48353402545739</v>
+        <v>-89.83414374909694</v>
       </c>
       <c r="H8" t="n">
-        <v>-39.97927699324763</v>
+        <v>-45.97841961289335</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-24.42582355848747</v>
+        <v>-29.93088339929312</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.591539187599762</v>
+        <v>-13.08947444605124</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.99600860243635</v>
+        <v>-31.97031911270867</v>
       </c>
       <c r="E9" t="n">
-        <v>-27.8169727086017</v>
+        <v>-37.02769691046678</v>
       </c>
       <c r="F9" t="n">
-        <v>-73.33214533766957</v>
+        <v>-73.96059042493496</v>
       </c>
       <c r="G9" t="n">
-        <v>-74.22373659561124</v>
+        <v>-89.26919439163539</v>
       </c>
       <c r="H9" t="n">
-        <v>-39.56437099840102</v>
+        <v>-45.8746931141817</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9271647436627009</v>
+        <v>0.9246121543050505</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9451837350311079</v>
+        <v>0.9432571508242535</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4009486773044051</v>
+        <v>0.7231532222561292</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7518781430271312</v>
+        <v>0.7578669421834958</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4359809968875115</v>
+        <v>-0.34351644617807</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.744756703890023</v>
+        <v>-1.631103423007457</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1407395997079683</v>
+        <v>0.2290449333972337</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04653925875319775</v>
+        <v>0.04968435160334696</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07103195556293429</v>
+        <v>0.07108350721120997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0206468769891227</v>
+        <v>0.01243963804579516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008509364270772856</v>
+        <v>0.009634098719231135</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02220954862413657</v>
+        <v>0.02157134488230331</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0173390692904988</v>
+        <v>0.01733920489729134</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03104601224844383</v>
+        <v>0.03029202422652964</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003114088194540495</v>
+        <v>0.003223224741645607</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00770479414479034</v>
+        <v>0.007975588424797925</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004571188814870025</v>
+        <v>0.0002112538351740953</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000146171497462669</v>
+        <v>0.0001426433806073592</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009743033468273867</v>
+        <v>0.0009115667293743451</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004967440533077035</v>
+        <v>0.0004761751659679581</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002148870019735933</v>
+        <v>0.002156742046261215</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05580401593559818</v>
+        <v>0.05677345102814877</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08777695679841231</v>
+        <v>0.08930614998306625</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02138033866633086</v>
+        <v>0.01453457378714957</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01209014050632452</v>
+        <v>0.01194334042918308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03121383261996813</v>
+        <v>0.03019216337684905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02228775568126373</v>
+        <v>0.02182143821951152</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03842550670131629</v>
+        <v>0.03742851947065137</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.02962451016955</v>
+        <v>49.62895392481384</v>
       </c>
       <c r="C6" t="n">
-        <v>50.0472591156189</v>
+        <v>114384662.623284</v>
       </c>
       <c r="D6" t="n">
-        <v>41.37646466153178</v>
+        <v>25.62890185650456</v>
       </c>
       <c r="E6" t="n">
-        <v>24.30424047984752</v>
+        <v>35187102.32529397</v>
       </c>
       <c r="F6" t="n">
-        <v>380.9520231500121</v>
+        <v>9135213.056796748</v>
       </c>
       <c r="G6" t="n">
-        <v>200.0102884352038</v>
+        <v>197.8050003598578</v>
       </c>
       <c r="H6" t="n">
-        <v>123.2866500587306</v>
+        <v>26451208.51137181</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02403043863736809</v>
+        <v>0.02587261102763678</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02183823539202088</v>
+        <v>0.02360576665008249</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1800353800257194</v>
+        <v>0.08420191100778311</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07453887714008453</v>
+        <v>0.07373976771137641</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8629526228180653</v>
+        <v>0.8093860611279662</v>
       </c>
       <c r="G7" t="n">
-        <v>1.647549464008645</v>
+        <v>1.58132869903683</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4684908363369839</v>
+        <v>0.4330224694269458</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-37.94636995622662</v>
+        <v>-47.63635653203745</v>
       </c>
       <c r="C8" t="n">
-        <v>-15.1954751659661</v>
+        <v>-24.98821909615634</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.14340239812598</v>
+        <v>-46.77470082332907</v>
       </c>
       <c r="E8" t="n">
-        <v>-38.98437991270387</v>
+        <v>-49.13097730648582</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.20545430115007</v>
+        <v>-80.00414909858473</v>
       </c>
       <c r="G8" t="n">
-        <v>-84.89666342141793</v>
+        <v>-95.44642208404373</v>
       </c>
       <c r="H8" t="n">
-        <v>-46.3952908592651</v>
+        <v>-57.33013749010618</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-36.56579791487308</v>
+        <v>-47.24190737736502</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.65315888136972</v>
+        <v>-25.40470015770023</v>
       </c>
       <c r="D9" t="n">
-        <v>-33.60108611352959</v>
+        <v>-47.19118188487296</v>
       </c>
       <c r="E9" t="n">
-        <v>-40.44206362810749</v>
+        <v>-49.54745836802971</v>
       </c>
       <c r="F9" t="n">
-        <v>-65.81110775263407</v>
+        <v>-79.03433579900873</v>
       </c>
       <c r="G9" t="n">
-        <v>-80.94201791918717</v>
+        <v>-94.31652336912066</v>
       </c>
       <c r="H9" t="n">
-        <v>-45.66920536828351</v>
+        <v>-57.12268449268288</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8598010413547705</v>
+        <v>0.8598086811380938</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8264294873892869</v>
+        <v>0.8266098183452423</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3228055113827804</v>
+        <v>0.3188194320530449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5439466012754477</v>
+        <v>0.5602060714643389</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3779649692266959</v>
+        <v>0.3048309089290936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4821921719469879</v>
+        <v>0.39710301573954</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5688566304293282</v>
+        <v>0.5445629879448922</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05523592590894563</v>
+        <v>0.05521512233269882</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1298277859773135</v>
+        <v>0.1297806971839785</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02064810740359931</v>
+        <v>0.02068858334125212</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01489188822970997</v>
+        <v>0.01459869948911055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01235315837486147</v>
+        <v>0.01601052436603365</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007907937851526083</v>
+        <v>0.009150313864701994</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04014413395765933</v>
+        <v>0.04090732342962928</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005994238833761062</v>
+        <v>0.005993912193061873</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02439650111203678</v>
+        <v>0.02437115417832035</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005167476899857656</v>
+        <v>0.0005197893527877573</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002686664086259708</v>
+        <v>0.0002590876822133867</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004220465407550112</v>
+        <v>0.0004716674786619268</v>
       </c>
       <c r="G4" t="n">
-        <v>9.371248059143744e-05</v>
+        <v>0.0001091118536167829</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005281985510959338</v>
+        <v>0.005287453789777013</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07742246982472893</v>
+        <v>0.07742036032635002</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1561937934491534</v>
+        <v>0.1561126329875976</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02273208503384073</v>
+        <v>0.02279888928846661</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0163910465994692</v>
+        <v>0.01609620086273114</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02054377133719637</v>
+        <v>0.02171790686649906</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009680520677703109</v>
+        <v>0.0104456619520633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05049394782034861</v>
+        <v>0.05076527538061795</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.23185986207807</v>
+        <v>33.21179394802869</v>
       </c>
       <c r="C6" t="n">
-        <v>45.23279648528143</v>
+        <v>82772193.72179256</v>
       </c>
       <c r="D6" t="n">
-        <v>36.31285504420452</v>
+        <v>36.34323508561203</v>
       </c>
       <c r="E6" t="n">
-        <v>43.80261827655498</v>
+        <v>69720770.16341294</v>
       </c>
       <c r="F6" t="n">
-        <v>241.9661335260649</v>
+        <v>2234684.868962158</v>
       </c>
       <c r="G6" t="n">
-        <v>87.48461557505826</v>
+        <v>124.6548364110461</v>
       </c>
       <c r="H6" t="n">
-        <v>81.33847979487369</v>
+        <v>25787973.82733886</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04625565477720159</v>
+        <v>0.04775313419371516</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06914870456163968</v>
+        <v>0.07057686242125157</v>
       </c>
       <c r="D7" t="n">
-        <v>0.203520069968156</v>
+        <v>0.206218022931038</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1370040861034039</v>
+        <v>0.1336195399382477</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1869059418105198</v>
+        <v>0.2103808945563353</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1554079471523176</v>
+        <v>0.1824454735756698</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1330404007288731</v>
+        <v>0.1418323212693763</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-40.05260818868243</v>
+        <v>-40.05309863400412</v>
       </c>
       <c r="C8" t="n">
-        <v>-16.27989332407796</v>
+        <v>-16.28613031107631</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.40773497812001</v>
+        <v>-39.37252151551809</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.33224038745274</v>
+        <v>-43.55006407315503</v>
       </c>
       <c r="F8" t="n">
-        <v>-87.24473956632021</v>
+        <v>-85.91083578014168</v>
       </c>
       <c r="G8" t="n">
-        <v>-114.5786293431541</v>
+        <v>-112.600781285056</v>
       </c>
       <c r="H8" t="n">
-        <v>-56.81597429796792</v>
+        <v>-56.29557193315853</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-39.46093445667378</v>
+        <v>-39.46142490199546</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.9046149163938</v>
+        <v>-16.91085190339214</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.03245657043585</v>
+        <v>-39.99724310783393</v>
       </c>
       <c r="E9" t="n">
-        <v>-43.95696197976858</v>
+        <v>-44.17478566547087</v>
       </c>
       <c r="F9" t="n">
-        <v>-85.7900196169562</v>
+        <v>-84.45611583077768</v>
       </c>
       <c r="G9" t="n">
-        <v>-112.8837812707695</v>
+        <v>-110.9059332126714</v>
       </c>
       <c r="H9" t="n">
-        <v>-56.50479480183296</v>
+        <v>-55.98439243702359</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4956584956651561</v>
+        <v>0.4954540784458054</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4465422460389288</v>
+        <v>0.4466827485425068</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2556606856119352</v>
+        <v>-0.2547069820064072</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.03133615224063</v>
+        <v>-1.030652762882765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6120746889689053</v>
+        <v>0.6125659857441943</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.880284362880962</v>
+        <v>-1.886605976126188</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2688342950100895</v>
+        <v>-0.2695438180471423</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08228677411251198</v>
+        <v>0.08241504847748764</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2080917606389486</v>
+        <v>0.2080309142080452</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02440999665061739</v>
+        <v>0.02440424442084847</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03158802472897491</v>
+        <v>0.03158053396128593</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0141545821709507</v>
+        <v>0.01413845356240746</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01964857561168319</v>
+        <v>0.01967020954366189</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06336328565228114</v>
+        <v>0.0633732340289561</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02156323741613086</v>
+        <v>0.02157197732152219</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07779220391115706</v>
+        <v>0.07777245468053869</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009581586525029658</v>
+        <v>0.0009574309086371023</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001196683963458876</v>
+        <v>0.001196280993389941</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002632046870229287</v>
+        <v>0.0002628713315927126</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000521271749539231</v>
+        <v>0.0005224158304635719</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01704912672996865</v>
+        <v>0.01704723851102403</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1468442624556059</v>
+        <v>0.1468740185380729</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2789125381031786</v>
+        <v>0.2788771318708988</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03095413788983576</v>
+        <v>0.03094238046170822</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03459312017524404</v>
+        <v>0.03458729525981963</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01622358428408867</v>
+        <v>0.01621330723796698</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02283137642673413</v>
+        <v>0.0228564177084593</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08839316988911451</v>
+        <v>0.08839175851282095</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.11232068680539</v>
+        <v>37.50622689114977</v>
       </c>
       <c r="C6" t="n">
-        <v>52.61839931689375</v>
+        <v>147506788.1318934</v>
       </c>
       <c r="D6" t="n">
-        <v>37.32888307127421</v>
+        <v>37.33514119838302</v>
       </c>
       <c r="E6" t="n">
-        <v>61.98757982354242</v>
+        <v>135032168.8904556</v>
       </c>
       <c r="F6" t="n">
-        <v>673.1618134103027</v>
+        <v>4305897.554513209</v>
       </c>
       <c r="G6" t="n">
-        <v>220.21239874734</v>
+        <v>220.4606098493872</v>
       </c>
       <c r="H6" t="n">
-        <v>180.4035658426931</v>
+        <v>47807524.97980669</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1663967174917448</v>
+        <v>0.171464160591324</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2204918689261313</v>
+        <v>0.2254358937136251</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7547378334806655</v>
+        <v>0.7641645924759364</v>
       </c>
       <c r="E7" t="n">
-        <v>1.220477048893221</v>
+        <v>1.230066451120405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1165618365902445</v>
+        <v>0.1214142142088566</v>
       </c>
       <c r="G7" t="n">
-        <v>1.728900398177932</v>
+        <v>1.742694967838362</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7012609505933232</v>
+        <v>0.7092067133247516</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-14.53088847189727</v>
+        <v>-14.52724137520021</v>
       </c>
       <c r="C8" t="n">
-        <v>4.677715642302232</v>
+        <v>4.676192219367749</v>
       </c>
       <c r="D8" t="n">
-        <v>-21.70298311398543</v>
+        <v>-21.70754198556609</v>
       </c>
       <c r="E8" t="n">
-        <v>-20.36920546666367</v>
+        <v>-20.37122624045691</v>
       </c>
       <c r="F8" t="n">
-        <v>-78.91094261000553</v>
+        <v>-78.92615054785652</v>
       </c>
       <c r="G8" t="n">
-        <v>-78.27010777983128</v>
+        <v>-78.24160680260643</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.85106863334682</v>
+        <v>-34.84959578871974</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-12.55864269853507</v>
+        <v>-12.55499560183802</v>
       </c>
       <c r="C9" t="n">
-        <v>2.595310334582781</v>
+        <v>2.593786911648298</v>
       </c>
       <c r="D9" t="n">
-        <v>-23.78538842170488</v>
+        <v>-23.78994729328554</v>
       </c>
       <c r="E9" t="n">
-        <v>-22.45161077438312</v>
+        <v>-22.45363154817636</v>
       </c>
       <c r="F9" t="n">
-        <v>-74.06187611212553</v>
+        <v>-74.07708404997652</v>
       </c>
       <c r="G9" t="n">
-        <v>-72.62061420521592</v>
+        <v>-72.59211322799106</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.81380364623029</v>
+        <v>-33.8123308016032</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3745116173092011</v>
+        <v>0.374511628918107</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05307034147357292</v>
+        <v>-0.05307034858632154</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.593142869552335</v>
+        <v>-3.593142729548513</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.212836676857659</v>
+        <v>-1.212836882486148</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.674096398956276</v>
+        <v>-2.674096410389298</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.96119841787935</v>
+        <v>-8.961198561043178</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.686638847901666</v>
+        <v>-2.686638883855892</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1236036039573822</v>
+        <v>0.1236036012589695</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2751620559091585</v>
+        <v>0.2751620537663014</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05196273179777992</v>
+        <v>0.05196273027124796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03082861211897715</v>
+        <v>0.03082860870973105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04357326612802866</v>
+        <v>0.0435732650577683</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03644501053908024</v>
+        <v>0.03644501120146878</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09359588007506776</v>
+        <v>0.09359587837758115</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02674290016004456</v>
+        <v>0.02674289966370312</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1480161080956977</v>
+        <v>0.1480161078388868</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003504895576545906</v>
+        <v>0.003504895469713004</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001303608052280411</v>
+        <v>0.001303607762182065</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002492849435910722</v>
+        <v>0.002492849311783335</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001802770377019884</v>
+        <v>0.001802770402929569</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03064385528291654</v>
+        <v>0.03064385507486632</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1635325660535068</v>
+        <v>0.1635325645359453</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3847286161643006</v>
+        <v>0.3847286158305447</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05920215854633939</v>
+        <v>0.05920215764406737</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0361055127685567</v>
+        <v>0.03610550875118734</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04992844315528697</v>
+        <v>0.0499284419122341</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04245904352455298</v>
+        <v>0.04245904382966683</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1226593900354239</v>
+        <v>0.1226593887506076</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.25784289138527</v>
+        <v>61.25783840216857</v>
       </c>
       <c r="C6" t="n">
-        <v>78.16372995605754</v>
+        <v>55407472.24138872</v>
       </c>
       <c r="D6" t="n">
-        <v>101.892135361467</v>
+        <v>101.8921315208959</v>
       </c>
       <c r="E6" t="n">
-        <v>109.3282339334233</v>
+        <v>144663186.6941223</v>
       </c>
       <c r="F6" t="n">
-        <v>2533.340362719523</v>
+        <v>53590819.8353707</v>
       </c>
       <c r="G6" t="n">
-        <v>660.6882242250205</v>
+        <v>660.6882307972</v>
       </c>
       <c r="H6" t="n">
-        <v>590.7784215144794</v>
+        <v>42277050.43484706</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2063665449192709</v>
+        <v>0.2068665410891601</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8390647562181207</v>
+        <v>0.8400647601262345</v>
       </c>
       <c r="D7" t="n">
-        <v>2.760792575538566</v>
+        <v>2.761792491386706</v>
       </c>
       <c r="E7" t="n">
-        <v>1.329527057387788</v>
+        <v>1.330527180358744</v>
       </c>
       <c r="F7" t="n">
-        <v>2.207947828584041</v>
+        <v>2.208947835270076</v>
       </c>
       <c r="G7" t="n">
-        <v>5.979242929255438</v>
+        <v>5.980243015190009</v>
       </c>
       <c r="H7" t="n">
-        <v>2.220490281983871</v>
+        <v>2.221406970570155</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.5933762990192</v>
+        <v>-30.59337646605692</v>
       </c>
       <c r="C8" t="n">
-        <v>-9.462605035936335</v>
+        <v>-9.462605046346455</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.92156730990587</v>
+        <v>-31.92156749279217</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.85571660438105</v>
+        <v>-37.85571793959087</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.93194645206646</v>
+        <v>-69.93194704958697</v>
       </c>
       <c r="G8" t="n">
-        <v>-80.13959908613695</v>
+        <v>-80.13959889929902</v>
       </c>
       <c r="H8" t="n">
-        <v>-43.31746846457431</v>
+        <v>-43.31746881561207</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-30.39615172168298</v>
+        <v>-30.3961518887207</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.67084556670828</v>
+        <v>-9.670845577118401</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.12980784067781</v>
+        <v>-32.12980802356412</v>
       </c>
       <c r="E9" t="n">
-        <v>-38.063957135153</v>
+        <v>-38.06395847036281</v>
       </c>
       <c r="F9" t="n">
-        <v>-69.44703980227845</v>
+        <v>-69.44704039979896</v>
       </c>
       <c r="G9" t="n">
-        <v>-79.57464972867541</v>
+        <v>-79.57464954183747</v>
       </c>
       <c r="H9" t="n">
-        <v>-43.21374196586265</v>
+        <v>-43.21374231690041</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global_ind/metrics_summary.xlsx
+++ b/results/cross_validation/global_ind/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7824659118456879</v>
+        <v>-0.7853519169707242</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5094093324748276</v>
+        <v>-0.6799816636859224</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1585806370570255</v>
+        <v>-0.2945111087674936</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.426337250544142</v>
+        <v>-0.1539621853081679</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.10425060541587</v>
+        <v>-5.238471411462817</v>
       </c>
       <c r="G2" t="n">
-        <v>-26.85398314701063</v>
+        <v>-38.19947240584995</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.875212732617858</v>
+        <v>-7.558625115340846</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08879918632510617</v>
+        <v>0.1871288937236316</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1934150974688515</v>
+        <v>0.3269989356012205</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02048626366742287</v>
+        <v>0.02713973240721687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04007148314460696</v>
+        <v>0.02297097043403405</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09075855340228256</v>
+        <v>0.05780836641271536</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06381530523248177</v>
+        <v>0.08167996289243065</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08289098154012532</v>
+        <v>0.1172878102452082</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009300720144298657</v>
+        <v>0.07633313325612083</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06895581216073432</v>
+        <v>0.2361327042816217</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008840796520419748</v>
+        <v>0.0009878042960485855</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002018494842983918</v>
+        <v>0.0006798126642274524</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009569637670777722</v>
+        <v>0.004232760453271744</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005040993421967398</v>
+        <v>0.007094291739157945</v>
       </c>
       <c r="H4" t="n">
-        <v>0.015961622982134</v>
+        <v>0.05424341778174138</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09644024131190598</v>
+        <v>0.27628451504947</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2625943871462875</v>
+        <v>0.4859348765849408</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02973347695850546</v>
+        <v>0.03142935405076893</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04492766233606994</v>
+        <v>0.02607321737391556</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09782452489420904</v>
+        <v>0.06505966840733009</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07099995367581163</v>
+        <v>0.08422761862452212</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1004200410537983</v>
+        <v>0.1615015416818246</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.73390094308097</v>
+        <v>61.06553800226001</v>
       </c>
       <c r="C6" t="n">
-        <v>199729669.8538492</v>
+        <v>77.4088394915687</v>
       </c>
       <c r="D6" t="n">
-        <v>40.76865592961261</v>
+        <v>47.61519562453687</v>
       </c>
       <c r="E6" t="n">
-        <v>195604688.7036716</v>
+        <v>48.82327596337516</v>
       </c>
       <c r="F6" t="n">
-        <v>104913387.589027</v>
+        <v>4382.771055851253</v>
       </c>
       <c r="G6" t="n">
-        <v>981.4755299282332</v>
+        <v>1189.639388290864</v>
       </c>
       <c r="H6" t="n">
-        <v>83374805.52077244</v>
+        <v>967.8872155373097</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07227073054730269</v>
+        <v>1.179077536741004</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1959462687700658</v>
+        <v>1.339574784205824</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6973860937470742</v>
+        <v>0.7790895912749642</v>
       </c>
       <c r="E7" t="n">
-        <v>2.059628243106662</v>
+        <v>0.6943290489148193</v>
       </c>
       <c r="F7" t="n">
-        <v>8.476947855988609</v>
+        <v>3.750008711512271</v>
       </c>
       <c r="G7" t="n">
-        <v>16.72044727899714</v>
+        <v>23.5306154519448</v>
       </c>
       <c r="H7" t="n">
-        <v>4.703771078526142</v>
+        <v>5.212115854098947</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-40.09897102255025</v>
+        <v>-21.15383366678466</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.04573629799032</v>
+        <v>-6.660167954280425</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.18578037159529</v>
+        <v>-39.52015576455705</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.23241903529991</v>
+        <v>-41.76215974919598</v>
       </c>
       <c r="F8" t="n">
-        <v>-53.78991922212141</v>
+        <v>-63.57881091210268</v>
       </c>
       <c r="G8" t="n">
-        <v>-66.77197741425418</v>
+        <v>-62.33004238310949</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.6874672273019</v>
+        <v>-39.16752840500505</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-39.90174644521403</v>
+        <v>-20.95660908944845</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.25397682876226</v>
+        <v>-6.86840848505237</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.39402090236724</v>
+        <v>-39.72839629532899</v>
       </c>
       <c r="E9" t="n">
-        <v>-35.44065956607186</v>
+        <v>-41.97040027996793</v>
       </c>
       <c r="F9" t="n">
-        <v>-53.30501257233341</v>
+        <v>-63.09390426231468</v>
       </c>
       <c r="G9" t="n">
-        <v>-66.20702805679264</v>
+        <v>-61.76509302564795</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.58374072859024</v>
+        <v>-39.0638019062934</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9261987934798601</v>
+        <v>0.01285879431279791</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9262391443112855</v>
+        <v>-0.356632800408567</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7246641793956985</v>
+        <v>-1.510128558045912</v>
       </c>
       <c r="E2" t="n">
-        <v>0.707502210414482</v>
+        <v>-3.594013481564944</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3502468801472898</v>
+        <v>-0.5608444930503984</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.750042046232926</v>
+        <v>-7.059063832619204</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1973859002035184</v>
+        <v>-2.177970728562705</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04704892059786654</v>
+        <v>0.1489265333015127</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08990934521939349</v>
+        <v>0.2825895147471342</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01319883098359961</v>
+        <v>0.0363420359291716</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01054873012113107</v>
+        <v>0.04540283780780691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02219347153061002</v>
+        <v>0.0307600838231013</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01807381062831841</v>
+        <v>0.03415984184253452</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03349551818015319</v>
+        <v>0.09636347457521023</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003155387617542021</v>
+        <v>0.0422054500740565</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01036758349958839</v>
+        <v>0.1906838501884471</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000210100867120362</v>
+        <v>0.001915407103483835</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001723138257241899</v>
+        <v>0.002706387249219502</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000916133282837866</v>
+        <v>0.001059022380346463</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004977005906848822</v>
+        <v>0.001458523456161739</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002553203280582951</v>
+        <v>0.04000477340861918</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05617283700813072</v>
+        <v>0.2054396506861723</v>
       </c>
       <c r="C5" t="n">
-        <v>0.101821331260146</v>
+        <v>0.436673619753297</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01449485657467372</v>
+        <v>0.04376536419914537</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01312683608963675</v>
+        <v>0.05202294925529984</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0302676937152117</v>
+        <v>0.0325426240544069</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02230920416968929</v>
+        <v>0.03819062000232176</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03969879313624803</v>
+        <v>0.1347724713251072</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.07413259799511</v>
+        <v>76.07009124589355</v>
       </c>
       <c r="C6" t="n">
-        <v>119061148.570011</v>
+        <v>49.87826430339936</v>
       </c>
       <c r="D6" t="n">
-        <v>26.18933101133058</v>
+        <v>101.7318200409694</v>
       </c>
       <c r="E6" t="n">
-        <v>38882905.13824324</v>
+        <v>124.4636468698693</v>
       </c>
       <c r="F6" t="n">
-        <v>12017048.46166951</v>
+        <v>1892.404563150786</v>
       </c>
       <c r="G6" t="n">
-        <v>216.1059097492752</v>
+        <v>578.3211959018358</v>
       </c>
       <c r="H6" t="n">
-        <v>28326898.92321618</v>
+        <v>470.4782635854589</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02584913328832138</v>
+        <v>0.3281861767580002</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03088556515632622</v>
+        <v>1.085937070508966</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08424781678827471</v>
+        <v>1.513758704772425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08936995655366234</v>
+        <v>2.765197031087874</v>
       </c>
       <c r="F7" t="n">
-        <v>0.814430714684347</v>
+        <v>0.9429893271627242</v>
       </c>
       <c r="G7" t="n">
-        <v>1.653722008566715</v>
+        <v>4.842480232410149</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4497508658396077</v>
+        <v>1.913091423783357</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-45.82779539124397</v>
+        <v>-18.48685325844336</v>
       </c>
       <c r="C8" t="n">
-        <v>-21.41442787140553</v>
+        <v>0.05716925820799368</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.80753693765547</v>
+        <v>-27.54695055360345</v>
       </c>
       <c r="E8" t="n">
-        <v>-45.99715905293696</v>
+        <v>-25.47284391111524</v>
       </c>
       <c r="F8" t="n">
-        <v>-77.94418438312198</v>
+        <v>-72.20490894937448</v>
       </c>
       <c r="G8" t="n">
-        <v>-92.87165450852677</v>
+        <v>-74.89429892318196</v>
       </c>
       <c r="H8" t="n">
-        <v>-54.81045969081512</v>
+        <v>-36.42478105625175</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-45.23612165923532</v>
+        <v>-17.50073037176227</v>
       </c>
       <c r="C9" t="n">
-        <v>-22.03914946372137</v>
+        <v>-0.984033395651732</v>
       </c>
       <c r="D9" t="n">
-        <v>-45.43225852997131</v>
+        <v>-28.58815320746318</v>
       </c>
       <c r="E9" t="n">
-        <v>-46.62188064525279</v>
+        <v>-26.51404656497497</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.48946443375797</v>
+        <v>-69.78037570043449</v>
       </c>
       <c r="G9" t="n">
-        <v>-91.17680643614216</v>
+        <v>-72.06955213587428</v>
       </c>
       <c r="H9" t="n">
-        <v>-54.49928019468015</v>
+        <v>-35.90614856269349</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.93205460833799</v>
+        <v>0.02213016696005154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9352803955330585</v>
+        <v>-0.349849790921938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6114646215201138</v>
+        <v>-1.499910377776507</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6682839361321029</v>
+        <v>-3.47630860438323</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1681270518406408</v>
+        <v>-0.5526222052997958</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.013013264634492</v>
+        <v>-7.010570016091044</v>
       </c>
       <c r="H2" t="n">
-        <v>0.327657207508022</v>
+        <v>-2.14452180458541</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04270291016760745</v>
+        <v>0.1487277167945368</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08321359295909064</v>
+        <v>0.2818880180758711</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01671975596259745</v>
+        <v>0.03626031443574911</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01006887919111687</v>
+        <v>0.04461788763263513</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01995266357936643</v>
+        <v>0.03066202315050746</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01445023460367513</v>
+        <v>0.03397173759555959</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03118467274390899</v>
+        <v>0.09602128294747654</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002905020901803853</v>
+        <v>0.04180905039675883</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009096774937143394</v>
+        <v>0.1897304526556838</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002964802027807304</v>
+        <v>0.001907609903212973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001954177640119749</v>
+        <v>0.002637045924895173</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007925662236358935</v>
+        <v>0.001053443613989976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003643136628538049</v>
+        <v>0.001449747080846427</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002275095615371609</v>
+        <v>0.03976455826256453</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05389824581379113</v>
+        <v>0.2044726152734366</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0953770147212807</v>
+        <v>0.4355805926067917</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01721860048844651</v>
+        <v>0.04367619378120045</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01397919039186372</v>
+        <v>0.05135217546409473</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02815255270194682</v>
+        <v>0.03245679611406486</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01908700245857911</v>
+        <v>0.03807554439330352</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03795210109598467</v>
+        <v>0.1342689862721486</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.14342649723626</v>
+        <v>76.64900417143554</v>
       </c>
       <c r="C6" t="n">
-        <v>114598081.5985517</v>
+        <v>49.71568531185098</v>
       </c>
       <c r="D6" t="n">
-        <v>33.07957751816367</v>
+        <v>101.5234687223257</v>
       </c>
       <c r="E6" t="n">
-        <v>19793230.46929319</v>
+        <v>122.0290238577726</v>
       </c>
       <c r="F6" t="n">
-        <v>8102515.912503227</v>
+        <v>1863.418194401926</v>
       </c>
       <c r="G6" t="n">
-        <v>155.0776223519975</v>
+        <v>576.2883589289536</v>
       </c>
       <c r="H6" t="n">
-        <v>23749010.04682909</v>
+        <v>464.9372892323775</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02441713212986569</v>
+        <v>0.3251272851897158</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02778362379608282</v>
+        <v>1.08053250827112</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1187681496859124</v>
+        <v>1.507616880530402</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1016516115951775</v>
+        <v>2.694477026924792</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7059858238174749</v>
+        <v>0.9380481442394636</v>
       </c>
       <c r="G7" t="n">
-        <v>1.212317997908691</v>
+        <v>4.813371655567813</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3651540564888673</v>
+        <v>1.893195583453884</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.5718322423185</v>
+        <v>-18.57178201597015</v>
       </c>
       <c r="C8" t="n">
-        <v>-20.19901198471876</v>
+        <v>0.02709469407835741</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.74118066879929</v>
+        <v>-27.5714250806128</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.24222546884742</v>
+        <v>-25.62857573707144</v>
       </c>
       <c r="F8" t="n">
-        <v>-77.68281391307833</v>
+        <v>-72.26829018446995</v>
       </c>
       <c r="G8" t="n">
-        <v>-94.9274395532578</v>
+        <v>-74.9727601419616</v>
       </c>
       <c r="H8" t="n">
-        <v>-53.56075063850335</v>
+        <v>-36.49762307766793</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-43.78293393297362</v>
+        <v>-17.58565912928905</v>
       </c>
       <c r="C9" t="n">
-        <v>-21.03197410780654</v>
+        <v>-1.014107959781368</v>
       </c>
       <c r="D9" t="n">
-        <v>-41.57414279188707</v>
+        <v>-28.61262773447253</v>
       </c>
       <c r="E9" t="n">
-        <v>-44.0751875919352</v>
+        <v>-26.66977839093117</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.74318731392633</v>
+        <v>-69.84375693552994</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.66764212341165</v>
+        <v>-72.14801335465391</v>
       </c>
       <c r="H9" t="n">
-        <v>-53.14584464365674</v>
+        <v>-35.97899058410966</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9323208969051008</v>
+        <v>0.02135013319848666</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9337066933935512</v>
+        <v>-0.3603544904920113</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6129539214285118</v>
+        <v>-2.392790204425771</v>
       </c>
       <c r="E2" t="n">
-        <v>0.66095927857297</v>
+        <v>-5.794064849065286</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1821857810364818</v>
+        <v>-0.2784097345452978</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.059799789741832</v>
+        <v>-7.244861261157043</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3163258699203034</v>
+        <v>-2.674855067747821</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04253358898377054</v>
+        <v>0.1502458846592076</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08493333960219897</v>
+        <v>0.2835296226576694</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01668361393389615</v>
+        <v>0.04331432633376062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0102432700111141</v>
+        <v>0.05783167808823388</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02001576446133205</v>
+        <v>0.02738446211302237</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01473915403606692</v>
+        <v>0.03620619751230661</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03152478850472979</v>
+        <v>0.09975202856070009</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002893635672659596</v>
+        <v>0.04184240092026058</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00931796933873329</v>
+        <v>0.1912069587216519</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002953437607388997</v>
+        <v>0.002588940888050178</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001997328043680826</v>
+        <v>0.004002463325731706</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008021049753412923</v>
+        <v>0.0008673923162520557</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003727810538211223</v>
+        <v>0.00149214893838216</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002313594600943714</v>
+        <v>0.04033338418505476</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05379252431945908</v>
+        <v>0.2045541515595823</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09652962933075673</v>
+        <v>0.4372721792221086</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01718556838568046</v>
+        <v>0.05088163605909481</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01413268567428295</v>
+        <v>0.06326502450589666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02832145786045083</v>
+        <v>0.02945152485444609</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01930753878206962</v>
+        <v>0.0386283437178215</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03821156739211661</v>
+        <v>0.137342143319825</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.0814627972389</v>
+        <v>81.45559495045845</v>
       </c>
       <c r="C6" t="n">
-        <v>115786675.8189136</v>
+        <v>50.55591308919636</v>
       </c>
       <c r="D6" t="n">
-        <v>32.898638136607</v>
+        <v>118.1758434350344</v>
       </c>
       <c r="E6" t="n">
-        <v>20557370.2816632</v>
+        <v>162.8892959447662</v>
       </c>
       <c r="F6" t="n">
-        <v>8794327.763580078</v>
+        <v>1754.330619080523</v>
       </c>
       <c r="G6" t="n">
-        <v>159.8589765614173</v>
+        <v>554.3216218169428</v>
       </c>
       <c r="H6" t="n">
-        <v>24189768.45053907</v>
+        <v>453.6214813861536</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02432927589933149</v>
+        <v>0.3253846406846365</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02841057051904795</v>
+        <v>1.08890243650552</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1183205642039637</v>
+        <v>2.044298639898733</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1038520293911667</v>
+        <v>4.087042358095196</v>
       </c>
       <c r="F7" t="n">
-        <v>0.714434415587367</v>
+        <v>0.7732601899699317</v>
       </c>
       <c r="G7" t="n">
-        <v>1.240401767320449</v>
+        <v>4.954005765207961</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3716247704868876</v>
+        <v>2.21214900506033</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.60717394350542</v>
+        <v>-18.56460569750363</v>
       </c>
       <c r="C8" t="n">
-        <v>-20.05486333680733</v>
+        <v>0.07360669576361012</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.76422353644959</v>
+        <v>-25.73903846261281</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.11118037674167</v>
+        <v>-23.12507165585409</v>
       </c>
       <c r="F8" t="n">
-        <v>-77.53925280059937</v>
+        <v>-74.60023021963659</v>
       </c>
       <c r="G8" t="n">
-        <v>-94.62875087061423</v>
+        <v>-74.59799344788733</v>
       </c>
       <c r="H8" t="n">
-        <v>-53.45090747745294</v>
+        <v>-36.09222213128847</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-43.81827563416054</v>
+        <v>-17.57848281082253</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.88782545989511</v>
+        <v>-0.9675959580961155</v>
       </c>
       <c r="D9" t="n">
-        <v>-41.59718565953737</v>
+        <v>-26.78024111647254</v>
       </c>
       <c r="E9" t="n">
-        <v>-43.94414249982945</v>
+        <v>-24.16627430971382</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.59962620144736</v>
+        <v>-72.17569697069658</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.36895344076808</v>
+        <v>-71.77324666057964</v>
       </c>
       <c r="H9" t="n">
-        <v>-53.03600148260632</v>
+        <v>-35.5735896377302</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3413256614529303</v>
+        <v>-1.029086591425855</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4043258201244568</v>
+        <v>-0.8988629672901018</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.716872459481684</v>
+        <v>-0.280788446601586</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.63000463767415</v>
+        <v>-0.1622430458527879</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.522317341546145</v>
+        <v>-6.395389160165701</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.725451833897227</v>
+        <v>-12.37324547977593</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.64149913183697</v>
+        <v>-3.523269281851994</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1226779301719572</v>
+        <v>0.210668615886091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2082971632956492</v>
+        <v>0.3562864381918411</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05045185157370972</v>
+        <v>0.02465934941190585</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03011463193908429</v>
+        <v>0.0222086699571266</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03863281183736978</v>
+        <v>0.06499967541728786</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02680369460643026</v>
+        <v>0.03045885755376665</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07949634723736676</v>
+        <v>0.1182136010696698</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02816177336175296</v>
+        <v>0.08675406551461282</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0837260053553502</v>
+        <v>0.2668979413398306</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003599310077628795</v>
+        <v>0.0009773329261631521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001549366104380409</v>
+        <v>0.0006846910163438441</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001711375082916304</v>
+        <v>0.005017721282842892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008552088038818331</v>
+        <v>0.002420280149452909</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01993383979765175</v>
+        <v>0.0604586720382077</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1678146994805668</v>
+        <v>0.2945404310355589</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2893544631681879</v>
+        <v>0.5166216617020918</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05999425037142139</v>
+        <v>0.03126232438836166</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0393619880643802</v>
+        <v>0.02616660116147766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04136876941505879</v>
+        <v>0.0708358756764035</v>
       </c>
       <c r="G5" t="n">
-        <v>0.029243953287506</v>
+        <v>0.04919634284632252</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1045230206311868</v>
+        <v>0.1647705394683693</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.85794523621493</v>
+        <v>82.69874812079547</v>
       </c>
       <c r="C6" t="n">
-        <v>93878892.53670304</v>
+        <v>98.71527347485141</v>
       </c>
       <c r="D6" t="n">
-        <v>111.0482101422981</v>
+        <v>38.19773350253099</v>
       </c>
       <c r="E6" t="n">
-        <v>119890323.1232264</v>
+        <v>51.6121177336514</v>
       </c>
       <c r="F6" t="n">
-        <v>47315072.79105236</v>
+        <v>4724.518032301897</v>
       </c>
       <c r="G6" t="n">
-        <v>408.8521821716963</v>
+        <v>127.7123349666179</v>
       </c>
       <c r="H6" t="n">
-        <v>43514145.03488656</v>
+        <v>853.9090400167239</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.217815542917348</v>
+        <v>1.340907646575971</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2378104577114081</v>
+        <v>1.514974898249824</v>
       </c>
       <c r="D7" t="n">
-        <v>2.836162509797691</v>
+        <v>0.7718413340575802</v>
       </c>
       <c r="E7" t="n">
-        <v>1.581171895150623</v>
+        <v>0.7003043949345542</v>
       </c>
       <c r="F7" t="n">
-        <v>1.51678633004377</v>
+        <v>4.446258305895401</v>
       </c>
       <c r="G7" t="n">
-        <v>2.837468392663771</v>
+        <v>8.029335680074793</v>
       </c>
       <c r="H7" t="n">
-        <v>1.537869188047435</v>
+        <v>2.800603709964687</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.12810797662934</v>
+        <v>-18.00210196878371</v>
       </c>
       <c r="C8" t="n">
-        <v>-12.88123391527929</v>
+        <v>-3.925333614967807</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.76207858193673</v>
+        <v>-37.58409920143608</v>
       </c>
       <c r="E8" t="n">
-        <v>-36.81945637969483</v>
+        <v>-39.71925735497644</v>
       </c>
       <c r="F8" t="n">
-        <v>-74.44549707472297</v>
+        <v>-59.53735251266497</v>
       </c>
       <c r="G8" t="n">
-        <v>-89.83414374909694</v>
+        <v>-74.31033575660055</v>
       </c>
       <c r="H8" t="n">
-        <v>-45.97841961289335</v>
+        <v>-38.8464134015716</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-29.93088339929312</v>
+        <v>-17.60765281411127</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.08947444605124</v>
+        <v>-4.341814676511697</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.97031911270867</v>
+        <v>-38.00058026297997</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.02769691046678</v>
+        <v>-40.13573841652033</v>
       </c>
       <c r="F9" t="n">
-        <v>-73.96059042493496</v>
+        <v>-58.56753921308897</v>
       </c>
       <c r="G9" t="n">
-        <v>-89.26919439163539</v>
+        <v>-73.18043704167748</v>
       </c>
       <c r="H9" t="n">
-        <v>-45.8746931141817</v>
+        <v>-38.63896040414829</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9246121543050505</v>
+        <v>-0.07754765751219406</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9432571508242535</v>
+        <v>-0.2602387229181446</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7231532222561292</v>
+        <v>-4.284764519011035</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7578669421834958</v>
+        <v>-6.218024089293901</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.34351644617807</v>
+        <v>-3.470294472399476</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.631103423007457</v>
+        <v>-24.7509146712048</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2290449333972337</v>
+        <v>-6.510297355389924</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04968435160334696</v>
+        <v>0.154488608791458</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07108350721120997</v>
+        <v>0.2728874968903159</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01243963804579516</v>
+        <v>0.0581453563659349</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009634098719231135</v>
+        <v>0.05971260037743614</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02157134488230331</v>
+        <v>0.04887995827486039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01733920489729134</v>
+        <v>0.0672002132550687</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03029202422652964</v>
+        <v>0.1102190389925123</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003223224741645607</v>
+        <v>0.04607079878697546</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007975588424797925</v>
+        <v>0.177135015289496</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002112538351740953</v>
+        <v>0.004032652219148978</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001426433806073592</v>
+        <v>0.004252222688987351</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009115667293743451</v>
+        <v>0.003033064417428333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004761751659679581</v>
+        <v>0.004660381633106529</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002156742046261215</v>
+        <v>0.03986402250585711</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05677345102814877</v>
+        <v>0.2146410929597952</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08930614998306625</v>
+        <v>0.4208741085995859</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01453457378714957</v>
+        <v>0.06350316700093767</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01194334042918308</v>
+        <v>0.06520906907008679</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03019216337684905</v>
+        <v>0.05507326408910528</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02182143821951152</v>
+        <v>0.06826698787193214</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03742851947065137</v>
+        <v>0.1479279482652405</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.62895392481384</v>
+        <v>86.6849932876617</v>
       </c>
       <c r="C6" t="n">
-        <v>114384662.623284</v>
+        <v>47.92680840201113</v>
       </c>
       <c r="D6" t="n">
-        <v>25.62890185650456</v>
+        <v>147.4913922114179</v>
       </c>
       <c r="E6" t="n">
-        <v>35187102.32529397</v>
+        <v>168.5975191169675</v>
       </c>
       <c r="F6" t="n">
-        <v>9135213.056796748</v>
+        <v>3634.43666514423</v>
       </c>
       <c r="G6" t="n">
-        <v>197.8050003598578</v>
+        <v>957.3900657260216</v>
       </c>
       <c r="H6" t="n">
-        <v>26451208.51137181</v>
+        <v>840.4212406480516</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02587261102763678</v>
+        <v>0.7140277128090821</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02360576665008249</v>
+        <v>1.007132255156181</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08420191100778311</v>
+        <v>3.17950442451343</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07373976771137641</v>
+        <v>4.339767565340924</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8093860611279662</v>
+        <v>2.689422973624086</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58132869903683</v>
+        <v>15.46007333700923</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4330224694269458</v>
+        <v>4.564988044742155</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-47.63635653203745</v>
+        <v>-21.6981836547161</v>
       </c>
       <c r="C8" t="n">
-        <v>-24.98821909615634</v>
+        <v>-4.385058233671721</v>
       </c>
       <c r="D8" t="n">
-        <v>-46.77470082332907</v>
+        <v>-27.07998600355974</v>
       </c>
       <c r="E8" t="n">
-        <v>-49.13097730648582</v>
+        <v>-26.76188068266635</v>
       </c>
       <c r="F8" t="n">
-        <v>-80.00414909858473</v>
+        <v>-63.57818173982952</v>
       </c>
       <c r="G8" t="n">
-        <v>-95.44642208404373</v>
+        <v>-63.7925532028584</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.33013749010618</v>
+        <v>-34.54930725288364</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.24190737736502</v>
+        <v>-21.10650992270745</v>
       </c>
       <c r="C9" t="n">
-        <v>-25.40470015770023</v>
+        <v>-5.009779825987556</v>
       </c>
       <c r="D9" t="n">
-        <v>-47.19118188487296</v>
+        <v>-27.70470759587558</v>
       </c>
       <c r="E9" t="n">
-        <v>-49.54745836802971</v>
+        <v>-27.38660227498219</v>
       </c>
       <c r="F9" t="n">
-        <v>-79.03433579900873</v>
+        <v>-62.12346179046551</v>
       </c>
       <c r="G9" t="n">
-        <v>-94.31652336912066</v>
+        <v>-62.09770513047379</v>
       </c>
       <c r="H9" t="n">
-        <v>-57.12268449268288</v>
+        <v>-34.23812775674867</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8598086811380938</v>
+        <v>0.07199016154160831</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8266098183452423</v>
+        <v>-0.1102121398269829</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3188194320530449</v>
+        <v>-43.69911423317989</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5602060714643389</v>
+        <v>-0.2659531178650831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3048309089290936</v>
+        <v>-0.6121669710555091</v>
       </c>
       <c r="G2" t="n">
-        <v>0.39710301573954</v>
+        <v>-3.059276790266954</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5445629879448922</v>
+        <v>-7.945788848442135</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05521512233269882</v>
+        <v>0.1507797174144304</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1297806971839785</v>
+        <v>0.2695324855241041</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02068858334125212</v>
+        <v>0.1822782044466678</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01459869948911055</v>
+        <v>0.02490448091297283</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01601052436603365</v>
+        <v>0.02331038743724577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009150313864701994</v>
+        <v>0.02312835281218326</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04090732342962928</v>
+        <v>0.1123222714246007</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005993912193061873</v>
+        <v>0.03967727482110585</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02437115417832035</v>
+        <v>0.156047771574156</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005197893527877573</v>
+        <v>0.0341086119462819</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002590876822133867</v>
+        <v>0.0007457878367245494</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004716674786619268</v>
+        <v>0.001093844332862713</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001091118536167829</v>
+        <v>0.0007346449335335644</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005287453789777013</v>
+        <v>0.03873465590744409</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07742036032635002</v>
+        <v>0.1991915530867357</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1561126329875976</v>
+        <v>0.395028823725758</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02279888928846661</v>
+        <v>0.1846851698060294</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01609620086273114</v>
+        <v>0.0273091163666009</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02171790686649906</v>
+        <v>0.03307331753638744</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0104456619520633</v>
+        <v>0.0271043342204446</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05076527538061795</v>
+        <v>0.1443987191236593</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.21179394802869</v>
+        <v>98.27451598591109</v>
       </c>
       <c r="C6" t="n">
-        <v>82772193.72179256</v>
+        <v>54.620481697447</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34323508561203</v>
+        <v>361.9576015793793</v>
       </c>
       <c r="E6" t="n">
-        <v>69720770.16341294</v>
+        <v>53.11276688981836</v>
       </c>
       <c r="F6" t="n">
-        <v>2234684.868962158</v>
+        <v>685.5283940054466</v>
       </c>
       <c r="G6" t="n">
-        <v>124.6548364110461</v>
+        <v>163.6192198405679</v>
       </c>
       <c r="H6" t="n">
-        <v>25787973.82733886</v>
+        <v>236.1854966664283</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04775313419371516</v>
+        <v>0.3076770439122916</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07057686242125157</v>
+        <v>0.8875941641000081</v>
       </c>
       <c r="D7" t="n">
-        <v>0.206218022931038</v>
+        <v>26.87022059663273</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1336195399382477</v>
+        <v>0.7636159736904643</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2103808945563353</v>
+        <v>0.9718315646993134</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1824454735756698</v>
+        <v>2.43959457706712</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1418323212693763</v>
+        <v>5.373422320016989</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-40.05309863400412</v>
+        <v>-23.04279010044796</v>
       </c>
       <c r="C8" t="n">
-        <v>-16.28613031107631</v>
+        <v>-5.145558543428248</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.37252151551809</v>
+        <v>-14.26923226100188</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.55006407315503</v>
+        <v>-37.20641639630234</v>
       </c>
       <c r="F8" t="n">
-        <v>-85.91083578014168</v>
+        <v>-75.8166825218731</v>
       </c>
       <c r="G8" t="n">
-        <v>-112.600781285056</v>
+        <v>-87.80960236832247</v>
       </c>
       <c r="H8" t="n">
-        <v>-56.29557193315853</v>
+        <v>-40.54838036522934</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-39.46142490199546</v>
+        <v>-22.4511163684393</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.91085190339214</v>
+        <v>-5.770280135744082</v>
       </c>
       <c r="D9" t="n">
-        <v>-39.99724310783393</v>
+        <v>-14.89395385331772</v>
       </c>
       <c r="E9" t="n">
-        <v>-44.17478566547087</v>
+        <v>-37.83113798861817</v>
       </c>
       <c r="F9" t="n">
-        <v>-84.45611583077768</v>
+        <v>-74.3619625725091</v>
       </c>
       <c r="G9" t="n">
-        <v>-110.9059332126714</v>
+        <v>-86.11475429593786</v>
       </c>
       <c r="H9" t="n">
-        <v>-55.98439243702359</v>
+        <v>-40.23720086909437</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4954540784458054</v>
+        <v>0.2061209256732376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4466827485425068</v>
+        <v>0.1355693108558236</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2547069820064072</v>
+        <v>-9.687627973735076</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.030652762882765</v>
+        <v>-4.540375911292728</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6125659857441943</v>
+        <v>-3.914483026247984</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.886605976126188</v>
+        <v>-15.1017063369092</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2695438180471423</v>
+        <v>-5.483750501942654</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08241504847748764</v>
+        <v>0.1390470212650308</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2080309142080452</v>
+        <v>0.2567128536828114</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02440424442084847</v>
+        <v>0.08582026226259054</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03158053396128593</v>
+        <v>0.05172321292284317</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01413845356240746</v>
+        <v>0.05154027311121574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01967020954366189</v>
+        <v>0.05178862526984778</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0633732340289561</v>
+        <v>0.1061053747523899</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02157197732152219</v>
+        <v>0.03394248304426824</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07777245468053869</v>
+        <v>0.1215015382035748</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009574309086371023</v>
+        <v>0.008155422348654974</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001196280993389941</v>
+        <v>0.003263900461410422</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002628713315927126</v>
+        <v>0.00333444333231304</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005224158304635719</v>
+        <v>0.002914074992377572</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01704723851102403</v>
+        <v>0.02885197706376651</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1468740185380729</v>
+        <v>0.1842348583853453</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2788771318708988</v>
+        <v>0.3485707076097686</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03094238046170822</v>
+        <v>0.09030737704448609</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03458729525981963</v>
+        <v>0.05713055628479756</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01621330723796698</v>
+        <v>0.05774463899197085</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0228564177084593</v>
+        <v>0.05398217291270862</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08839175851282095</v>
+        <v>0.1319950518715128</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.50622689114977</v>
+        <v>91.28304148274545</v>
       </c>
       <c r="C6" t="n">
-        <v>147506788.1318934</v>
+        <v>60.91276855493501</v>
       </c>
       <c r="D6" t="n">
-        <v>37.33514119838302</v>
+        <v>152.3666926333759</v>
       </c>
       <c r="E6" t="n">
-        <v>135032168.8904556</v>
+        <v>144.6477189163851</v>
       </c>
       <c r="F6" t="n">
-        <v>4305897.554513209</v>
+        <v>3823.568429800823</v>
       </c>
       <c r="G6" t="n">
-        <v>220.4606098493872</v>
+        <v>797.6775253402293</v>
       </c>
       <c r="H6" t="n">
-        <v>47807524.97980669</v>
+        <v>845.076029454749</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.171464160591324</v>
+        <v>0.2629234604290165</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2254358937136251</v>
+        <v>0.3453802834857553</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7641645924759364</v>
+        <v>6.425994375529163</v>
       </c>
       <c r="E7" t="n">
-        <v>1.230066451120405</v>
+        <v>3.330795007421611</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1214142142088566</v>
+        <v>2.955358036414029</v>
       </c>
       <c r="G7" t="n">
-        <v>1.742694967838362</v>
+        <v>9.667103507134851</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7092067133247516</v>
+        <v>3.831259111735738</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-14.52724137520021</v>
+        <v>-26.44779075829493</v>
       </c>
       <c r="C8" t="n">
-        <v>4.676192219367749</v>
+        <v>-8.646970137019673</v>
       </c>
       <c r="D8" t="n">
-        <v>-21.70754198556609</v>
+        <v>-24.85443352461478</v>
       </c>
       <c r="E8" t="n">
-        <v>-20.37122624045691</v>
+        <v>-30.3489940294202</v>
       </c>
       <c r="F8" t="n">
-        <v>-78.92615054785652</v>
+        <v>-64.44139436473259</v>
       </c>
       <c r="G8" t="n">
-        <v>-78.24160680260643</v>
+        <v>-71.89663687240221</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.84959578871974</v>
+        <v>-37.77270328108073</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-12.55499560183802</v>
+        <v>-26.05334160362249</v>
       </c>
       <c r="C9" t="n">
-        <v>2.593786911648298</v>
+        <v>-9.063451198563563</v>
       </c>
       <c r="D9" t="n">
-        <v>-23.78994729328554</v>
+        <v>-25.27091458615867</v>
       </c>
       <c r="E9" t="n">
-        <v>-22.45363154817636</v>
+        <v>-30.76547509096409</v>
       </c>
       <c r="F9" t="n">
-        <v>-74.07708404997652</v>
+        <v>-63.47158106515658</v>
       </c>
       <c r="G9" t="n">
-        <v>-72.59211322799106</v>
+        <v>-70.76673815747914</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.8123308016032</v>
+        <v>-37.56525028365743</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.374511628918107</v>
+        <v>-0.5138271356027622</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05307034858632154</v>
+        <v>-0.8160710115834942</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.593142729548513</v>
+        <v>-0.9328676085886785</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.212836882486148</v>
+        <v>-1.319074900464885</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.674096410389298</v>
+        <v>0.4621477129639738</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.961198561043178</v>
+        <v>-1.811626779927902</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.686638883855892</v>
+        <v>-0.821886620533958</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1236036012589695</v>
+        <v>0.1627555490793596</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2751620537663014</v>
+        <v>0.3938288669250914</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05196273027124796</v>
+        <v>0.03409846295180098</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03082860870973105</v>
+        <v>0.02787619956517612</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0435732650577683</v>
+        <v>0.01715972297709919</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03644501120146878</v>
+        <v>0.0181070948716821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09359587837758115</v>
+        <v>0.1089709827283682</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02674289966370312</v>
+        <v>0.06472402856281929</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1480161078388868</v>
+        <v>0.2552609759988682</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003504895469713004</v>
+        <v>0.001474915830791823</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001303607762182065</v>
+        <v>0.001366194236431612</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002492849311783335</v>
+        <v>0.0003649291212723582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001802770402929569</v>
+        <v>0.0005088461505788288</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03064385507486632</v>
+        <v>0.05394998165012702</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1635325645359453</v>
+        <v>0.2544091754690056</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3847286158305447</v>
+        <v>0.5052335855808362</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05920215764406737</v>
+        <v>0.03840463293395503</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03610550875118734</v>
+        <v>0.03696206482911382</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0499284419122341</v>
+        <v>0.01910311810339763</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04245904382966683</v>
+        <v>0.02255761845982037</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1226593887506076</v>
+        <v>0.1461116992293548</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.25783840216857</v>
+        <v>53.53950832982124</v>
       </c>
       <c r="C6" t="n">
-        <v>55407472.24138872</v>
+        <v>105.1190193297718</v>
       </c>
       <c r="D6" t="n">
-        <v>101.8921315208959</v>
+        <v>81.01631371728077</v>
       </c>
       <c r="E6" t="n">
-        <v>144663186.6941223</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>53590819.8353707</v>
+        <v>732.5229943792402</v>
       </c>
       <c r="G6" t="n">
-        <v>660.6882307972</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>42277050.43484706</v>
+        <v>195.3663059593523</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2068665410891601</v>
+        <v>1.002909921349604</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8400647601262345</v>
+        <v>1.451007973348512</v>
       </c>
       <c r="D7" t="n">
-        <v>2.761792491386706</v>
+        <v>1.165785447316316</v>
       </c>
       <c r="E7" t="n">
-        <v>1.330527180358744</v>
+        <v>1.397357612209936</v>
       </c>
       <c r="F7" t="n">
-        <v>2.208947835270076</v>
+        <v>0.1636111364956985</v>
       </c>
       <c r="G7" t="n">
-        <v>5.980243015190009</v>
+        <v>1.691688452567552</v>
       </c>
       <c r="H7" t="n">
-        <v>2.221406970570155</v>
+        <v>1.14539342388127</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.59337646605692</v>
+        <v>-16.63860485928564</v>
       </c>
       <c r="C8" t="n">
-        <v>-9.462605046346455</v>
+        <v>-0.1928129313212779</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.92156749279217</v>
+        <v>-31.11492612813105</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.85571793959087</v>
+        <v>-31.57435800616668</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.93194704958697</v>
+        <v>-86.98968893840416</v>
       </c>
       <c r="G8" t="n">
-        <v>-80.13959889929902</v>
+        <v>-90.58374298887142</v>
       </c>
       <c r="H8" t="n">
-        <v>-43.31746881561207</v>
+        <v>-42.8490223086967</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-30.3961518887207</v>
+        <v>-15.84970654994076</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.670845577118401</v>
+        <v>-1.025775054409058</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.12980802356412</v>
+        <v>-31.94788825121883</v>
       </c>
       <c r="E9" t="n">
-        <v>-38.06395847036281</v>
+        <v>-32.40732012925446</v>
       </c>
       <c r="F9" t="n">
-        <v>-69.44704039979896</v>
+        <v>-85.05006233925215</v>
       </c>
       <c r="G9" t="n">
-        <v>-79.57464954183747</v>
+        <v>-88.32394555902528</v>
       </c>
       <c r="H9" t="n">
-        <v>-43.21374231690041</v>
+        <v>-42.43411631385009</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global_ind/metrics_summary.xlsx
+++ b/results/cross_validation/global_ind/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7853519169707242</v>
+        <v>-0.7823160883497264</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6799816636859224</v>
+        <v>-0.6770074044568413</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2945111087674936</v>
+        <v>-0.306887083839253</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1539621853081679</v>
+        <v>-0.1468338627129084</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.238471411462817</v>
+        <v>-3.562922229872765</v>
       </c>
       <c r="G2" t="n">
-        <v>-38.19947240584995</v>
+        <v>-19.56311203498541</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.558625115340846</v>
+        <v>-4.17317978403615</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1871288937236316</v>
+        <v>0.1868555298197099</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3269989356012205</v>
+        <v>0.3265776317157603</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02713973240721687</v>
+        <v>0.0271251499912767</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02297097043403405</v>
+        <v>0.02296380356326922</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05780836641271536</v>
+        <v>0.05414246272686188</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08167996289243065</v>
+        <v>0.07895004278772159</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1172878102452082</v>
+        <v>0.1161024367674333</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07633313325612083</v>
+        <v>0.07620333570278325</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2361327042816217</v>
+        <v>0.235714652174162</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009878042960485855</v>
+        <v>0.0009972480476401139</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006798126642274524</v>
+        <v>0.0006756132857411791</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004232760453271744</v>
+        <v>0.003841900646759329</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007094291739157945</v>
+        <v>0.006678772489375917</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05424341778174138</v>
+        <v>0.05401858705774363</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.27628451504947</v>
+        <v>0.2760495167588294</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4859348765849408</v>
+        <v>0.4855045336288447</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03142935405076893</v>
+        <v>0.03157923443720753</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02607321737391556</v>
+        <v>0.0259925621234456</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06505966840733009</v>
+        <v>0.06198306741973431</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08422761862452212</v>
+        <v>0.08172375719076991</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1615015416818246</v>
+        <v>0.1604721119264719</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.06553800226001</v>
+        <v>60.94715964511741</v>
       </c>
       <c r="C6" t="n">
-        <v>77.4088394915687</v>
+        <v>77.10456525590368</v>
       </c>
       <c r="D6" t="n">
-        <v>47.61519562453687</v>
+        <v>47.21042956033012</v>
       </c>
       <c r="E6" t="n">
-        <v>48.82327596337516</v>
+        <v>48.82730241287865</v>
       </c>
       <c r="F6" t="n">
-        <v>4382.771055851253</v>
+        <v>3975.071755040604</v>
       </c>
       <c r="G6" t="n">
-        <v>1189.639388290864</v>
+        <v>1102.268319442748</v>
       </c>
       <c r="H6" t="n">
-        <v>967.8872155373097</v>
+        <v>885.2382552262637</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.179077536741004</v>
+        <v>1.177074322993733</v>
       </c>
       <c r="C7" t="n">
-        <v>1.339574784205824</v>
+        <v>1.337204955717932</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7790895912749642</v>
+        <v>0.7865283975702481</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6943290489148193</v>
+        <v>0.6900461762277827</v>
       </c>
       <c r="F7" t="n">
-        <v>3.750008711512271</v>
+        <v>2.744131998829122</v>
       </c>
       <c r="G7" t="n">
-        <v>23.5306154519448</v>
+        <v>12.34821750247637</v>
       </c>
       <c r="H7" t="n">
-        <v>5.212115854098947</v>
+        <v>3.180533892302531</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.15383366678466</v>
+        <v>-21.16915037458526</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.660167954280425</v>
+        <v>-6.670799838794617</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.52015576455705</v>
+        <v>-39.46306614954614</v>
       </c>
       <c r="E8" t="n">
-        <v>-41.76215974919598</v>
+        <v>-41.79933824874729</v>
       </c>
       <c r="F8" t="n">
-        <v>-63.57881091210268</v>
+        <v>-70.3032449716365</v>
       </c>
       <c r="G8" t="n">
-        <v>-62.33004238310949</v>
+        <v>-68.12349494352736</v>
       </c>
       <c r="H8" t="n">
-        <v>-39.16752840500505</v>
+        <v>-41.2548490878062</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-20.95660908944845</v>
+        <v>-20.97192579724904</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.86840848505237</v>
+        <v>-6.879040369566562</v>
       </c>
       <c r="D9" t="n">
-        <v>-39.72839629532899</v>
+        <v>-39.67130668031808</v>
       </c>
       <c r="E9" t="n">
-        <v>-41.97040027996793</v>
+        <v>-42.00757877951924</v>
       </c>
       <c r="F9" t="n">
-        <v>-63.09390426231468</v>
+        <v>-69.73829561417496</v>
       </c>
       <c r="G9" t="n">
-        <v>-61.76509302564795</v>
+        <v>-67.48443761391211</v>
       </c>
       <c r="H9" t="n">
-        <v>-39.0638019062934</v>
+        <v>-41.12543080912334</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01285879431279791</v>
+        <v>0.01378477906948428</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.356632800408567</v>
+        <v>-0.3515163980379843</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.510128558045912</v>
+        <v>-1.492852413558861</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.594013481564944</v>
+        <v>-3.44862182251074</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5608444930503984</v>
+        <v>-0.2594377031270509</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.059063832619204</v>
+        <v>-3.354745878158779</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.177970728562705</v>
+        <v>-1.482231572720655</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1489265333015127</v>
+        <v>0.1490010806140611</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2825895147471342</v>
+        <v>0.2820672110883485</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0363420359291716</v>
+        <v>0.03620719857873327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04540283780780691</v>
+        <v>0.04443407475388</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0307600838231013</v>
+        <v>0.03091868140769711</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03415984184253452</v>
+        <v>0.03262998210370528</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09636347457521023</v>
+        <v>0.09587637142440421</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0422054500740565</v>
+        <v>0.04216585938207393</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1906838501884471</v>
+        <v>0.1899647054774816</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001915407103483835</v>
+        <v>0.00190222417316529</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002706387249219502</v>
+        <v>0.002620735316810909</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001059022380346463</v>
+        <v>0.001060424500448219</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001458523456161739</v>
+        <v>0.001414394714174919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04000477340861918</v>
+        <v>0.03985472392735915</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2054396506861723</v>
+        <v>0.205343272064302</v>
       </c>
       <c r="C5" t="n">
-        <v>0.436673619753297</v>
+        <v>0.4358494068798094</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04376536419914537</v>
+        <v>0.0436144949892268</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05202294925529984</v>
+        <v>0.05119311786569469</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0325426240544069</v>
+        <v>0.0325641597534501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03819062000232176</v>
+        <v>0.03760843940094988</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1347724713251072</v>
+        <v>0.1343621484922388</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76.07009124589355</v>
+        <v>76.49749837086317</v>
       </c>
       <c r="C6" t="n">
-        <v>49.87826430339936</v>
+        <v>49.7507464159933</v>
       </c>
       <c r="D6" t="n">
-        <v>101.7318200409694</v>
+        <v>101.3823112490681</v>
       </c>
       <c r="E6" t="n">
-        <v>124.4636468698693</v>
+        <v>121.4627502440684</v>
       </c>
       <c r="F6" t="n">
-        <v>1892.404563150786</v>
+        <v>1759.766207014051</v>
       </c>
       <c r="G6" t="n">
-        <v>578.3211959018358</v>
+        <v>547.7941512898773</v>
       </c>
       <c r="H6" t="n">
-        <v>470.4782635854589</v>
+        <v>442.7756107639869</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3281861767580002</v>
+        <v>0.3278806678466065</v>
       </c>
       <c r="C7" t="n">
-        <v>1.085937070508966</v>
+        <v>1.081860426491265</v>
       </c>
       <c r="D7" t="n">
-        <v>1.513758704772425</v>
+        <v>1.503374561977748</v>
       </c>
       <c r="E7" t="n">
-        <v>2.765197031087874</v>
+        <v>2.677842122949979</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9429893271627242</v>
+        <v>0.7621472161768582</v>
       </c>
       <c r="G7" t="n">
-        <v>4.842480232410149</v>
+        <v>2.619827679495113</v>
       </c>
       <c r="H7" t="n">
-        <v>1.913091423783357</v>
+        <v>1.495488779156261</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.48685325844336</v>
+        <v>-18.49529964279587</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05716925820799368</v>
+        <v>0.03449809166722062</v>
       </c>
       <c r="D8" t="n">
-        <v>-27.54695055360345</v>
+        <v>-27.58838875995615</v>
       </c>
       <c r="E8" t="n">
-        <v>-25.47284391111524</v>
+        <v>-25.66580207188469</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.20490894937448</v>
+        <v>-79.03811772576184</v>
       </c>
       <c r="G8" t="n">
-        <v>-74.89429892318196</v>
+        <v>-81.85475044533149</v>
       </c>
       <c r="H8" t="n">
-        <v>-36.42478105625175</v>
+        <v>-38.76797675901047</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.50073037176227</v>
+        <v>-17.50917675611478</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.984033395651732</v>
+        <v>-1.006704562192505</v>
       </c>
       <c r="D9" t="n">
-        <v>-28.58815320746318</v>
+        <v>-28.62959141381588</v>
       </c>
       <c r="E9" t="n">
-        <v>-26.51404656497497</v>
+        <v>-26.70700472574442</v>
       </c>
       <c r="F9" t="n">
-        <v>-69.78037570043449</v>
+        <v>-76.21337093845415</v>
       </c>
       <c r="G9" t="n">
-        <v>-72.06955213587428</v>
+        <v>-78.6594637972552</v>
       </c>
       <c r="H9" t="n">
-        <v>-35.90614856269349</v>
+        <v>-38.12088536559615</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02213016696005154</v>
+        <v>0.02326993480633999</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.349849790921938</v>
+        <v>-0.3446247259365742</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.499910377776507</v>
+        <v>-1.482980376192851</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.47630860438323</v>
+        <v>-3.332897877824362</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5526222052997958</v>
+        <v>-0.2539844570792846</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.010570016091044</v>
+        <v>-3.329129282644509</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.14452180458541</v>
+        <v>-1.453391130811873</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1487277167945368</v>
+        <v>0.1488007777771706</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2818880180758711</v>
+        <v>0.2813510273811096</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03626031443574911</v>
+        <v>0.03612758556131547</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04461788763263513</v>
+        <v>0.04364485823471833</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03066202315050746</v>
+        <v>0.03084453424409424</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03397173759555959</v>
+        <v>0.03243888910967238</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09602128294747654</v>
+        <v>0.09553461205134678</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04180905039675883</v>
+        <v>0.04176031935944077</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1897304526556838</v>
+        <v>0.1889960346845173</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001907609903212973</v>
+        <v>0.001894691104615432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002637045924895173</v>
+        <v>0.002552560983064308</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001053443613989976</v>
+        <v>0.001055832962731295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001449747080846427</v>
+        <v>0.001406074601290201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03976455826256453</v>
+        <v>0.03961091894927655</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2044726152734366</v>
+        <v>0.2043534177826267</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4355805926067917</v>
+        <v>0.4347367418156847</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04367619378120045</v>
+        <v>0.04352804963027212</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05135217546409473</v>
+        <v>0.05052287583921077</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03245679611406486</v>
+        <v>0.03249358340859462</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03807554439330352</v>
+        <v>0.03749766127760772</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1342689862721486</v>
+        <v>0.1338553882923328</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76.64900417143554</v>
+        <v>77.10131045441287</v>
       </c>
       <c r="C6" t="n">
-        <v>49.71568531185098</v>
+        <v>49.58481741248614</v>
       </c>
       <c r="D6" t="n">
-        <v>101.5234687223257</v>
+        <v>101.1797371775791</v>
       </c>
       <c r="E6" t="n">
-        <v>122.0290238577726</v>
+        <v>119.0147413451327</v>
       </c>
       <c r="F6" t="n">
-        <v>1863.418194401926</v>
+        <v>1732.589395693212</v>
       </c>
       <c r="G6" t="n">
-        <v>576.2883589289536</v>
+        <v>545.8995276673451</v>
       </c>
       <c r="H6" t="n">
-        <v>464.9372892323775</v>
+        <v>437.5615882916945</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3251272851897158</v>
+        <v>0.3247512431097066</v>
       </c>
       <c r="C7" t="n">
-        <v>1.08053250827112</v>
+        <v>1.076369284120269</v>
       </c>
       <c r="D7" t="n">
-        <v>1.507616880530402</v>
+        <v>1.497440793262172</v>
       </c>
       <c r="E7" t="n">
-        <v>2.694477026924792</v>
+        <v>2.608312312070907</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9380481442394636</v>
+        <v>0.7588688403953947</v>
       </c>
       <c r="G7" t="n">
-        <v>4.813371655567813</v>
+        <v>2.604446074028512</v>
       </c>
       <c r="H7" t="n">
-        <v>1.893195583453884</v>
+        <v>1.47836475783116</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.57178201597015</v>
+        <v>-18.58227819146728</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02709469407835741</v>
+        <v>0.003824532113272383</v>
       </c>
       <c r="D8" t="n">
-        <v>-27.5714250806128</v>
+        <v>-27.61219675528741</v>
       </c>
       <c r="E8" t="n">
-        <v>-25.62857573707144</v>
+        <v>-25.82394870024029</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.26829018446995</v>
+        <v>-79.09452871073884</v>
       </c>
       <c r="G8" t="n">
-        <v>-74.9727601419616</v>
+        <v>-81.93734798866991</v>
       </c>
       <c r="H8" t="n">
-        <v>-36.49762307766793</v>
+        <v>-38.84107930238174</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.58565912928905</v>
+        <v>-17.59615530478618</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.014107959781368</v>
+        <v>-1.037378121746453</v>
       </c>
       <c r="D9" t="n">
-        <v>-28.61262773447253</v>
+        <v>-28.65339940914713</v>
       </c>
       <c r="E9" t="n">
-        <v>-26.66977839093117</v>
+        <v>-26.86515135410001</v>
       </c>
       <c r="F9" t="n">
-        <v>-69.84375693552994</v>
+        <v>-76.26978192343115</v>
       </c>
       <c r="G9" t="n">
-        <v>-72.14801335465391</v>
+        <v>-78.74206134059362</v>
       </c>
       <c r="H9" t="n">
-        <v>-35.97899058410966</v>
+        <v>-38.19398790896742</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02135013319848666</v>
+        <v>0.01812392425552778</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3603544904920113</v>
+        <v>-0.3575253356094592</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.392790204425771</v>
+        <v>-2.35735428939352</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.794064849065286</v>
+        <v>-5.492992234719369</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2784097345452978</v>
+        <v>-0.3819218769613919</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.244861261157043</v>
+        <v>-4.010986379697517</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.674855067747821</v>
+        <v>-2.097109365354288</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1502458846592076</v>
+        <v>0.1503438555277505</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2835296226576694</v>
+        <v>0.2832455746402339</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04331432633376062</v>
+        <v>0.04306434647450755</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05783167808823388</v>
+        <v>0.0562588222840119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02738446211302237</v>
+        <v>0.03088596239353735</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03620619751230661</v>
+        <v>0.03832490547140281</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09975202856070009</v>
+        <v>0.1003539111319073</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04184240092026058</v>
+        <v>0.04198033822820198</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1912069587216519</v>
+        <v>0.1908093020045049</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002588940888050178</v>
+        <v>0.002561900757713562</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004002463325731706</v>
+        <v>0.003825097915763992</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008673923162520557</v>
+        <v>0.001163554030816099</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00149214893838216</v>
+        <v>0.00162753759841512</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04033338418505476</v>
+        <v>0.04032795508923594</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2045541515595823</v>
+        <v>0.2048910398924316</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4372721792221086</v>
+        <v>0.4368172409652633</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05088163605909481</v>
+        <v>0.05061522258879794</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06326502450589666</v>
+        <v>0.06184737598123296</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02945152485444609</v>
+        <v>0.03411090779818237</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0386283437178215</v>
+        <v>0.04034275149782325</v>
       </c>
       <c r="H5" t="n">
-        <v>0.137342143319825</v>
+        <v>0.1381040897872886</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81.45559495045845</v>
+        <v>81.49088537957932</v>
       </c>
       <c r="C6" t="n">
-        <v>50.55591308919636</v>
+        <v>50.47971040610919</v>
       </c>
       <c r="D6" t="n">
-        <v>118.1758434350344</v>
+        <v>117.5251399091162</v>
       </c>
       <c r="E6" t="n">
-        <v>162.8892959447662</v>
+        <v>158.0192599063454</v>
       </c>
       <c r="F6" t="n">
-        <v>1754.330619080523</v>
+        <v>1695.999752285465</v>
       </c>
       <c r="G6" t="n">
-        <v>554.3216218169428</v>
+        <v>547.4663205920912</v>
       </c>
       <c r="H6" t="n">
-        <v>453.6214813861536</v>
+        <v>441.8301780797844</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3253846406846365</v>
+        <v>0.3264490594830831</v>
       </c>
       <c r="C7" t="n">
-        <v>1.08890243650552</v>
+        <v>1.086648224171982</v>
       </c>
       <c r="D7" t="n">
-        <v>2.044298639898733</v>
+        <v>2.022999234696911</v>
       </c>
       <c r="E7" t="n">
-        <v>4.087042358095196</v>
+        <v>3.906150477913692</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7732601899699317</v>
+        <v>0.8357821018199778</v>
       </c>
       <c r="G7" t="n">
-        <v>4.954005765207961</v>
+        <v>3.013870380456292</v>
       </c>
       <c r="H7" t="n">
-        <v>2.21214900506033</v>
+        <v>1.86531657975699</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.56460569750363</v>
+        <v>-18.53498516959758</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07360669576361012</v>
+        <v>0.06111538892699819</v>
       </c>
       <c r="D8" t="n">
-        <v>-25.73903846261281</v>
+        <v>-25.80203487507982</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.12507165585409</v>
+        <v>-23.39702727883242</v>
       </c>
       <c r="F8" t="n">
-        <v>-74.60023021963659</v>
+        <v>-77.83158979563264</v>
       </c>
       <c r="G8" t="n">
-        <v>-74.59799344788733</v>
+        <v>-79.88961915085071</v>
       </c>
       <c r="H8" t="n">
-        <v>-36.09222213128847</v>
+        <v>-37.56569014684436</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.57848281082253</v>
+        <v>-17.54886228291648</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.9675959580961155</v>
+        <v>-0.9800872649327275</v>
       </c>
       <c r="D9" t="n">
-        <v>-26.78024111647254</v>
+        <v>-26.84323752893955</v>
       </c>
       <c r="E9" t="n">
-        <v>-24.16627430971382</v>
+        <v>-24.43822993269215</v>
       </c>
       <c r="F9" t="n">
-        <v>-72.17569697069658</v>
+        <v>-75.00684300832495</v>
       </c>
       <c r="G9" t="n">
-        <v>-71.77324666057964</v>
+        <v>-76.69433250277442</v>
       </c>
       <c r="H9" t="n">
-        <v>-35.5735896377302</v>
+        <v>-36.91859875343005</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.029086591425855</v>
+        <v>-0.9496884370953038</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8988629672901018</v>
+        <v>-0.903313745568129</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.280788446601586</v>
+        <v>0.1842037638425481</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1622430458527879</v>
+        <v>0.09458520374717816</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.395389160165701</v>
+        <v>-0.2000229567452745</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.37324547977593</v>
+        <v>-21.48159712079644</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.523269281851994</v>
+        <v>-3.875972215435903</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.210668615886091</v>
+        <v>0.2036009284764081</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3562864381918411</v>
+        <v>0.3569346801229619</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02465934941190585</v>
+        <v>0.02346699773595238</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0222086699571266</v>
+        <v>0.0190597046271351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06499967541728786</v>
+        <v>0.02298019653248973</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03045885755376665</v>
+        <v>0.06454037193905916</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1182136010696698</v>
+        <v>0.1150971465723344</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08675406551461282</v>
+        <v>0.08335937910170244</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2668979413398306</v>
+        <v>0.2675235281147735</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009773329261631521</v>
+        <v>0.0006225107079566476</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006846910163438441</v>
+        <v>0.000533390480821703</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005017721282842892</v>
+        <v>0.001010398324008751</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002420280149452909</v>
+        <v>0.007301884661823009</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0604586720382077</v>
+        <v>0.06005851523184767</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2945404310355589</v>
+        <v>0.2887202436645246</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5166216617020918</v>
+        <v>0.5172267666263739</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03126232438836166</v>
+        <v>0.02495016448756696</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02616660116147766</v>
+        <v>0.02309524801385997</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0708358756764035</v>
+        <v>0.03178676334590785</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04919634284632252</v>
+        <v>0.08545106589050255</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1647705394683693</v>
+        <v>0.161871708671456</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82.69874812079547</v>
+        <v>78.22914956383057</v>
       </c>
       <c r="C6" t="n">
-        <v>98.71527347485141</v>
+        <v>99.12539305293008</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19773350253099</v>
+        <v>47.60278561250001</v>
       </c>
       <c r="E6" t="n">
-        <v>51.6121177336514</v>
+        <v>39.81877799760491</v>
       </c>
       <c r="F6" t="n">
-        <v>4724.518032301897</v>
+        <v>403.4226051522059</v>
       </c>
       <c r="G6" t="n">
-        <v>127.7123349666179</v>
+        <v>800.2835124508069</v>
       </c>
       <c r="H6" t="n">
-        <v>853.9090400167239</v>
+        <v>244.7470373049797</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.340907646575971</v>
+        <v>1.288516192999566</v>
       </c>
       <c r="C7" t="n">
-        <v>1.514974898249824</v>
+        <v>1.51852118670156</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7718413340575802</v>
+        <v>0.2461746283428053</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7003043949345542</v>
+        <v>0.2729978122124218</v>
       </c>
       <c r="F7" t="n">
-        <v>4.446258305895401</v>
+        <v>0.723428331700777</v>
       </c>
       <c r="G7" t="n">
-        <v>8.029335680074793</v>
+        <v>13.50118091100442</v>
       </c>
       <c r="H7" t="n">
-        <v>2.800603709964687</v>
+        <v>2.925136510493591</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.00210196878371</v>
+        <v>-18.36134734460813</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.925333614967807</v>
+        <v>-3.91128656566816</v>
       </c>
       <c r="D8" t="n">
-        <v>-37.58409920143608</v>
+        <v>-40.29049836941944</v>
       </c>
       <c r="E8" t="n">
-        <v>-39.71925735497644</v>
+        <v>-41.2175407556248</v>
       </c>
       <c r="F8" t="n">
-        <v>-59.53735251266497</v>
+        <v>-85.66633839370634</v>
       </c>
       <c r="G8" t="n">
-        <v>-74.31033575660055</v>
+        <v>-64.87471907814681</v>
       </c>
       <c r="H8" t="n">
-        <v>-38.8464134015716</v>
+        <v>-42.38695508452895</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.60765281411127</v>
+        <v>-17.96689818993569</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.341814676511697</v>
+        <v>-4.32776762721205</v>
       </c>
       <c r="D9" t="n">
-        <v>-38.00058026297997</v>
+        <v>-40.70697943096333</v>
       </c>
       <c r="E9" t="n">
-        <v>-40.13573841652033</v>
+        <v>-41.63402181716869</v>
       </c>
       <c r="F9" t="n">
-        <v>-58.56753921308897</v>
+        <v>-84.53643967878327</v>
       </c>
       <c r="G9" t="n">
-        <v>-73.18043704167748</v>
+        <v>-63.59660441891629</v>
       </c>
       <c r="H9" t="n">
-        <v>-38.63896040414829</v>
+        <v>-42.12811852716322</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.07754765751219406</v>
+        <v>-0.08235292338944777</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2602387229181446</v>
+        <v>-0.2611948815356866</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.284764519011035</v>
+        <v>-4.284072555558113</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.218024089293901</v>
+        <v>-6.215364274057012</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.470294472399476</v>
+        <v>-2.549995122221021</v>
       </c>
       <c r="G2" t="n">
-        <v>-24.7509146712048</v>
+        <v>-12.58090778104342</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.510297355389924</v>
+        <v>-4.328981256300783</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.154488608791458</v>
+        <v>0.1544578201938022</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2728874968903159</v>
+        <v>0.2729912614067463</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0581453563659349</v>
+        <v>0.05814086353605746</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05971260037743614</v>
+        <v>0.05969956003694721</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04887995827486039</v>
+        <v>0.0489459770981144</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0672002132550687</v>
+        <v>0.06481396601247276</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1102190389925123</v>
+        <v>0.1098415747140234</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04607079878697546</v>
+        <v>0.04627624903857733</v>
       </c>
       <c r="C4" t="n">
-        <v>0.177135015289496</v>
+        <v>0.1772694098040093</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004032652219148978</v>
+        <v>0.004032124201685956</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004252222688987351</v>
+        <v>0.004250655760620405</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003033064417428333</v>
+        <v>0.002989033752704068</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004660381633106529</v>
+        <v>0.004410995432717755</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03986402250585711</v>
+        <v>0.03987141133171913</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2146410929597952</v>
+        <v>0.2151191507945709</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4208741085995859</v>
+        <v>0.4210337395079037</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06350316700093767</v>
+        <v>0.06349900945436832</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06520906907008679</v>
+        <v>0.06519705331240366</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05507326408910528</v>
+        <v>0.05467205641554072</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06826698787193214</v>
+        <v>0.06641532528504061</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1479279482652405</v>
+        <v>0.1476560557949713</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86.6849932876617</v>
+        <v>86.11241211214697</v>
       </c>
       <c r="C6" t="n">
-        <v>47.92680840201113</v>
+        <v>47.94508226345389</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4913922114179</v>
+        <v>147.4815413455485</v>
       </c>
       <c r="E6" t="n">
-        <v>168.5975191169675</v>
+        <v>168.5574058350518</v>
       </c>
       <c r="F6" t="n">
-        <v>3634.43666514423</v>
+        <v>3333.28431650717</v>
       </c>
       <c r="G6" t="n">
-        <v>957.3900657260216</v>
+        <v>892.9394854161966</v>
       </c>
       <c r="H6" t="n">
-        <v>840.4212406480516</v>
+        <v>779.3867072465946</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7140277128090821</v>
+        <v>0.717198502687677</v>
       </c>
       <c r="C7" t="n">
-        <v>1.007132255156181</v>
+        <v>1.007894102647025</v>
       </c>
       <c r="D7" t="n">
-        <v>3.17950442451343</v>
+        <v>3.179088507217229</v>
       </c>
       <c r="E7" t="n">
-        <v>4.339767565340924</v>
+        <v>4.338169482499077</v>
       </c>
       <c r="F7" t="n">
-        <v>2.689422973624086</v>
+        <v>2.137181720586399</v>
       </c>
       <c r="G7" t="n">
-        <v>15.46007333700923</v>
+        <v>8.157720062231856</v>
       </c>
       <c r="H7" t="n">
-        <v>4.564988044742155</v>
+        <v>3.256208729644877</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.6981836547161</v>
+        <v>-21.65813786313673</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.385058233671721</v>
+        <v>-4.380507685943545</v>
       </c>
       <c r="D8" t="n">
-        <v>-27.07998600355974</v>
+        <v>-27.08077166818758</v>
       </c>
       <c r="E8" t="n">
-        <v>-26.76188068266635</v>
+        <v>-26.76409206799047</v>
       </c>
       <c r="F8" t="n">
-        <v>-63.57818173982952</v>
+        <v>-69.56646634468898</v>
       </c>
       <c r="G8" t="n">
-        <v>-63.7925532028584</v>
+        <v>-69.93116850605982</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.54930725288364</v>
+        <v>-36.56352402266785</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.10650992270745</v>
+        <v>-21.06646413112808</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.009779825987556</v>
+        <v>-5.00522927825938</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.70470759587558</v>
+        <v>-27.70549326050342</v>
       </c>
       <c r="E9" t="n">
-        <v>-27.38660227498219</v>
+        <v>-27.3888136603063</v>
       </c>
       <c r="F9" t="n">
-        <v>-62.12346179046551</v>
+        <v>-67.87161827230436</v>
       </c>
       <c r="G9" t="n">
-        <v>-62.09770513047379</v>
+        <v>-68.01399651721404</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.23812775674867</v>
+        <v>-36.17526918661926</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07199016154160831</v>
+        <v>0.06765441584622733</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1102121398269829</v>
+        <v>-0.1128701718724501</v>
       </c>
       <c r="D2" t="n">
-        <v>-43.69911423317989</v>
+        <v>-44.10645481891156</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2659531178650831</v>
+        <v>-0.2554398248829635</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6121669710555091</v>
+        <v>-0.2774541327016584</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.059276790266954</v>
+        <v>-1.397894042920501</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.945788848442135</v>
+        <v>-7.680409762573817</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1507797174144304</v>
+        <v>0.1510569370533039</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2695324855241041</v>
+        <v>0.269606360141496</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1822782044466678</v>
+        <v>0.1831678970184684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02490448091297283</v>
+        <v>0.02474739014253439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02331038743724577</v>
+        <v>0.02435930629775725</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02312835281218326</v>
+        <v>0.02299334282091663</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1123222714246007</v>
+        <v>0.1126552055790794</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03967727482110585</v>
+        <v>0.03986265062896995</v>
       </c>
       <c r="C4" t="n">
-        <v>0.156047771574156</v>
+        <v>0.1564213758274229</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0341086119462819</v>
+        <v>0.03441944186331814</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007457878367245494</v>
+        <v>0.0007395943324633418</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001093844332862713</v>
+        <v>0.001075594018784916</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007346449335335644</v>
+        <v>0.0007788212571642105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03873465590744409</v>
+        <v>0.03888291298802057</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1991915530867357</v>
+        <v>0.1996563313019899</v>
       </c>
       <c r="C5" t="n">
-        <v>0.395028823725758</v>
+        <v>0.3955014232938016</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1846851698060294</v>
+        <v>0.1855247742575588</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0273091163666009</v>
+        <v>0.02719548367768703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03307331753638744</v>
+        <v>0.03279625007199628</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0271043342204446</v>
+        <v>0.02790736922685853</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1443987191236593</v>
+        <v>0.144763605304982</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98.27451598591109</v>
+        <v>98.30320084919066</v>
       </c>
       <c r="C6" t="n">
-        <v>54.620481697447</v>
+        <v>54.51706485233812</v>
       </c>
       <c r="D6" t="n">
-        <v>361.9576015793793</v>
+        <v>364.3896855720177</v>
       </c>
       <c r="E6" t="n">
-        <v>53.11276688981836</v>
+        <v>52.86303005040527</v>
       </c>
       <c r="F6" t="n">
-        <v>685.5283940054466</v>
+        <v>633.9186529699905</v>
       </c>
       <c r="G6" t="n">
-        <v>163.6192198405679</v>
+        <v>162.2355465186614</v>
       </c>
       <c r="H6" t="n">
-        <v>236.1854966664283</v>
+        <v>227.7045301354339</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3076770439122916</v>
+        <v>0.3091075306864108</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8875941641000081</v>
+        <v>0.8897120292818621</v>
       </c>
       <c r="D7" t="n">
-        <v>26.87022059663273</v>
+        <v>27.11506010995559</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7636159736904643</v>
+        <v>0.7572993269952268</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9718315646993134</v>
+        <v>0.7709783112472941</v>
       </c>
       <c r="G7" t="n">
-        <v>2.43959457706712</v>
+        <v>1.442826775512331</v>
       </c>
       <c r="H7" t="n">
-        <v>5.373422320016989</v>
+        <v>5.214164013946451</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-23.04279010044796</v>
+        <v>-23.00083921145571</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.145558543428248</v>
+        <v>-5.131210716729584</v>
       </c>
       <c r="D8" t="n">
-        <v>-14.26923226100188</v>
+        <v>-14.21480222283694</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.20641639630234</v>
+        <v>-37.25645232873681</v>
       </c>
       <c r="F8" t="n">
-        <v>-75.8166825218731</v>
+        <v>-82.85346852723019</v>
       </c>
       <c r="G8" t="n">
-        <v>-87.80960236832247</v>
+        <v>-94.20820586101007</v>
       </c>
       <c r="H8" t="n">
-        <v>-40.54838036522934</v>
+        <v>-42.77749647799988</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.4511163684393</v>
+        <v>-22.40916547944705</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.770280135744082</v>
+        <v>-5.755932309045418</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.89395385331772</v>
+        <v>-14.83952381515277</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.83113798861817</v>
+        <v>-37.88117392105265</v>
       </c>
       <c r="F9" t="n">
-        <v>-74.3619625725091</v>
+        <v>-81.15862045484558</v>
       </c>
       <c r="G9" t="n">
-        <v>-86.11475429593786</v>
+        <v>-92.29103387216429</v>
       </c>
       <c r="H9" t="n">
-        <v>-40.23720086909437</v>
+        <v>-42.38924164195129</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2061209256732376</v>
+        <v>0.2335993026237932</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1355693108558236</v>
+        <v>-0.5290231103151299</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.687627973735076</v>
+        <v>-11.39188456335302</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.540375911292728</v>
+        <v>-1.465382854393294</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.914483026247984</v>
+        <v>-2.956289008524867</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.1017063369092</v>
+        <v>-1.375084784861915</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.483750501942654</v>
+        <v>-2.91401083647074</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1390470212650308</v>
+        <v>0.1371205589208931</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2567128536828114</v>
+        <v>0.3054874404833713</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08582026226259054</v>
+        <v>0.09314302752381215</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05172321292284317</v>
+        <v>0.02963463919130589</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05154027311121574</v>
+        <v>0.05195667172321858</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05178862526984778</v>
+        <v>0.02549988844523405</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1061053747523899</v>
+        <v>0.1071403710479725</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03394248304426824</v>
+        <v>0.03276763869594077</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1215015382035748</v>
+        <v>0.2149144658850919</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008155422348654974</v>
+        <v>0.009455891668224241</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003263900461410422</v>
+        <v>0.001452385968902619</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00333444333231304</v>
+        <v>0.00333112609307881</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002914074992377572</v>
+        <v>0.0007714129502423021</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02885197706376651</v>
+        <v>0.04378215354358009</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1842348583853453</v>
+        <v>0.1810183380101054</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3485707076097686</v>
+        <v>0.4635886817914042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09030737704448609</v>
+        <v>0.09724140922582437</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05713055628479756</v>
+        <v>0.03811018195840343</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05774463899197085</v>
+        <v>0.05771590849218965</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05398217291270862</v>
+        <v>0.02777432177825954</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1319950518715128</v>
+        <v>0.1442414735426978</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91.28304148274545</v>
+        <v>91.80024955120913</v>
       </c>
       <c r="C6" t="n">
-        <v>60.91276855493501</v>
+        <v>62.24422658038182</v>
       </c>
       <c r="D6" t="n">
-        <v>152.3666926333759</v>
+        <v>167.961944138628</v>
       </c>
       <c r="E6" t="n">
-        <v>144.6477189163851</v>
+        <v>105.1771770970309</v>
       </c>
       <c r="F6" t="n">
-        <v>3823.568429800823</v>
+        <v>3493.744197000073</v>
       </c>
       <c r="G6" t="n">
-        <v>797.6775253402293</v>
+        <v>286.2741150805386</v>
       </c>
       <c r="H6" t="n">
-        <v>845.076029454749</v>
+        <v>701.2003182413104</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2629234604290165</v>
+        <v>0.2543575563000206</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3453802834857553</v>
+        <v>1.221294118428206</v>
       </c>
       <c r="D7" t="n">
-        <v>6.425994375529163</v>
+        <v>7.45136898634733</v>
       </c>
       <c r="E7" t="n">
-        <v>3.330795007421611</v>
+        <v>1.48426305299244</v>
       </c>
       <c r="F7" t="n">
-        <v>2.955358036414029</v>
+        <v>2.381436981645231</v>
       </c>
       <c r="G7" t="n">
-        <v>9.667103507134851</v>
+        <v>1.429130849047489</v>
       </c>
       <c r="H7" t="n">
-        <v>3.831259111735738</v>
+        <v>2.370308590793453</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-26.44779075829493</v>
+        <v>-24.76482488175663</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.646970137019673</v>
+        <v>-3.2250909786219</v>
       </c>
       <c r="D8" t="n">
-        <v>-24.85443352461478</v>
+        <v>-21.96670364874051</v>
       </c>
       <c r="E8" t="n">
-        <v>-30.3489940294202</v>
+        <v>-33.20728547459781</v>
       </c>
       <c r="F8" t="n">
-        <v>-64.44139436473259</v>
+        <v>-68.15778325884912</v>
       </c>
       <c r="G8" t="n">
-        <v>-71.89663687240221</v>
+        <v>-94.34201414101415</v>
       </c>
       <c r="H8" t="n">
-        <v>-37.77270328108073</v>
+        <v>-40.94395039726336</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-26.05334160362249</v>
+        <v>-24.17315114974798</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.063451198563563</v>
+        <v>-3.849812570937734</v>
       </c>
       <c r="D9" t="n">
-        <v>-25.27091458615867</v>
+        <v>-22.59142524105635</v>
       </c>
       <c r="E9" t="n">
-        <v>-30.76547509096409</v>
+        <v>-33.83200706691365</v>
       </c>
       <c r="F9" t="n">
-        <v>-63.47158106515658</v>
+        <v>-66.46293518646451</v>
       </c>
       <c r="G9" t="n">
-        <v>-70.76673815747914</v>
+        <v>-92.42484215216837</v>
       </c>
       <c r="H9" t="n">
-        <v>-37.56525028365743</v>
+        <v>-40.55569556121476</v>
       </c>
     </row>
   </sheetData>
@@ -2686,19 +2686,19 @@
         <v>-0.8160710115834942</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9328676085886785</v>
+        <v>-0.9191158532285701</v>
       </c>
       <c r="E2" t="n">
         <v>-1.319074900464885</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4621477129639738</v>
+        <v>0.1227574786645215</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.811626779927902</v>
+        <v>-1.433744581814734</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.821886620533958</v>
+        <v>-0.8131793340049874</v>
       </c>
     </row>
     <row r="3">
@@ -2714,19 +2714,19 @@
         <v>0.3938288669250914</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03409846295180098</v>
+        <v>0.03396110384090924</v>
       </c>
       <c r="E3" t="n">
         <v>0.02787619956517612</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01715972297709919</v>
+        <v>0.02218259399273563</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0181070948716821</v>
+        <v>0.02157942154108264</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1089709827283682</v>
+        <v>0.1103639558240591</v>
       </c>
     </row>
     <row r="4">
@@ -2742,19 +2742,19 @@
         <v>0.2552609759988682</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001474915830791823</v>
+        <v>0.001464422260724389</v>
       </c>
       <c r="E4" t="n">
         <v>0.001366194236431612</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003649291212723582</v>
+        <v>0.0007386228474416795</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005088461505788288</v>
+        <v>0.0007904652920013855</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05394998165012702</v>
+        <v>0.05405745153304776</v>
       </c>
     </row>
     <row r="5">
@@ -2770,19 +2770,19 @@
         <v>0.5052335855808362</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03840463293395503</v>
+        <v>0.03826777052199917</v>
       </c>
       <c r="E5" t="n">
         <v>0.03696206482911382</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01910311810339763</v>
+        <v>0.02717761666227706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02255761845982037</v>
+        <v>0.02811521459995256</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1461116992293548</v>
+        <v>0.1483609046105307</v>
       </c>
     </row>
     <row r="6">
@@ -2798,19 +2798,19 @@
         <v>105.1190193297718</v>
       </c>
       <c r="D6" t="n">
-        <v>81.01631371728077</v>
+        <v>80.65500296057162</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>732.5229943792402</v>
+        <v>680.6986970648953</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>195.3663059593523</v>
+        <v>186.6687046141767</v>
       </c>
     </row>
     <row r="7">
@@ -2826,19 +2826,19 @@
         <v>1.451007973348512</v>
       </c>
       <c r="D7" t="n">
-        <v>1.165785447316316</v>
+        <v>1.157519703102156</v>
       </c>
       <c r="E7" t="n">
         <v>1.397357612209936</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1636111364956985</v>
+        <v>0.2656897923938528</v>
       </c>
       <c r="G7" t="n">
-        <v>1.691688452567552</v>
+        <v>1.465353400497643</v>
       </c>
       <c r="H7" t="n">
-        <v>1.14539342388127</v>
+        <v>1.123306400483617</v>
       </c>
     </row>
     <row r="8">
@@ -2854,19 +2854,19 @@
         <v>-0.1928129313212779</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.11492612813105</v>
+        <v>-31.15776685344548</v>
       </c>
       <c r="E8" t="n">
         <v>-31.57435800616668</v>
       </c>
       <c r="F8" t="n">
-        <v>-86.98968893840416</v>
+        <v>-85.73940059354416</v>
       </c>
       <c r="G8" t="n">
-        <v>-90.58374298887142</v>
+        <v>-92.00044332131378</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.8490223086967</v>
+        <v>-42.88389776084617</v>
       </c>
     </row>
     <row r="9">
@@ -2882,19 +2882,19 @@
         <v>-1.025775054409058</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.94788825121883</v>
+        <v>-31.99072897653326</v>
       </c>
       <c r="E9" t="n">
         <v>-32.40732012925446</v>
       </c>
       <c r="F9" t="n">
-        <v>-85.05006233925215</v>
+        <v>-83.47960316369802</v>
       </c>
       <c r="G9" t="n">
-        <v>-88.32394555902528</v>
+        <v>-89.44421400285275</v>
       </c>
       <c r="H9" t="n">
-        <v>-42.43411631385009</v>
+        <v>-42.36622464611472</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global_ind/metrics_summary.xlsx
+++ b/results/cross_validation/global_ind/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7823160883497264</v>
+        <v>0.7824658892906128</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6770074044568413</v>
+        <v>0.5094093513821161</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.306887083839253</v>
+        <v>-0.1585806900532691</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1468338627129084</v>
+        <v>-2.426336607928623</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.562922229872765</v>
+        <v>-13.10424892552914</v>
       </c>
       <c r="G2" t="n">
-        <v>-19.56311203498541</v>
+        <v>-26.85397935651841</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.17317978403615</v>
+        <v>-6.875211723226119</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1868555298197099</v>
+        <v>0.08879919021515653</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3265776317157603</v>
+        <v>0.1934150966512781</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0271251499912767</v>
+        <v>0.02048625967132823</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02296380356326922</v>
+        <v>0.04007148459297521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05414246272686188</v>
+        <v>0.09075855073308403</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07895004278772159</v>
+        <v>0.06381530104050372</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1161024367674333</v>
+        <v>0.08289098048405429</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07620333570278325</v>
+        <v>0.009300721108646102</v>
       </c>
       <c r="C4" t="n">
-        <v>0.235714652174162</v>
+        <v>0.06895581008857561</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009972480476401139</v>
+        <v>0.0008840796924818882</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006756132857411791</v>
+        <v>0.002018495101166572</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003841900646759329</v>
+        <v>0.009569637037269296</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006678772489375917</v>
+        <v>0.005040992735966898</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05401858705774363</v>
+        <v>0.01596162262735106</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2760495167588294</v>
+        <v>0.09644024631162086</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4855045336288447</v>
+        <v>0.2625943832007372</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03157923443720753</v>
+        <v>0.02973347763854555</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0259925621234456</v>
+        <v>0.04492766520938488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06198306741973431</v>
+        <v>0.09782452165622532</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08172375719076991</v>
+        <v>0.07099994884481887</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1604721119264719</v>
+        <v>0.1004200404768888</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60.94715964511741</v>
+        <v>64.73390371812778</v>
       </c>
       <c r="C6" t="n">
-        <v>77.10456525590368</v>
+        <v>42.67404350982396</v>
       </c>
       <c r="D6" t="n">
-        <v>47.21042956033012</v>
+        <v>40.76864506170178</v>
       </c>
       <c r="E6" t="n">
-        <v>48.82730241287865</v>
+        <v>91.95205648780433</v>
       </c>
       <c r="F6" t="n">
-        <v>3975.071755040604</v>
+        <v>6045.828601163543</v>
       </c>
       <c r="G6" t="n">
-        <v>1102.268319442748</v>
+        <v>981.4754545381314</v>
       </c>
       <c r="H6" t="n">
-        <v>885.2382552262637</v>
+        <v>1211.238784079855</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.177074322993733</v>
+        <v>0.07227073798886843</v>
       </c>
       <c r="C7" t="n">
-        <v>1.337204955717932</v>
+        <v>0.1959462616473681</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7865283975702481</v>
+        <v>0.6973861256014362</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6900461762277827</v>
+        <v>2.059627857898807</v>
       </c>
       <c r="F7" t="n">
-        <v>2.744131998829122</v>
+        <v>8.476946847169662</v>
       </c>
       <c r="G7" t="n">
-        <v>12.34821750247637</v>
+        <v>16.7204450037414</v>
       </c>
       <c r="H7" t="n">
-        <v>3.180533892302531</v>
+        <v>4.703770472341257</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.16915037458526</v>
+        <v>-40.0989700893831</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.670799838794617</v>
+        <v>-14.0457364782935</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.46306614954614</v>
+        <v>-40.18578009714098</v>
       </c>
       <c r="E8" t="n">
-        <v>-41.79933824874729</v>
+        <v>-35.23241826784894</v>
       </c>
       <c r="F8" t="n">
-        <v>-70.3032449716365</v>
+        <v>-53.78992001651945</v>
       </c>
       <c r="G8" t="n">
-        <v>-68.12349494352736</v>
+        <v>-66.77197918335133</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.2548490878062</v>
+        <v>-41.68746735542288</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-20.97192579724904</v>
+        <v>-39.90174551204688</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.879040369566562</v>
+        <v>-14.25397700906544</v>
       </c>
       <c r="D9" t="n">
-        <v>-39.67130668031808</v>
+        <v>-40.39402062791292</v>
       </c>
       <c r="E9" t="n">
-        <v>-42.00757877951924</v>
+        <v>-35.44065879862089</v>
       </c>
       <c r="F9" t="n">
-        <v>-69.73829561417496</v>
+        <v>-53.30501336673144</v>
       </c>
       <c r="G9" t="n">
-        <v>-67.48443761391211</v>
+        <v>-66.20702982588979</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.12543080912334</v>
+        <v>-41.58374085671122</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01378477906948428</v>
+        <v>0.9291635146888031</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3515163980379843</v>
+        <v>0.9241812184151683</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.492852413558861</v>
+        <v>0.7640394692998611</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.44862182251074</v>
+        <v>0.6175956270268713</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2594377031270509</v>
+        <v>-0.2872136294863503</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.354745878158779</v>
+        <v>-0.9743439915382948</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.482231572720655</v>
+        <v>0.3289037014010099</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1490010806140611</v>
+        <v>0.04403556628886632</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2820672110883485</v>
+        <v>0.09242833585278583</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03620719857873327</v>
+        <v>0.0115618576089384</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04443407475388</v>
+        <v>0.01303824750660437</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03091868140769711</v>
+        <v>0.02105628095420116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03262998210370528</v>
+        <v>0.01413858807315966</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09587637142440421</v>
+        <v>0.03270981271409262</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04216585938207393</v>
+        <v>0.003028630278017903</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1899647054774816</v>
+        <v>0.0106568388917315</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00190222417316529</v>
+        <v>0.0001800547128138745</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002620735316810909</v>
+        <v>0.0002252789033408987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001060424500448219</v>
+        <v>0.0008733656991344032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001414394714174919</v>
+        <v>0.0003573153261964814</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03985472392735915</v>
+        <v>0.002553580635205843</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.205343272064302</v>
+        <v>0.05503299263185588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4358494068798094</v>
+        <v>0.1032319664238335</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0436144949892268</v>
+        <v>0.01341844673626104</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05119311786569469</v>
+        <v>0.01500929389881145</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0325641597534501</v>
+        <v>0.02955276127766072</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03760843940094988</v>
+        <v>0.01890278620194603</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1343621484922388</v>
+        <v>0.03919137452839477</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76.49749837086317</v>
+        <v>48.81292239343433</v>
       </c>
       <c r="C6" t="n">
-        <v>49.7507464159933</v>
+        <v>47.39377760677964</v>
       </c>
       <c r="D6" t="n">
-        <v>101.3823112490681</v>
+        <v>23.02651505059477</v>
       </c>
       <c r="E6" t="n">
-        <v>121.4627502440684</v>
+        <v>38.34320171762113</v>
       </c>
       <c r="F6" t="n">
-        <v>1759.766207014051</v>
+        <v>396.7409059402107</v>
       </c>
       <c r="G6" t="n">
-        <v>547.7941512898773</v>
+        <v>161.4657176384032</v>
       </c>
       <c r="H6" t="n">
-        <v>442.7756107639869</v>
+        <v>119.2971733911739</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3278806678466065</v>
+        <v>0.02487098678797161</v>
       </c>
       <c r="C7" t="n">
-        <v>1.081860426491265</v>
+        <v>0.03170542169966156</v>
       </c>
       <c r="D7" t="n">
-        <v>1.503374561977748</v>
+        <v>0.0724141975090114</v>
       </c>
       <c r="E7" t="n">
-        <v>2.677842122949979</v>
+        <v>0.1163790071242773</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7621472161768582</v>
+        <v>0.7765508896705985</v>
       </c>
       <c r="G7" t="n">
-        <v>2.619827679495113</v>
+        <v>1.188106636379652</v>
       </c>
       <c r="H7" t="n">
-        <v>1.495488779156261</v>
+        <v>0.3683378565285287</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.49529964279587</v>
+        <v>-46.19680333614539</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03449809166722062</v>
+        <v>-21.24932066074852</v>
       </c>
       <c r="D8" t="n">
-        <v>-27.58838875995615</v>
+        <v>-45.73349875910093</v>
       </c>
       <c r="E8" t="n">
-        <v>-25.66580207188469</v>
+        <v>-44.38902811793378</v>
       </c>
       <c r="F8" t="n">
-        <v>-79.03811772576184</v>
+        <v>-78.51787428583665</v>
       </c>
       <c r="G8" t="n">
-        <v>-81.85475044533149</v>
+        <v>-97.17959469191756</v>
       </c>
       <c r="H8" t="n">
-        <v>-38.76797675901047</v>
+        <v>-55.54435330861381</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.50917675611478</v>
+        <v>-45.60512960413674</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.006704562192505</v>
+        <v>-21.87404225306436</v>
       </c>
       <c r="D9" t="n">
-        <v>-28.62959141381588</v>
+        <v>-46.35822035141677</v>
       </c>
       <c r="E9" t="n">
-        <v>-26.70700472574442</v>
+        <v>-45.01374971024961</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.21337093845415</v>
+        <v>-77.06315433647265</v>
       </c>
       <c r="G9" t="n">
-        <v>-78.6594637972552</v>
+        <v>-95.48474661953294</v>
       </c>
       <c r="H9" t="n">
-        <v>-38.12088536559615</v>
+        <v>-55.23317381247885</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02326993480633999</v>
+        <v>0.9320547132127137</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3446247259365742</v>
+        <v>0.9352803973170256</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.482980376192851</v>
+        <v>0.6114635403394146</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.332897877824362</v>
+        <v>0.6682832368174884</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2539844570792846</v>
+        <v>-0.1681262850760565</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.329129282644509</v>
+        <v>-1.013004705580842</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.453391130811873</v>
+        <v>0.3276584828382907</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1488007777771706</v>
+        <v>0.0427028383252445</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2813510273811096</v>
+        <v>0.08321360916164439</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03612758556131547</v>
+        <v>0.01671978073648907</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04364485823471833</v>
+        <v>0.01006889473483804</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03084453424409424</v>
+        <v>0.01995265683073481</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03243888910967238</v>
+        <v>0.01445018684761118</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09553461205134678</v>
+        <v>0.03118466110609366</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04176031935944077</v>
+        <v>0.002905016417860834</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1889960346845173</v>
+        <v>0.009096774763620237</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001894691104615432</v>
+        <v>0.0002964810277987099</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002552560983064308</v>
+        <v>0.0001954182376329676</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001055832962731295</v>
+        <v>0.0007925657453221845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001406074601290201</v>
+        <v>0.0003643121138425585</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03961091894927655</v>
+        <v>0.002275094717679582</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2043534177826267</v>
+        <v>0.05389820421740259</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4347367418156847</v>
+        <v>0.09537701381161101</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04352804963027212</v>
+        <v>0.01721862444560279</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05052287583921077</v>
+        <v>0.01397920733206885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03249358340859462</v>
+        <v>0.02815254420691289</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03749766127760772</v>
+        <v>0.01908696188089028</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1338553882923328</v>
+        <v>0.0379520926490814</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77.10131045441287</v>
+        <v>44.14323684719844</v>
       </c>
       <c r="C6" t="n">
-        <v>49.58481741248614</v>
+        <v>47.46600825357591</v>
       </c>
       <c r="D6" t="n">
-        <v>101.1797371775791</v>
+        <v>33.07962230437267</v>
       </c>
       <c r="E6" t="n">
-        <v>119.0147413451327</v>
+        <v>27.86820301829407</v>
       </c>
       <c r="F6" t="n">
-        <v>1732.589395693212</v>
+        <v>453.0527868880115</v>
       </c>
       <c r="G6" t="n">
-        <v>545.8995276673451</v>
+        <v>155.0773572626175</v>
       </c>
       <c r="H6" t="n">
-        <v>437.5615882916945</v>
+        <v>126.7812024290117</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3247512431097066</v>
+        <v>0.02441709752868847</v>
       </c>
       <c r="C7" t="n">
-        <v>1.076369284120269</v>
+        <v>0.02778362313942648</v>
       </c>
       <c r="D7" t="n">
-        <v>1.497440793262172</v>
+        <v>0.1187684746176347</v>
       </c>
       <c r="E7" t="n">
-        <v>2.608312312070907</v>
+        <v>0.1016518217210966</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7588688403953947</v>
+        <v>0.7059853630890851</v>
       </c>
       <c r="G7" t="n">
-        <v>2.604446074028512</v>
+        <v>1.212312860307885</v>
       </c>
       <c r="H7" t="n">
-        <v>1.47836475783116</v>
+        <v>0.3651532067339693</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.58227819146728</v>
+        <v>-44.57184613396323</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003824532113272383</v>
+        <v>-20.19901209917019</v>
       </c>
       <c r="D8" t="n">
-        <v>-27.61219675528741</v>
+        <v>-40.74116397257154</v>
       </c>
       <c r="E8" t="n">
-        <v>-25.82394870024029</v>
+        <v>-43.24221092706547</v>
       </c>
       <c r="F8" t="n">
-        <v>-79.09452871073884</v>
+        <v>-77.6828211550804</v>
       </c>
       <c r="G8" t="n">
-        <v>-81.93734798866991</v>
+        <v>-94.92749482757515</v>
       </c>
       <c r="H8" t="n">
-        <v>-38.84107930238174</v>
+        <v>-53.56075818590433</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.59615530478618</v>
+        <v>-43.78294782461835</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.037378121746453</v>
+        <v>-21.03197422225797</v>
       </c>
       <c r="D9" t="n">
-        <v>-28.65339940914713</v>
+        <v>-41.57412609565932</v>
       </c>
       <c r="E9" t="n">
-        <v>-26.86515135410001</v>
+        <v>-44.07517305015325</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.26978192343115</v>
+        <v>-75.7431945559284</v>
       </c>
       <c r="G9" t="n">
-        <v>-78.74206134059362</v>
+        <v>-92.667697397729</v>
       </c>
       <c r="H9" t="n">
-        <v>-38.19398790896742</v>
+        <v>-53.14585219105771</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01812392425552778</v>
+        <v>0.9323210020234601</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3575253356094592</v>
+        <v>0.933706693649946</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.35735428939352</v>
+        <v>0.6129528269087325</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.492992234719369</v>
+        <v>0.6609585744547751</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3819218769613919</v>
+        <v>-0.1821850017510909</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.010986379697517</v>
+        <v>-1.059791095869473</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.097109365354288</v>
+        <v>0.3163271665693916</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1503438555277505</v>
+        <v>0.04253350997813896</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2832455746402339</v>
+        <v>0.08493335552286792</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04306434647450755</v>
+        <v>0.01668363880929221</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0562588222840119</v>
+        <v>0.01024327948374632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03088596239353735</v>
+        <v>0.0200157576737275</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03832490547140281</v>
+        <v>0.014739106256143</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1003539111319073</v>
+        <v>0.03152477462065265</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04198033822820198</v>
+        <v>0.002893631178299882</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1908093020045049</v>
+        <v>0.009317969381798456</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002561900757713562</v>
+        <v>0.0002953445959355486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003825097915763992</v>
+        <v>0.0001997332821801447</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001163554030816099</v>
+        <v>0.0008021044890369502</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00162753759841512</v>
+        <v>0.0003727794804104851</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04032795508923594</v>
+        <v>0.002313593734610245</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2048910398924316</v>
+        <v>0.05379248254449577</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4368172409652633</v>
+        <v>0.09652962955382381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05061522258879794</v>
+        <v>0.01718559268502395</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06184737598123296</v>
+        <v>0.0141327025787761</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03411090779818237</v>
+        <v>0.02832144927500975</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04034275149782325</v>
+        <v>0.01930749803600883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1381040897872886</v>
+        <v>0.03821155911218971</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81.49088537957932</v>
+        <v>44.08126599164056</v>
       </c>
       <c r="C6" t="n">
-        <v>50.47971040610919</v>
+        <v>47.39442395067762</v>
       </c>
       <c r="D6" t="n">
-        <v>117.5251399091162</v>
+        <v>32.89868311823873</v>
       </c>
       <c r="E6" t="n">
-        <v>158.0192599063454</v>
+        <v>28.24198378471847</v>
       </c>
       <c r="F6" t="n">
-        <v>1695.999752285465</v>
+        <v>423.7313008113784</v>
       </c>
       <c r="G6" t="n">
-        <v>547.4663205920912</v>
+        <v>159.8587112382217</v>
       </c>
       <c r="H6" t="n">
-        <v>441.8301780797844</v>
+        <v>122.7010614824793</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3264490594830831</v>
+        <v>0.02432924121777188</v>
       </c>
       <c r="C7" t="n">
-        <v>1.086648224171982</v>
+        <v>0.02841057047227513</v>
       </c>
       <c r="D7" t="n">
-        <v>2.022999234696911</v>
+        <v>0.1183208931445351</v>
       </c>
       <c r="E7" t="n">
-        <v>3.906150477913692</v>
+        <v>0.1038522409610936</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8357821018199778</v>
+        <v>0.7144339473353063</v>
       </c>
       <c r="G7" t="n">
-        <v>3.013870380456292</v>
+        <v>1.240396548794259</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86531657975699</v>
+        <v>0.3716239069875401</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.53498516959758</v>
+        <v>-44.60718792220676</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06111538892699819</v>
+        <v>-20.05486330907693</v>
       </c>
       <c r="D8" t="n">
-        <v>-25.80203487507982</v>
+        <v>-40.76420656919491</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.39702727883242</v>
+        <v>-43.11116602322096</v>
       </c>
       <c r="F8" t="n">
-        <v>-77.83158979563264</v>
+        <v>-77.53926007602348</v>
       </c>
       <c r="G8" t="n">
-        <v>-79.88961915085071</v>
+        <v>-94.62880574030581</v>
       </c>
       <c r="H8" t="n">
-        <v>-37.56569014684436</v>
+        <v>-53.45091494000481</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.54886228291648</v>
+        <v>-43.81828961286188</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.9800872649327275</v>
+        <v>-20.88782543216471</v>
       </c>
       <c r="D9" t="n">
-        <v>-26.84323752893955</v>
+        <v>-41.59716869228269</v>
       </c>
       <c r="E9" t="n">
-        <v>-24.43822993269215</v>
+        <v>-43.94412814630874</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.00684300832495</v>
+        <v>-75.59963347687147</v>
       </c>
       <c r="G9" t="n">
-        <v>-76.69433250277442</v>
+        <v>-92.36900831045966</v>
       </c>
       <c r="H9" t="n">
-        <v>-36.91859875343005</v>
+        <v>-53.03600894515819</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.9496884370953038</v>
+        <v>0.3413256603975047</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.903313745568129</v>
+        <v>0.4043258234277325</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1842037638425481</v>
+        <v>-3.71687254946163</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09458520374717816</v>
+        <v>-1.630004205442799</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2000229567452745</v>
+        <v>-1.522317279100774</v>
       </c>
       <c r="G2" t="n">
-        <v>-21.48159712079644</v>
+        <v>-3.725451492983289</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.875972215435903</v>
+        <v>-1.641499007193876</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2036009284764081</v>
+        <v>0.1226779314085144</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3569346801229619</v>
+        <v>0.2082971651956806</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02346699773595238</v>
+        <v>0.05045185220581116</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0190597046271351</v>
+        <v>0.03011463521642217</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02298019653248973</v>
+        <v>0.03863281217633793</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06454037193905916</v>
+        <v>0.02680369334331373</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1150971465723344</v>
+        <v>0.07949634825768</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08335937910170244</v>
+        <v>0.02816177340687792</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2675235281147735</v>
+        <v>0.08372600560182912</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006225107079566476</v>
+        <v>0.003599310146289911</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000533390480821703</v>
+        <v>0.001549366338511351</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001010398324008751</v>
+        <v>0.001711375131088132</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007301884661823009</v>
+        <v>0.0008552087421834791</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06005851523184767</v>
+        <v>0.01993383989446332</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2887202436645246</v>
+        <v>0.1678146996150156</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5172267666263739</v>
+        <v>0.2893544635940996</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02495016448756696</v>
+        <v>0.05999425094365218</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02309524801385997</v>
+        <v>0.03936199103845423</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03178676334590785</v>
+        <v>0.04136876999728336</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08545106589050255</v>
+        <v>0.02924395223261519</v>
       </c>
       <c r="H5" t="n">
-        <v>0.161871708671456</v>
+        <v>0.1045230212368534</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78.22914956383057</v>
+        <v>61.85794901160716</v>
       </c>
       <c r="C6" t="n">
-        <v>99.12539305293008</v>
+        <v>57.14315599064462</v>
       </c>
       <c r="D6" t="n">
-        <v>47.60278561250001</v>
+        <v>111.0482110259288</v>
       </c>
       <c r="E6" t="n">
-        <v>39.81877799760491</v>
+        <v>136.2554744538268</v>
       </c>
       <c r="F6" t="n">
-        <v>403.4226051522059</v>
+        <v>2485.463275726586</v>
       </c>
       <c r="G6" t="n">
-        <v>800.2835124508069</v>
+        <v>408.8521635964034</v>
       </c>
       <c r="H6" t="n">
-        <v>244.7470373049797</v>
+        <v>543.4367049674995</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.288516192999566</v>
+        <v>0.2178155432655632</v>
       </c>
       <c r="C7" t="n">
-        <v>1.51852118670156</v>
+        <v>0.2378104568929607</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2461746283428053</v>
+        <v>2.836162563881784</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2729978122124218</v>
+        <v>1.581171636139596</v>
       </c>
       <c r="F7" t="n">
-        <v>0.723428331700777</v>
+        <v>1.516786292643988</v>
       </c>
       <c r="G7" t="n">
-        <v>13.50118091100442</v>
+        <v>2.837468188029031</v>
       </c>
       <c r="H7" t="n">
-        <v>2.925136510493591</v>
+        <v>1.537869113475487</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.36134734460813</v>
+        <v>-30.1281079622082</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.91128656566816</v>
+        <v>-12.88123389761604</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.29049836941944</v>
+        <v>-31.7620784674796</v>
       </c>
       <c r="E8" t="n">
-        <v>-41.2175407556248</v>
+        <v>-36.81945547301077</v>
       </c>
       <c r="F8" t="n">
-        <v>-85.66633839370634</v>
+        <v>-74.44549673694668</v>
       </c>
       <c r="G8" t="n">
-        <v>-64.87471907814681</v>
+        <v>-89.83414468697156</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.38695508452895</v>
+        <v>-45.97841953737214</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-17.96689818993569</v>
+        <v>-29.93088338487199</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.32776762721205</v>
+        <v>-13.08947442838798</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.70697943096333</v>
+        <v>-31.97031899825154</v>
       </c>
       <c r="E9" t="n">
-        <v>-41.63402181716869</v>
+        <v>-37.02769600378272</v>
       </c>
       <c r="F9" t="n">
-        <v>-84.53643967878327</v>
+        <v>-73.96059008715868</v>
       </c>
       <c r="G9" t="n">
-        <v>-63.59660441891629</v>
+        <v>-89.26919532951001</v>
       </c>
       <c r="H9" t="n">
-        <v>-42.12811852716322</v>
+        <v>-45.87469303866049</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.08235292338944777</v>
+        <v>0.9246396860211746</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2611948815356866</v>
+        <v>0.9408269619817829</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.284072555558113</v>
+        <v>0.7232347780107389</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.215364274057012</v>
+        <v>0.7585915643276081</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.549995122221021</v>
+        <v>-0.3435233884103925</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.58090778104342</v>
+        <v>-1.678459460887902</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.328981256300783</v>
+        <v>0.2208850235071684</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1544578201938022</v>
+        <v>0.04965970633732172</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2729912614067463</v>
+        <v>0.07422540258859167</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05814086353605746</v>
+        <v>0.01244009825011944</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05969956003694721</v>
+        <v>0.009545244515129149</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0489459770981144</v>
+        <v>0.02157138974486436</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06481396601247276</v>
+        <v>0.01757359421346807</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1098415747140234</v>
+        <v>0.0308359059415824</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04627624903857733</v>
+        <v>0.003222047616768604</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1772694098040093</v>
+        <v>0.008317167853573096</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004032124201685956</v>
+        <v>0.0002111916023170535</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004250655760620405</v>
+        <v>0.000142216542197701</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002989033752704068</v>
+        <v>0.0009115714878583855</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004410995432717755</v>
+        <v>0.0004847456269388653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03987141133171913</v>
+        <v>0.002214823454942284</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2151191507945709</v>
+        <v>0.05676308322112712</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4210337395079037</v>
+        <v>0.09119850795694574</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06349900945436832</v>
+        <v>0.01453243277352603</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06519705331240366</v>
+        <v>0.01192545773535343</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05467205641554072</v>
+        <v>0.0301922421800433</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06641532528504061</v>
+        <v>0.02201693954524255</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1476560557949713</v>
+        <v>0.03777144390203969</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86.11241211214697</v>
+        <v>49.62827642155693</v>
       </c>
       <c r="C6" t="n">
-        <v>47.94508226345389</v>
+        <v>48.3878194938052</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4815413455485</v>
+        <v>25.62913236689382</v>
       </c>
       <c r="E6" t="n">
-        <v>168.5574058350518</v>
+        <v>29.09193559752254</v>
       </c>
       <c r="F6" t="n">
-        <v>3333.28431650717</v>
+        <v>431.8434343986668</v>
       </c>
       <c r="G6" t="n">
-        <v>892.9394854161966</v>
+        <v>201.7816920609537</v>
       </c>
       <c r="H6" t="n">
-        <v>779.3867072465946</v>
+        <v>131.0603817232331</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.717198502687677</v>
+        <v>0.02586352752538564</v>
       </c>
       <c r="C7" t="n">
-        <v>1.007894102647025</v>
+        <v>0.02457392890296629</v>
       </c>
       <c r="D7" t="n">
-        <v>3.179088507217229</v>
+        <v>0.08417740071840028</v>
       </c>
       <c r="E7" t="n">
-        <v>4.338169482499077</v>
+        <v>0.07352208228125598</v>
       </c>
       <c r="F7" t="n">
-        <v>2.137181720586399</v>
+        <v>0.8093902331292374</v>
       </c>
       <c r="G7" t="n">
-        <v>8.157720062231856</v>
+        <v>1.609754320410456</v>
       </c>
       <c r="H7" t="n">
-        <v>3.256208729644877</v>
+        <v>0.4378802488279502</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.65813786313673</v>
+        <v>-47.63964394129549</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.380507685943545</v>
+        <v>-24.73660090588266</v>
       </c>
       <c r="D8" t="n">
-        <v>-27.08077166818758</v>
+        <v>-46.77646861207437</v>
       </c>
       <c r="E8" t="n">
-        <v>-26.76409206799047</v>
+        <v>-49.14895830114065</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.56646634468898</v>
+        <v>-80.00408645735662</v>
       </c>
       <c r="G8" t="n">
-        <v>-69.93116850605982</v>
+        <v>-95.21452170699213</v>
       </c>
       <c r="H8" t="n">
-        <v>-36.56352402266785</v>
+        <v>-57.25337998745699</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.06646413112808</v>
+        <v>-47.24519478662305</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.00522927825938</v>
+        <v>-25.15308196742656</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.70549326050342</v>
+        <v>-47.19294967361827</v>
       </c>
       <c r="E9" t="n">
-        <v>-27.3888136603063</v>
+        <v>-49.56543936268454</v>
       </c>
       <c r="F9" t="n">
-        <v>-67.87161827230436</v>
+        <v>-79.03427315778062</v>
       </c>
       <c r="G9" t="n">
-        <v>-68.01399651721404</v>
+        <v>-94.08462299206906</v>
       </c>
       <c r="H9" t="n">
-        <v>-36.17526918661926</v>
+        <v>-57.04592699003368</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06765441584622733</v>
+        <v>0.8598010413547705</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1128701718724501</v>
+        <v>0.8264294873892869</v>
       </c>
       <c r="D2" t="n">
-        <v>-44.10645481891156</v>
+        <v>0.3228055113827804</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2554398248829635</v>
+        <v>0.5439466012754477</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2774541327016584</v>
+        <v>0.3045733874425821</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.397894042920501</v>
+        <v>0.3975164558633356</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.680409762573817</v>
+        <v>0.5425120807847005</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1510569370533039</v>
+        <v>0.05523592590894563</v>
       </c>
       <c r="C3" t="n">
-        <v>0.269606360141496</v>
+        <v>0.1298277859773135</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1831678970184684</v>
+        <v>0.02064810740359931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02474739014253439</v>
+        <v>0.01489188822970997</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02435930629775725</v>
+        <v>0.01606321142005481</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02299334282091663</v>
+        <v>0.009148476478376667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1126552055790794</v>
+        <v>0.04096923256966665</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03986265062896995</v>
+        <v>0.005994238833761062</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1564213758274229</v>
+        <v>0.02439650111203678</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03441944186331814</v>
+        <v>0.0005167476899857656</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007395943324633418</v>
+        <v>0.0002686664086259708</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001075594018784916</v>
+        <v>0.0004718422301939428</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007788212571642105</v>
+        <v>0.0001090370295266902</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03888291298802057</v>
+        <v>0.005292838884021702</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1996563313019899</v>
+        <v>0.07742246982472893</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3955014232938016</v>
+        <v>0.1561937934491534</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1855247742575588</v>
+        <v>0.02273208503384073</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02719548367768703</v>
+        <v>0.0163910465994692</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03279625007199628</v>
+        <v>0.02172192970695612</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02790736922685853</v>
+        <v>0.01044207975102135</v>
       </c>
       <c r="H5" t="n">
-        <v>0.144763605304982</v>
+        <v>0.05081723406086162</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98.30320084919066</v>
+        <v>33.23185986207807</v>
       </c>
       <c r="C6" t="n">
-        <v>54.51706485233812</v>
+        <v>45.23279648528143</v>
       </c>
       <c r="D6" t="n">
-        <v>364.3896855720177</v>
+        <v>36.31285504420452</v>
       </c>
       <c r="E6" t="n">
-        <v>52.86303005040527</v>
+        <v>43.80261827655498</v>
       </c>
       <c r="F6" t="n">
-        <v>633.9186529699905</v>
+        <v>833.9641185755299</v>
       </c>
       <c r="G6" t="n">
-        <v>162.2355465186614</v>
+        <v>124.6927922407326</v>
       </c>
       <c r="H6" t="n">
-        <v>227.7045301354339</v>
+        <v>186.2061734140636</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3091075306864108</v>
+        <v>0.04775565477720159</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8897120292818621</v>
+        <v>0.07064870456163969</v>
       </c>
       <c r="D7" t="n">
-        <v>27.11506010995559</v>
+        <v>0.205020069968156</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7572993269952268</v>
+        <v>0.1385040861034039</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7709783112472941</v>
+        <v>0.2104582733283612</v>
       </c>
       <c r="G7" t="n">
-        <v>1.442826775512331</v>
+        <v>0.182321389161668</v>
       </c>
       <c r="H7" t="n">
-        <v>5.214164013946451</v>
+        <v>0.1424513629834051</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-23.00083921145571</v>
+        <v>-40.05260818868243</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.131210716729584</v>
+        <v>-16.27989332407796</v>
       </c>
       <c r="D8" t="n">
-        <v>-14.21480222283694</v>
+        <v>-39.40773497812001</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.25645232873681</v>
+        <v>-43.33224038745274</v>
       </c>
       <c r="F8" t="n">
-        <v>-82.85346852723019</v>
+        <v>-85.90639063582893</v>
       </c>
       <c r="G8" t="n">
-        <v>-94.20820586101007</v>
+        <v>-112.6096991689831</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.77749647799988</v>
+        <v>-56.26476111385752</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.40916547944705</v>
+        <v>-39.46093445667378</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.755932309045418</v>
+        <v>-16.9046149163938</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.83952381515277</v>
+        <v>-40.03245657043585</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.88117392105265</v>
+        <v>-43.95696197976858</v>
       </c>
       <c r="F9" t="n">
-        <v>-81.15862045484558</v>
+        <v>-84.45167068646492</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.29103387216429</v>
+        <v>-110.9148510965985</v>
       </c>
       <c r="H9" t="n">
-        <v>-42.38924164195129</v>
+        <v>-55.95358161772256</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2335993026237932</v>
+        <v>0.7394060961973371</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.5290231103151299</v>
+        <v>0.4144709073449666</v>
       </c>
       <c r="D2" t="n">
-        <v>-11.39188456335302</v>
+        <v>-3.524297293112767</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.465382854393294</v>
+        <v>-0.9466887115055269</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.956289008524867</v>
+        <v>-0.3111702299276902</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.375084784861915</v>
+        <v>-1.425316985999446</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.91401083647074</v>
+        <v>-0.8422660361671875</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1371205589208931</v>
+        <v>0.07506320890186741</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3054874404833713</v>
+        <v>0.2205623939938714</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09314302752381215</v>
+        <v>0.0532990537379114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02963463919130589</v>
+        <v>0.02646022691646854</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05195667172321858</v>
+        <v>0.01956691099138066</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02549988844523405</v>
+        <v>0.01768338265804934</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1071403710479725</v>
+        <v>0.06877252953325813</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03276763869594077</v>
+        <v>0.01114175250023135</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2149144658850919</v>
+        <v>0.08230004593076669</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009455891668224241</v>
+        <v>0.003452361491893905</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001452385968902619</v>
+        <v>0.001146817162848943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00333112609307881</v>
+        <v>0.0008896200897142198</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007714129502423021</v>
+        <v>0.0004389320876688019</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04378215354358009</v>
+        <v>0.01656158821052065</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1810183380101054</v>
+        <v>0.1055545001420183</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4635886817914042</v>
+        <v>0.2868798458079039</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09724140922582437</v>
+        <v>0.05875679953753357</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03811018195840343</v>
+        <v>0.03386468902631386</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05771590849218965</v>
+        <v>0.02982649978985499</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02777432177825954</v>
+        <v>0.02095070613771292</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1442414735426978</v>
+        <v>0.08930550674022292</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>91.80024955120913</v>
+        <v>46.86897250989751</v>
       </c>
       <c r="C6" t="n">
-        <v>62.24422658038182</v>
+        <v>72.26040622100717</v>
       </c>
       <c r="D6" t="n">
-        <v>167.961944138628</v>
+        <v>87.10102801527523</v>
       </c>
       <c r="E6" t="n">
-        <v>105.1771770970309</v>
+        <v>87.02923797625945</v>
       </c>
       <c r="F6" t="n">
-        <v>3493.744197000073</v>
+        <v>166.7390792138425</v>
       </c>
       <c r="G6" t="n">
-        <v>286.2741150805386</v>
+        <v>131.3889818871309</v>
       </c>
       <c r="H6" t="n">
-        <v>701.2003182413104</v>
+        <v>98.56461763723546</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2543575563000206</v>
+        <v>0.08747739789096082</v>
       </c>
       <c r="C7" t="n">
-        <v>1.221294118428206</v>
+        <v>0.2347687599480467</v>
       </c>
       <c r="D7" t="n">
-        <v>7.45136898634733</v>
+        <v>2.722411681956312</v>
       </c>
       <c r="E7" t="n">
-        <v>1.48426305299244</v>
+        <v>1.172618770931305</v>
       </c>
       <c r="F7" t="n">
-        <v>2.381436981645231</v>
+        <v>0.7909476060822141</v>
       </c>
       <c r="G7" t="n">
-        <v>1.429130849047489</v>
+        <v>1.458804696522404</v>
       </c>
       <c r="H7" t="n">
-        <v>2.370308590793453</v>
+        <v>1.077838152221874</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-24.76482488175663</v>
+        <v>-34.47350166770975</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.2250909786219</v>
+        <v>-8.984301679258552</v>
       </c>
       <c r="D8" t="n">
-        <v>-21.96670364874051</v>
+        <v>-28.01218075014929</v>
       </c>
       <c r="E8" t="n">
-        <v>-33.20728547459781</v>
+        <v>-34.62458914923864</v>
       </c>
       <c r="F8" t="n">
-        <v>-68.15778325884912</v>
+        <v>-78.29659262232886</v>
       </c>
       <c r="G8" t="n">
-        <v>-94.34201414101415</v>
+        <v>-94.50515611043964</v>
       </c>
       <c r="H8" t="n">
-        <v>-40.94395039726336</v>
+        <v>-46.48272032985412</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-24.17315114974798</v>
+        <v>-33.8818279357011</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.849812570937734</v>
+        <v>-9.609023271574387</v>
       </c>
       <c r="D9" t="n">
-        <v>-22.59142524105635</v>
+        <v>-28.63690234246513</v>
       </c>
       <c r="E9" t="n">
-        <v>-33.83200706691365</v>
+        <v>-35.24931074155448</v>
       </c>
       <c r="F9" t="n">
-        <v>-66.46293518646451</v>
+        <v>-76.84187267296485</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.42484215216837</v>
+        <v>-92.81030803805503</v>
       </c>
       <c r="H9" t="n">
-        <v>-40.55569556121476</v>
+        <v>-46.17154083371917</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5138271356027622</v>
+        <v>0.3745116173092011</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8160710115834942</v>
+        <v>-0.05307034147357292</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9191158532285701</v>
+        <v>-3.593142869552335</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.319074900464885</v>
+        <v>-1.212836676857659</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1227574786645215</v>
+        <v>-2.674096398956276</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.433744581814734</v>
+        <v>-8.96119841787935</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8131793340049874</v>
+        <v>-2.686638847901666</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1627555490793596</v>
+        <v>0.1236036039573822</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3938288669250914</v>
+        <v>0.2751620559091585</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03396110384090924</v>
+        <v>0.05196273179777992</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02787619956517612</v>
+        <v>0.03082861211897715</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02218259399273563</v>
+        <v>0.04357326612802866</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02157942154108264</v>
+        <v>0.03644501053908024</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1103639558240591</v>
+        <v>0.09359588007506776</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06472402856281929</v>
+        <v>0.02674290016004456</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2552609759988682</v>
+        <v>0.1480161080956977</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001464422260724389</v>
+        <v>0.003504895576545906</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001366194236431612</v>
+        <v>0.001303608052280411</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007386228474416795</v>
+        <v>0.002492849435910722</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007904652920013855</v>
+        <v>0.001802770377019884</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05405745153304776</v>
+        <v>0.03064385528291654</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2544091754690056</v>
+        <v>0.1635325660535068</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5052335855808362</v>
+        <v>0.3847286161643006</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03826777052199917</v>
+        <v>0.05920215854633939</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03696206482911382</v>
+        <v>0.0361055127685567</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02717761666227706</v>
+        <v>0.04992844315528697</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02811521459995256</v>
+        <v>0.04245904352455298</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1483609046105307</v>
+        <v>0.1226593900354239</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53.53950832982124</v>
+        <v>61.25784289138527</v>
       </c>
       <c r="C6" t="n">
-        <v>105.1190193297718</v>
+        <v>78.16372995605754</v>
       </c>
       <c r="D6" t="n">
-        <v>80.65500296057162</v>
+        <v>101.892135361467</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>109.3282339334233</v>
       </c>
       <c r="F6" t="n">
-        <v>680.6986970648953</v>
+        <v>2533.340362719523</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>660.6882242250205</v>
       </c>
       <c r="H6" t="n">
-        <v>186.6687046141767</v>
+        <v>590.7784215144794</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.002909921349604</v>
+        <v>0.2068665449192709</v>
       </c>
       <c r="C7" t="n">
-        <v>1.451007973348512</v>
+        <v>0.8400647562181207</v>
       </c>
       <c r="D7" t="n">
-        <v>1.157519703102156</v>
+        <v>2.761792575538565</v>
       </c>
       <c r="E7" t="n">
-        <v>1.397357612209936</v>
+        <v>1.330527057387788</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2656897923938528</v>
+        <v>2.208947828584041</v>
       </c>
       <c r="G7" t="n">
-        <v>1.465353400497643</v>
+        <v>5.980242929255438</v>
       </c>
       <c r="H7" t="n">
-        <v>1.123306400483617</v>
+        <v>2.221406948650538</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-16.63860485928564</v>
+        <v>-30.5933762990192</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1928129313212779</v>
+        <v>-9.462605035936335</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.15776685344548</v>
+        <v>-31.92156730990587</v>
       </c>
       <c r="E8" t="n">
-        <v>-31.57435800616668</v>
+        <v>-37.85571660438105</v>
       </c>
       <c r="F8" t="n">
-        <v>-85.73940059354416</v>
+        <v>-69.93194645206646</v>
       </c>
       <c r="G8" t="n">
-        <v>-92.00044332131378</v>
+        <v>-80.13959908613695</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.88389776084617</v>
+        <v>-43.31746846457431</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-15.84970654994076</v>
+        <v>-30.39615172168298</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.025775054409058</v>
+        <v>-9.67084556670828</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.99072897653326</v>
+        <v>-32.12980784067781</v>
       </c>
       <c r="E9" t="n">
-        <v>-32.40732012925446</v>
+        <v>-38.063957135153</v>
       </c>
       <c r="F9" t="n">
-        <v>-83.47960316369802</v>
+        <v>-69.44703980227845</v>
       </c>
       <c r="G9" t="n">
-        <v>-89.44421400285275</v>
+        <v>-79.57464972867541</v>
       </c>
       <c r="H9" t="n">
-        <v>-42.36622464611472</v>
+        <v>-43.21374196586265</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global_ind/metrics_summary.xlsx
+++ b/results/cross_validation/global_ind/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7824658892906128</v>
+        <v>-0.9934417619397524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5094093513821161</v>
+        <v>-0.7816361454702143</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1585806900532691</v>
+        <v>-0.9841137905698507</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.426336607928623</v>
+        <v>-0.06768132562063256</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.10424892552914</v>
+        <v>-0.4659801376829533</v>
       </c>
       <c r="G2" t="n">
-        <v>-26.85397935651841</v>
+        <v>-2.425476311799479</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.875211723226119</v>
+        <v>-0.9530549121804804</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08879919021515653</v>
+        <v>0.2324725703891376</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1934150966512781</v>
+        <v>0.3659371787024921</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02048625967132823</v>
+        <v>0.03200775631949011</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04007148459297521</v>
+        <v>0.02028611876830659</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09075855073308403</v>
+        <v>0.0294693958680851</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06381530104050372</v>
+        <v>0.02160590778713678</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08289098048405429</v>
+        <v>0.116963154639108</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009300721108646102</v>
+        <v>0.1084437618608304</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06895581008857561</v>
+        <v>0.2948699301127666</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008840796924818882</v>
+        <v>0.0017174217156472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002018495101166572</v>
+        <v>0.0005447410940482207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009569637037269296</v>
+        <v>0.0009963718364054811</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005040992735966898</v>
+        <v>0.0006329677914194211</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01596162262735106</v>
+        <v>0.06786753240185289</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09644024631162086</v>
+        <v>0.3293080045501938</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2625943832007372</v>
+        <v>0.5430192723216798</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02973347763854555</v>
+        <v>0.04144178707110976</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04492766520938488</v>
+        <v>0.023339689244894</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09782452165622532</v>
+        <v>0.03156535817008072</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07099994884481887</v>
+        <v>0.02515885115460205</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1004200404768888</v>
+        <v>0.1656388270854267</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.73390371812778</v>
+        <v>77.23777296428051</v>
       </c>
       <c r="C6" t="n">
-        <v>42.67404350982396</v>
+        <v>135.0081218697641</v>
       </c>
       <c r="D6" t="n">
-        <v>40.76864506170178</v>
+        <v>40.08571682764376</v>
       </c>
       <c r="E6" t="n">
-        <v>91.95205648780433</v>
+        <v>2337.692786792215</v>
       </c>
       <c r="F6" t="n">
-        <v>6045.828601163543</v>
+        <v>1397.580439909465</v>
       </c>
       <c r="G6" t="n">
-        <v>981.4754545381314</v>
+        <v>342.0048059267148</v>
       </c>
       <c r="H6" t="n">
-        <v>1211.238784079855</v>
+        <v>721.6016073816804</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07227073798886843</v>
+        <v>1.348886323769014</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1959462616473681</v>
+        <v>1.482799589440002</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6973861256014362</v>
+        <v>1.193872664743816</v>
       </c>
       <c r="E7" t="n">
-        <v>2.059627857898807</v>
+        <v>0.6423714329040471</v>
       </c>
       <c r="F7" t="n">
-        <v>8.476946847169662</v>
+        <v>0.8819830031807399</v>
       </c>
       <c r="G7" t="n">
-        <v>16.7204450037414</v>
+        <v>2.057171941987675</v>
       </c>
       <c r="H7" t="n">
-        <v>4.703770472341257</v>
+        <v>1.267847492670882</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-40.0989700893831</v>
+        <v>-17.99371207817067</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.0457364782935</v>
+        <v>-5.327325608475032</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.18578009714098</v>
+        <v>-36.20158669189473</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.23241826784894</v>
+        <v>-43.09119959781108</v>
       </c>
       <c r="F8" t="n">
-        <v>-53.78992001651945</v>
+        <v>-80.93668048390599</v>
       </c>
       <c r="G8" t="n">
-        <v>-66.77197918335133</v>
+        <v>-93.74618325412955</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.68746735542288</v>
+        <v>-46.21611461906451</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-39.90174551204688</v>
+        <v>-17.79648750083446</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.25397700906544</v>
+        <v>-5.535566139246978</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.39402062791292</v>
+        <v>-36.40982722266667</v>
       </c>
       <c r="E9" t="n">
-        <v>-35.44065879862089</v>
+        <v>-43.29944012858302</v>
       </c>
       <c r="F9" t="n">
-        <v>-53.30501336673144</v>
+        <v>-80.45177383411799</v>
       </c>
       <c r="G9" t="n">
-        <v>-66.20702982588979</v>
+        <v>-93.181233896668</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.58374085671122</v>
+        <v>-46.11238812035285</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9291635146888031</v>
+        <v>-0.000881496792722869</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9241812184151683</v>
+        <v>-0.3473864275306975</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7640394692998611</v>
+        <v>-2.469915508747921</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6175956270268713</v>
+        <v>-7.906121058046635</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2872136294863503</v>
+        <v>-0.2919117699708647</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9743439915382948</v>
+        <v>-7.947750848603697</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3289037014010099</v>
+        <v>-3.160661184948756</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04403556628886632</v>
+        <v>0.1782226029044912</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09242833585278583</v>
+        <v>0.301158041755801</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0115618576089384</v>
+        <v>0.04549747323092746</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01303824750660437</v>
+        <v>0.06297476660063452</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02105628095420116</v>
+        <v>0.02742315134317915</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01413858807315966</v>
+        <v>0.03830601845227426</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03270981271409262</v>
+        <v>0.1089303423812179</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003028630278017903</v>
+        <v>0.05444821953739219</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0106568388917315</v>
+        <v>0.2229993720833552</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001800547128138745</v>
+        <v>0.003003511328084227</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002252789033408987</v>
+        <v>0.004543987060995072</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008733656991344032</v>
+        <v>0.0008780640812461766</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003573153261964814</v>
+        <v>0.001653387026295534</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002553580635205843</v>
+        <v>0.04792109018622806</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05503299263185588</v>
+        <v>0.2333414226779982</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1032319664238335</v>
+        <v>0.4722280932805196</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01341844673626104</v>
+        <v>0.05480430026999913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01500929389881145</v>
+        <v>0.06740910221175678</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02955276127766072</v>
+        <v>0.02963214607898281</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01890278620194603</v>
+        <v>0.04066186206134113</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03919137452839477</v>
+        <v>0.149679487763433</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.81292239343433</v>
+        <v>112.6599714508167</v>
       </c>
       <c r="C6" t="n">
-        <v>47.39377760677964</v>
+        <v>479.5447843247415</v>
       </c>
       <c r="D6" t="n">
-        <v>23.02651505059477</v>
+        <v>110.7994459498473</v>
       </c>
       <c r="E6" t="n">
-        <v>38.34320171762113</v>
+        <v>6000.006787572638</v>
       </c>
       <c r="F6" t="n">
-        <v>396.7409059402107</v>
+        <v>1260.840153197889</v>
       </c>
       <c r="G6" t="n">
-        <v>161.4657176384032</v>
+        <v>503.1460277330658</v>
       </c>
       <c r="H6" t="n">
-        <v>119.2971733911739</v>
+        <v>1411.166195038167</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02487098678797161</v>
+        <v>0.6827564054279829</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03170542169966156</v>
+        <v>1.126630977435116</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0724141975090114</v>
+        <v>2.09215422110807</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1163790071242773</v>
+        <v>5.356034216713375</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7765508896705985</v>
+        <v>0.7823763516962636</v>
       </c>
       <c r="G7" t="n">
-        <v>1.188106636379652</v>
+        <v>5.376965250999032</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3683378565285287</v>
+        <v>2.569486237229973</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-46.19680333614539</v>
+        <v>-14.19454616258027</v>
       </c>
       <c r="C8" t="n">
-        <v>-21.24932066074852</v>
+        <v>2.996482060225858</v>
       </c>
       <c r="D8" t="n">
-        <v>-45.73349875910093</v>
+        <v>-22.84783939231996</v>
       </c>
       <c r="E8" t="n">
-        <v>-44.38902811793378</v>
+        <v>-20.36370267035773</v>
       </c>
       <c r="F8" t="n">
-        <v>-78.51787428583665</v>
+        <v>-72.45349177822155</v>
       </c>
       <c r="G8" t="n">
-        <v>-97.17959469191756</v>
+        <v>-71.26408157416381</v>
       </c>
       <c r="H8" t="n">
-        <v>-55.54435330861381</v>
+        <v>-33.02119658623624</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-45.60512960413674</v>
+        <v>-13.01119869856295</v>
       </c>
       <c r="C9" t="n">
-        <v>-21.87404225306436</v>
+        <v>1.747038875594189</v>
       </c>
       <c r="D9" t="n">
-        <v>-46.35822035141677</v>
+        <v>-24.09728257695163</v>
       </c>
       <c r="E9" t="n">
-        <v>-45.01374971024961</v>
+        <v>-21.6131458549894</v>
       </c>
       <c r="F9" t="n">
-        <v>-77.06315433647265</v>
+        <v>-69.54405187949354</v>
       </c>
       <c r="G9" t="n">
-        <v>-95.48474661953294</v>
+        <v>-67.87438542939459</v>
       </c>
       <c r="H9" t="n">
-        <v>-55.23317381247885</v>
+        <v>-32.39883759396632</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9320547132127137</v>
+        <v>0.01111242474347385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9352803973170256</v>
+        <v>-0.3298714171291417</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6114635403394146</v>
+        <v>-1.542544812048841</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6682832368174884</v>
+        <v>-4.251695234682621</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1681262850760565</v>
+        <v>-0.652442930113329</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.013004705580842</v>
+        <v>-8.047363370086648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3276584828382907</v>
+        <v>-2.468800889886185</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0427028383252445</v>
+        <v>0.1682975313815171</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08321360916164439</v>
+        <v>0.2985340495047836</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01671978073648907</v>
+        <v>0.03997070115342687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01006889473483804</v>
+        <v>0.04594062187995038</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01995265683073481</v>
+        <v>0.03175947745634123</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01445018684761118</v>
+        <v>0.03694022085761374</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03118466110609366</v>
+        <v>0.1035737670389388</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002905016417860834</v>
+        <v>0.05379574701690924</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009096774763620237</v>
+        <v>0.2201005479288485</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002964810277987099</v>
+        <v>0.002200791957584593</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001954182376329676</v>
+        <v>0.002679464498534593</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007925657453221845</v>
+        <v>0.001123103618194006</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003643121138425585</v>
+        <v>0.001671793668753867</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002275094717679582</v>
+        <v>0.0469285747814708</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05389820421740259</v>
+        <v>0.2319391019576243</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09537701381161101</v>
+        <v>0.4691487481906442</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01721862444560279</v>
+        <v>0.04691259913482297</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01397920733206885</v>
+        <v>0.05176354410716671</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02815254420691289</v>
+        <v>0.03351273814826246</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01908696188089028</v>
+        <v>0.04088757352489711</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0379520926490814</v>
+        <v>0.1456940508439029</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.14323684719844</v>
+        <v>80.47315921821622</v>
       </c>
       <c r="C6" t="n">
-        <v>47.46600825357591</v>
+        <v>501.122637823031</v>
       </c>
       <c r="D6" t="n">
-        <v>33.07962230437267</v>
+        <v>95.96760807404576</v>
       </c>
       <c r="E6" t="n">
-        <v>27.86820301829407</v>
+        <v>4924.549110131893</v>
       </c>
       <c r="F6" t="n">
-        <v>453.0527868880115</v>
+        <v>1283.593105571611</v>
       </c>
       <c r="G6" t="n">
-        <v>155.0773572626175</v>
+        <v>528.4164807941836</v>
       </c>
       <c r="H6" t="n">
-        <v>126.7812024290117</v>
+        <v>1235.687016935497</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02441709752868847</v>
+        <v>0.3368232954887944</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02778362313942648</v>
+        <v>1.111063617377873</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1187684746176347</v>
+        <v>1.533607995969923</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1016518217210966</v>
+        <v>3.159768391107521</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7059853630890851</v>
+        <v>0.9980381031334692</v>
       </c>
       <c r="G7" t="n">
-        <v>1.212312860307885</v>
+        <v>5.435758533188245</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3651532067339693</v>
+        <v>2.095843322710971</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.57184613396323</v>
+        <v>-16.30304780002517</v>
       </c>
       <c r="C8" t="n">
-        <v>-20.19901209917019</v>
+        <v>0.9179751940077114</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.74116397257154</v>
+        <v>-26.71362801605067</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.24221092706547</v>
+        <v>-25.53282991042684</v>
       </c>
       <c r="F8" t="n">
-        <v>-77.6828211550804</v>
+        <v>-71.49991206064492</v>
       </c>
       <c r="G8" t="n">
-        <v>-94.92749482757515</v>
+        <v>-73.12015628526808</v>
       </c>
       <c r="H8" t="n">
-        <v>-53.56075818590433</v>
+        <v>-35.37526647973466</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-43.78294782461835</v>
+        <v>-15.31692491334407</v>
       </c>
       <c r="C9" t="n">
-        <v>-21.03197422225797</v>
+        <v>-0.1232274598520142</v>
       </c>
       <c r="D9" t="n">
-        <v>-41.57412609565932</v>
+        <v>-27.7548306699104</v>
       </c>
       <c r="E9" t="n">
-        <v>-44.07517305015325</v>
+        <v>-26.57403256428657</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.7431945559284</v>
+        <v>-69.07537881170492</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.667697397729</v>
+        <v>-70.29540949796039</v>
       </c>
       <c r="H9" t="n">
-        <v>-53.14585219105771</v>
+        <v>-34.8566339861764</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9323210020234601</v>
+        <v>0.004073885602492</v>
       </c>
       <c r="C2" t="n">
-        <v>0.933706693649946</v>
+        <v>-0.3431920197067935</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6129528269087325</v>
+        <v>-2.483899940642714</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6609585744547751</v>
+        <v>-7.842429172266234</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1821850017510909</v>
+        <v>-0.2697458639717798</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.059791095869473</v>
+        <v>-7.916051407164485</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3163271665693916</v>
+        <v>-3.141874086358252</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04253350997813896</v>
+        <v>0.1786560752842943</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08493335552286792</v>
+        <v>0.3006932411157606</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01668363880929221</v>
+        <v>0.04566096967595724</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01024327948374632</v>
+        <v>0.06270893759263049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0200157576737275</v>
+        <v>0.02719478509008395</v>
       </c>
       <c r="G3" t="n">
-        <v>0.014739106256143</v>
+        <v>0.03817602646535095</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03152477462065265</v>
+        <v>0.1088483392040129</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002893631178299882</v>
+        <v>0.05417864541756783</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009317969381798456</v>
+        <v>0.2223051760517785</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002953445959355486</v>
+        <v>0.003015616060751908</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001997332821801447</v>
+        <v>0.004511490859451187</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008021044890369502</v>
+        <v>0.0008629987444805595</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003727794804104851</v>
+        <v>0.001647529526896722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002313593734610245</v>
+        <v>0.04775357611015444</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05379248254449577</v>
+        <v>0.2327630671252805</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09652962955382381</v>
+        <v>0.4714924984045647</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01718559268502395</v>
+        <v>0.05491462519904791</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0141327025787761</v>
+        <v>0.06716763252825864</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02832144927500975</v>
+        <v>0.0293768402739396</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01930749803600883</v>
+        <v>0.04058977121020421</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03821155911218971</v>
+        <v>0.1493840724568826</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.08126599164056</v>
+        <v>115.0114684310534</v>
       </c>
       <c r="C6" t="n">
-        <v>47.39442395067762</v>
+        <v>483.6415155834754</v>
       </c>
       <c r="D6" t="n">
-        <v>32.89868311823873</v>
+        <v>111.0720578829274</v>
       </c>
       <c r="E6" t="n">
-        <v>28.24198378471847</v>
+        <v>5984.98573396688</v>
       </c>
       <c r="F6" t="n">
-        <v>423.7313008113784</v>
+        <v>1239.270206296147</v>
       </c>
       <c r="G6" t="n">
-        <v>159.8587112382217</v>
+        <v>501.0823676864179</v>
       </c>
       <c r="H6" t="n">
-        <v>122.7010614824793</v>
+        <v>1405.84389164115</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02432924121777188</v>
+        <v>0.3397028861115499</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02841057047227513</v>
+        <v>1.123142458296566</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1183208931445351</v>
+        <v>2.100561826870681</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1038522409610936</v>
+        <v>5.317773590562973</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7144339473353063</v>
+        <v>0.7690557166253408</v>
       </c>
       <c r="G7" t="n">
-        <v>1.240396548794259</v>
+        <v>5.357937385636347</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3716239069875401</v>
+        <v>2.50136231068391</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-44.60718792220676</v>
+        <v>-14.23921599743263</v>
       </c>
       <c r="C8" t="n">
-        <v>-20.05486330907693</v>
+        <v>2.977774954803106</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.76420656919491</v>
+        <v>-22.82370682650939</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.11116602322096</v>
+        <v>-20.40676567552286</v>
       </c>
       <c r="F8" t="n">
-        <v>-77.53926007602348</v>
+        <v>-72.66116786055885</v>
       </c>
       <c r="G8" t="n">
-        <v>-94.62880574030581</v>
+        <v>-71.31021880355689</v>
       </c>
       <c r="H8" t="n">
-        <v>-53.45091494000481</v>
+        <v>-33.07721670146292</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-43.81828961286188</v>
+        <v>-13.05586853341532</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.88782543216471</v>
+        <v>1.728331770171437</v>
       </c>
       <c r="D9" t="n">
-        <v>-41.59716869228269</v>
+        <v>-24.07315001114106</v>
       </c>
       <c r="E9" t="n">
-        <v>-43.94412814630874</v>
+        <v>-21.65620886015453</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.59963347687147</v>
+        <v>-69.75172796183085</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.36900831045966</v>
+        <v>-67.92052265878768</v>
       </c>
       <c r="H9" t="n">
-        <v>-53.03600894515819</v>
+        <v>-32.454857709193</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3413256603975047</v>
+        <v>-1.022429562094536</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4043258234277325</v>
+        <v>-0.7959859498554618</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.71687254946163</v>
+        <v>-0.7563523143676505</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.630004205442799</v>
+        <v>-4.18441326883215</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.522317279100774</v>
+        <v>-0.2934920826157075</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.725451492983289</v>
+        <v>-4.066077136898291</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.641499007193876</v>
+        <v>-1.853125052443966</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1226779314085144</v>
+        <v>0.2298126668703558</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2082971651956806</v>
+        <v>0.3721914199320548</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05045185220581116</v>
+        <v>0.03046874456549402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03011463521642217</v>
+        <v>0.04311133764147269</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03863281217633793</v>
+        <v>0.0234956819689575</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02680369334331373</v>
+        <v>0.01584880526731883</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07949634825768</v>
+        <v>0.1191547760409423</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02816177340687792</v>
+        <v>0.1100207058964544</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08372600560182912</v>
+        <v>0.2972448964194212</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003599310146289911</v>
+        <v>0.001520274502076764</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001549366338511351</v>
+        <v>0.002645136604239171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001711375131088132</v>
+        <v>0.0008791381606088927</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008552087421834791</v>
+        <v>0.0009361219768057316</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01993383989446332</v>
+        <v>0.06887437892660103</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1678146996150156</v>
+        <v>0.3316936928801246</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2893544635940996</v>
+        <v>0.5452017025096503</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05999425094365218</v>
+        <v>0.03899069763516375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03936199103845423</v>
+        <v>0.05143089153649946</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04136876999728336</v>
+        <v>0.02965026409003624</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02924395223261519</v>
+        <v>0.03059611048492491</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1045230212368534</v>
+        <v>0.1712605598560666</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.85794901160716</v>
+        <v>75.09213820739903</v>
       </c>
       <c r="C6" t="n">
-        <v>57.14315599064462</v>
+        <v>134.8806740628361</v>
       </c>
       <c r="D6" t="n">
-        <v>111.0482110259288</v>
+        <v>44.06467056245027</v>
       </c>
       <c r="E6" t="n">
-        <v>136.2554744538268</v>
+        <v>5157.535737371612</v>
       </c>
       <c r="F6" t="n">
-        <v>2485.463275726586</v>
+        <v>490.6504175598679</v>
       </c>
       <c r="G6" t="n">
-        <v>408.8521635964034</v>
+        <v>100.5938661810789</v>
       </c>
       <c r="H6" t="n">
-        <v>543.4367049674995</v>
+        <v>1000.469583990874</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2178155432655632</v>
+        <v>1.368486725511758</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2378104568929607</v>
+        <v>1.494734424900467</v>
       </c>
       <c r="D7" t="n">
-        <v>2.836162563881784</v>
+        <v>1.056939772923498</v>
       </c>
       <c r="E7" t="n">
-        <v>1.581171636139596</v>
+        <v>3.115351152545225</v>
       </c>
       <c r="F7" t="n">
-        <v>1.516786292643988</v>
+        <v>0.778326042994277</v>
       </c>
       <c r="G7" t="n">
-        <v>2.837468188029031</v>
+        <v>3.041956852906503</v>
       </c>
       <c r="H7" t="n">
-        <v>1.537869113475487</v>
+        <v>1.809299161963621</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.1281079622082</v>
+        <v>-17.86378025933325</v>
       </c>
       <c r="C8" t="n">
-        <v>-12.88123389761604</v>
+        <v>-5.279193477276056</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.7620784674796</v>
+        <v>-36.9331862017446</v>
       </c>
       <c r="E8" t="n">
-        <v>-36.81945547301077</v>
+        <v>-33.61019541274185</v>
       </c>
       <c r="F8" t="n">
-        <v>-74.44549673694668</v>
+        <v>-82.43882191990841</v>
       </c>
       <c r="G8" t="n">
-        <v>-89.83414468697156</v>
+        <v>-88.65894204740201</v>
       </c>
       <c r="H8" t="n">
-        <v>-45.97841953737214</v>
+        <v>-44.1306865530677</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-29.93088338487199</v>
+        <v>-17.66655568199703</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.08947442838798</v>
+        <v>-5.487434008048002</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.97031899825154</v>
+        <v>-37.14142673251655</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.02769600378272</v>
+        <v>-33.81843594351379</v>
       </c>
       <c r="F9" t="n">
-        <v>-73.96059008715868</v>
+        <v>-81.9539152701204</v>
       </c>
       <c r="G9" t="n">
-        <v>-89.26919532951001</v>
+        <v>-88.09399268994046</v>
       </c>
       <c r="H9" t="n">
-        <v>-45.87469303866049</v>
+        <v>-44.02696005435604</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9246396860211746</v>
+        <v>-0.1316818125995651</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9408269619817829</v>
+        <v>-0.2854604642427856</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7232347780107389</v>
+        <v>-3.506688245775955</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7585915643276081</v>
+        <v>-7.100585511232493</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3435233884103925</v>
+        <v>-3.566228133492235</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.678459460887902</v>
+        <v>-23.90487395223806</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2208850235071684</v>
+        <v>-6.415919686596848</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04965970633732172</v>
+        <v>0.1737712570199745</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07422540258859167</v>
+        <v>0.294084680453863</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01244009825011944</v>
+        <v>0.05575522971351281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009545244515129149</v>
+        <v>0.05942096560049833</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02157138974486436</v>
+        <v>0.04939909340094995</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01757359421346807</v>
+        <v>0.06669952004172634</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0308359059415824</v>
+        <v>0.1165217910384208</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003222047616768604</v>
+        <v>0.0615637914941451</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008317167853573096</v>
+        <v>0.2127503071924691</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002111916023170535</v>
+        <v>0.003900927605933663</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000142216542197701</v>
+        <v>0.004132995218638746</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009115714878583855</v>
+        <v>0.003103494374763475</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004847456269388653</v>
+        <v>0.004601982797786747</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002214823454942284</v>
+        <v>0.04834224978062281</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05676308322112712</v>
+        <v>0.2481205180837431</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09119850795694574</v>
+        <v>0.4612486392310216</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01453243277352603</v>
+        <v>0.06245740633370604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01192545773535343</v>
+        <v>0.06428837545496656</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0301922421800433</v>
+        <v>0.0557090152018816</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02201693954524255</v>
+        <v>0.06783791563562921</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03777144390203969</v>
+        <v>0.159943644990158</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.62827642155693</v>
+        <v>84.58552780370812</v>
       </c>
       <c r="C6" t="n">
-        <v>48.3878194938052</v>
+        <v>512.0760052714734</v>
       </c>
       <c r="D6" t="n">
-        <v>25.62913236689382</v>
+        <v>127.5123680833419</v>
       </c>
       <c r="E6" t="n">
-        <v>29.09193559752254</v>
+        <v>5816.287181772554</v>
       </c>
       <c r="F6" t="n">
-        <v>431.8434343986668</v>
+        <v>2577.271391327341</v>
       </c>
       <c r="G6" t="n">
-        <v>201.7816920609537</v>
+        <v>821.8229142749483</v>
       </c>
       <c r="H6" t="n">
-        <v>131.0603817232331</v>
+        <v>1656.592564755561</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02586352752538564</v>
+        <v>0.7681983956515424</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02457392890296629</v>
+        <v>1.072126708615128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08417740071840028</v>
+        <v>2.71247424611388</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07352208228125598</v>
+        <v>4.869137500045591</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8093902331292374</v>
+        <v>2.74708177222001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.609754320410456</v>
+        <v>14.95236714725974</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4378802488279502</v>
+        <v>4.520230961650982</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-47.63964394129549</v>
+        <v>-19.08913243516301</v>
       </c>
       <c r="C8" t="n">
-        <v>-24.73660090588266</v>
+        <v>-3.285816405700785</v>
       </c>
       <c r="D8" t="n">
-        <v>-46.77646861207437</v>
+        <v>-27.27924543871507</v>
       </c>
       <c r="E8" t="n">
-        <v>-49.14895830114065</v>
+        <v>-26.93251740196474</v>
       </c>
       <c r="F8" t="n">
-        <v>-80.00408645735662</v>
+        <v>-63.30271901589857</v>
       </c>
       <c r="G8" t="n">
-        <v>-95.21452170699213</v>
+        <v>-63.95648432971009</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.25337998745699</v>
+        <v>-33.97431917119204</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.24519478662305</v>
+        <v>-18.49745870315435</v>
       </c>
       <c r="C9" t="n">
-        <v>-25.15308196742656</v>
+        <v>-3.91053799801662</v>
       </c>
       <c r="D9" t="n">
-        <v>-47.19294967361827</v>
+        <v>-27.90396703103091</v>
       </c>
       <c r="E9" t="n">
-        <v>-49.56543936268454</v>
+        <v>-27.55723899428057</v>
       </c>
       <c r="F9" t="n">
-        <v>-79.03427315778062</v>
+        <v>-61.84799906653457</v>
       </c>
       <c r="G9" t="n">
-        <v>-94.08462299206906</v>
+        <v>-62.26163625732548</v>
       </c>
       <c r="H9" t="n">
-        <v>-57.04592699003368</v>
+        <v>-33.66313967505708</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8598010413547705</v>
+        <v>0.01806866614184222</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8264294873892869</v>
+        <v>-0.1367955767168594</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3228055113827804</v>
+        <v>-42.08227530413816</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5439466012754477</v>
+        <v>-0.3715595800641449</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3045733874425821</v>
+        <v>-0.5563494283563883</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3975164558633356</v>
+        <v>-3.166378244546506</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5425120807847005</v>
+        <v>-7.715881577946703</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05523592590894563</v>
+        <v>0.1700669527276107</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1298277859773135</v>
+        <v>0.2875122157722852</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02064810740359931</v>
+        <v>0.1901986703747624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01489188822970997</v>
+        <v>0.02288357865149238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01606321142005481</v>
+        <v>0.02177177974516553</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009148476478376667</v>
+        <v>0.0240098583351987</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04096923256966665</v>
+        <v>0.1194071759344192</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005994238833761062</v>
+        <v>0.05341732563532994</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02439650111203678</v>
+        <v>0.1881455049681504</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005167476899857656</v>
+        <v>0.03729142729539087</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002686664086259708</v>
+        <v>0.0006997826488743282</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004718422301939428</v>
+        <v>0.00105779246127511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001090370295266902</v>
+        <v>0.0007698734411282954</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005292838884021702</v>
+        <v>0.04689695107502482</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07742246982472893</v>
+        <v>0.2311218848039492</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1561937934491534</v>
+        <v>0.4337574264126787</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02273208503384073</v>
+        <v>0.1931098839919668</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0163910465994692</v>
+        <v>0.02645340524156254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02172192970695612</v>
+        <v>0.03252372151638108</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01044207975102135</v>
+        <v>0.0277465933247362</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05081723406086162</v>
+        <v>0.1574521525485457</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.23185986207807</v>
+        <v>95.92130668712528</v>
       </c>
       <c r="C6" t="n">
-        <v>45.23279648528143</v>
+        <v>644.1304258088439</v>
       </c>
       <c r="D6" t="n">
-        <v>36.31285504420452</v>
+        <v>336.5046468388908</v>
       </c>
       <c r="E6" t="n">
-        <v>43.80261827655498</v>
+        <v>1832.96466873756</v>
       </c>
       <c r="F6" t="n">
-        <v>833.9641185755299</v>
+        <v>192.5517314124227</v>
       </c>
       <c r="G6" t="n">
-        <v>124.6927922407326</v>
+        <v>157.2610656394512</v>
       </c>
       <c r="H6" t="n">
-        <v>186.2061734140636</v>
+        <v>543.2223075207156</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04775565477720159</v>
+        <v>0.3334715281021783</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07064870456163969</v>
+        <v>0.9484810529855262</v>
       </c>
       <c r="D7" t="n">
-        <v>0.205020069968156</v>
+        <v>25.90457318069645</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1385040861034039</v>
+        <v>0.8269154437469111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2104582733283612</v>
+        <v>0.9382905664596183</v>
       </c>
       <c r="G7" t="n">
-        <v>0.182321389161668</v>
+        <v>2.503904769545483</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1424513629834051</v>
+        <v>5.242606090256027</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-40.05260818868243</v>
+        <v>-20.36658121984855</v>
       </c>
       <c r="C8" t="n">
-        <v>-16.27989332407796</v>
+        <v>-4.023237917461465</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.40773497812001</v>
+        <v>-13.73395085982225</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.33224038745274</v>
+        <v>-37.58844463646746</v>
       </c>
       <c r="F8" t="n">
-        <v>-85.90639063582893</v>
+        <v>-76.21885351384641</v>
       </c>
       <c r="G8" t="n">
-        <v>-112.6096991689831</v>
+        <v>-87.2006974443549</v>
       </c>
       <c r="H8" t="n">
-        <v>-56.26476111385752</v>
+        <v>-39.85529426530017</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-39.46093445667378</v>
+        <v>-19.77490748783989</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.9046149163938</v>
+        <v>-4.6479595097773</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.03245657043585</v>
+        <v>-14.35867245213809</v>
       </c>
       <c r="E9" t="n">
-        <v>-43.95696197976858</v>
+        <v>-38.2131662287833</v>
       </c>
       <c r="F9" t="n">
-        <v>-84.45167068646492</v>
+        <v>-74.76413356448241</v>
       </c>
       <c r="G9" t="n">
-        <v>-110.9148510965985</v>
+        <v>-85.50584937197029</v>
       </c>
       <c r="H9" t="n">
-        <v>-55.95358161772256</v>
+        <v>-39.54411476916521</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7394060961973371</v>
+        <v>0.1670316426522996</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4144709073449666</v>
+        <v>0.1006410412295492</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.524297293112767</v>
+        <v>-9.48878514470594</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9466887115055269</v>
+        <v>-3.229702378815886</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3111702299276902</v>
+        <v>-3.418727474292292</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.425316985999446</v>
+        <v>-15.4154255764923</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8422660361671875</v>
+        <v>-5.214161315070762</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07506320890186741</v>
+        <v>0.1584177195888447</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2205623939938714</v>
+        <v>0.278222775292895</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0532990537379114</v>
+        <v>0.0905728187691434</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02646022691646854</v>
+        <v>0.0406075190808291</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01956691099138066</v>
+        <v>0.04860977177453168</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01768338265804934</v>
+        <v>0.0526119586584104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06877252953325813</v>
+        <v>0.1115070938607757</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01114175250023135</v>
+        <v>0.04531370010725758</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08230004593076669</v>
+        <v>0.1488485255494986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003452361491893905</v>
+        <v>0.009078948729599877</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001146817162848943</v>
+        <v>0.002158034093173992</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008896200897142198</v>
+        <v>0.003003243696803846</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004389320876688019</v>
+        <v>0.003033282010029105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01656158821052065</v>
+        <v>0.0352392890310605</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1055545001420183</v>
+        <v>0.2128701484644044</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2868798458079039</v>
+        <v>0.3858089236260595</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05875679953753357</v>
+        <v>0.095283517617686</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03386468902631386</v>
+        <v>0.04645464554997693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02982649978985499</v>
+        <v>0.05480185851596501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02095070613771292</v>
+        <v>0.05507523953673833</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08930550674022292</v>
+        <v>0.1417157222184717</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.86897250989751</v>
+        <v>92.94584488145793</v>
       </c>
       <c r="C6" t="n">
-        <v>72.26040622100717</v>
+        <v>782.9569147983855</v>
       </c>
       <c r="D6" t="n">
-        <v>87.10102801527523</v>
+        <v>144.9542881897643</v>
       </c>
       <c r="E6" t="n">
-        <v>87.02923797625945</v>
+        <v>4481.775988682196</v>
       </c>
       <c r="F6" t="n">
-        <v>166.7390792138425</v>
+        <v>2528.195184629992</v>
       </c>
       <c r="G6" t="n">
-        <v>131.3889818871309</v>
+        <v>706.5145059359163</v>
       </c>
       <c r="H6" t="n">
-        <v>98.56461763723546</v>
+        <v>1456.223787852952</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08747739789096082</v>
+        <v>0.2826100972793905</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2347687599480467</v>
+        <v>0.3750016555157842</v>
       </c>
       <c r="D7" t="n">
-        <v>2.722411681956312</v>
+        <v>6.307981615045005</v>
       </c>
       <c r="E7" t="n">
-        <v>1.172618770931305</v>
+        <v>2.542842675019975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7909476060822141</v>
+        <v>2.657441025750901</v>
       </c>
       <c r="G7" t="n">
-        <v>1.458804696522404</v>
+        <v>9.855501940709424</v>
       </c>
       <c r="H7" t="n">
-        <v>1.077838152221874</v>
+        <v>3.670229834886746</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-34.47350166770975</v>
+        <v>-23.84731275433056</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.984301679258552</v>
+        <v>-7.428956583094733</v>
       </c>
       <c r="D8" t="n">
-        <v>-28.01218075014929</v>
+        <v>-24.21078123050139</v>
       </c>
       <c r="E8" t="n">
-        <v>-34.62458914923864</v>
+        <v>-32.83134568259537</v>
       </c>
       <c r="F8" t="n">
-        <v>-78.29659262232886</v>
+        <v>-65.69674810588023</v>
       </c>
       <c r="G8" t="n">
-        <v>-94.50515611043964</v>
+        <v>-71.3754309625357</v>
       </c>
       <c r="H8" t="n">
-        <v>-46.48272032985412</v>
+        <v>-37.56509588648967</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-33.8818279357011</v>
+        <v>-23.45286359965812</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.609023271574387</v>
+        <v>-7.845437644638623</v>
       </c>
       <c r="D9" t="n">
-        <v>-28.63690234246513</v>
+        <v>-24.62726229204528</v>
       </c>
       <c r="E9" t="n">
-        <v>-35.24931074155448</v>
+        <v>-33.24782674413926</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.84187267296485</v>
+        <v>-64.72693480630423</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.81030803805503</v>
+        <v>-70.24553224761263</v>
       </c>
       <c r="H9" t="n">
-        <v>-46.17154083371917</v>
+        <v>-37.35764288906635</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3745116173092011</v>
+        <v>-0.508767857020658</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05307034147357292</v>
+        <v>-0.8397068160312384</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.593142869552335</v>
+        <v>-0.6748935485742886</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.212836676857659</v>
+        <v>-2.102037690138895</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.674096398956276</v>
+        <v>0.5057325211362637</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.96119841787935</v>
+        <v>-1.967071214259471</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.686638847901666</v>
+        <v>-0.9311241008147145</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1236036039573822</v>
+        <v>0.1817705233903026</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2751620559091585</v>
+        <v>0.4259759120121767</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05196273179777992</v>
+        <v>0.03516516945451098</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03082861211897715</v>
+        <v>0.03274873246809459</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04357326612802866</v>
+        <v>0.01636071885581005</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03644501053908024</v>
+        <v>0.01906515598921837</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09359588007506776</v>
+        <v>0.1185143686950189</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02674290016004456</v>
+        <v>0.08207737256934654</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1480161080956977</v>
+        <v>0.3044809242618617</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003504895576545906</v>
+        <v>0.001449764910354629</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001303608052280411</v>
+        <v>0.00158268892089389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002492849435910722</v>
+        <v>0.0003359351078039472</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001802770377019884</v>
+        <v>0.000548262589644758</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03064385528291654</v>
+        <v>0.06507915805998425</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1635325660535068</v>
+        <v>0.2864914877781651</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3847286161643006</v>
+        <v>0.5517979016468455</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05920215854633939</v>
+        <v>0.0380757785259163</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0361055127685567</v>
+        <v>0.03978302302356986</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04992844315528697</v>
+        <v>0.01832853261458612</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04245904352455298</v>
+        <v>0.02341500778656198</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1226593900354239</v>
+        <v>0.1596486218959408</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.25784289138527</v>
+        <v>53.52075444405669</v>
       </c>
       <c r="C6" t="n">
-        <v>78.16372995605754</v>
+        <v>1865.649643013516</v>
       </c>
       <c r="D6" t="n">
-        <v>101.892135361467</v>
+        <v>69.91225478501963</v>
       </c>
       <c r="E6" t="n">
-        <v>109.3282339334233</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>2533.340362719523</v>
+        <v>609.822462302742</v>
       </c>
       <c r="G6" t="n">
-        <v>660.6882242250205</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>590.7784215144794</v>
+        <v>466.4841857575557</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2068665449192709</v>
+        <v>1.02416903580948</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8400647562181207</v>
+        <v>1.53409738358535</v>
       </c>
       <c r="D7" t="n">
-        <v>2.761792575538565</v>
+        <v>1.01096580001907</v>
       </c>
       <c r="E7" t="n">
-        <v>1.330527057387788</v>
+        <v>1.867438378572589</v>
       </c>
       <c r="F7" t="n">
-        <v>2.208947828584041</v>
+        <v>0.1505153982345837</v>
       </c>
       <c r="G7" t="n">
-        <v>5.980242929255438</v>
+        <v>1.785010296181185</v>
       </c>
       <c r="H7" t="n">
-        <v>2.221406948650538</v>
+        <v>1.228699382067043</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.5933762990192</v>
+        <v>-14.50083617811464</v>
       </c>
       <c r="C8" t="n">
-        <v>-9.462605035936335</v>
+        <v>0.8651189606192329</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.92156730990587</v>
+        <v>-31.21812319890509</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.85571660438105</v>
+        <v>-30.69178017867859</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.93194645206646</v>
+        <v>-87.98311057827085</v>
       </c>
       <c r="G8" t="n">
-        <v>-80.13959908613695</v>
+        <v>-89.61383069882078</v>
       </c>
       <c r="H8" t="n">
-        <v>-43.31746846457431</v>
+        <v>-42.19042697869512</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-30.39615172168298</v>
+        <v>-13.71193786876976</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.67084556670828</v>
+        <v>0.03215683753145271</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.12980784067781</v>
+        <v>-32.05108532199287</v>
       </c>
       <c r="E9" t="n">
-        <v>-38.063957135153</v>
+        <v>-31.52474230176637</v>
       </c>
       <c r="F9" t="n">
-        <v>-69.44703980227845</v>
+        <v>-86.04348397911885</v>
       </c>
       <c r="G9" t="n">
-        <v>-79.57464972867541</v>
+        <v>-87.35403326897463</v>
       </c>
       <c r="H9" t="n">
-        <v>-43.21374196586265</v>
+        <v>-41.7755209838485</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global_ind/metrics_summary.xlsx
+++ b/results/cross_validation/global_ind/metrics_summary.xlsx
@@ -482,25 +482,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6239499472556587</v>
+        <v>-0.3348520942290647</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7527735975417398</v>
+        <v>-0.3910280424095061</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9122335214925984</v>
+        <v>-1.55455199563998</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3681073445717913</v>
+        <v>-11.98233712002995</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5802318766232522</v>
+        <v>0.4347599307358749</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7368231893048305</v>
+        <v>-0.0492393526943149</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6623532461316451</v>
+        <v>-2.31287477904449</v>
       </c>
     </row>
     <row r="3">
@@ -510,25 +510,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2594279611063632</v>
+        <v>0.6014591031913611</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2535083276291322</v>
+        <v>0.5536321248821315</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0196325089019739</v>
+        <v>0.1449043640834347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04536255020646254</v>
+        <v>0.2160050816798269</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07014576598153914</v>
+        <v>0.08966270827582805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06452328412682429</v>
+        <v>0.1688162416629165</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1187667329920492</v>
+        <v>0.2957466039625831</v>
       </c>
     </row>
     <row r="4">
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1995004582601259</v>
+        <v>0.7081599977576237</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1266031665295795</v>
+        <v>0.7123371660525556</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007755422874194832</v>
+        <v>0.0225731182533837</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002287745390912964</v>
+        <v>0.0470021002056118</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009204024780648173</v>
+        <v>0.01239370813265159</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007617712553666349</v>
+        <v>0.03037047134854934</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05766477496705872</v>
+        <v>0.2554727602917293</v>
       </c>
     </row>
     <row r="5">
@@ -566,25 +566,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.446654741674289</v>
+        <v>0.8415224285529315</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3558133872264779</v>
+        <v>0.844000690789146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02784855988053032</v>
+        <v>0.1502435298220316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04783038146317635</v>
+        <v>0.2167996775957285</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09593760879159004</v>
+        <v>0.1113270323535645</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08727950821164353</v>
+        <v>0.1742712579530811</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1768940312079512</v>
+        <v>0.3896941028444139</v>
       </c>
     </row>
     <row r="6">
@@ -594,25 +594,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.93408076496078</v>
+        <v>57.8659249035649</v>
       </c>
       <c r="C6" t="n">
-        <v>29.80296874871598</v>
+        <v>46.8974315581541</v>
       </c>
       <c r="D6" t="n">
-        <v>8.764258404308183</v>
+        <v>86.14150944549465</v>
       </c>
       <c r="E6" t="n">
-        <v>31.57536297007752</v>
+        <v>166.7213658017702</v>
       </c>
       <c r="F6" t="n">
-        <v>19.76093796416057</v>
+        <v>46.80802030279129</v>
       </c>
       <c r="G6" t="n">
-        <v>26.95523531728989</v>
+        <v>95.94438218101159</v>
       </c>
       <c r="H6" t="n">
-        <v>24.13214069491882</v>
+        <v>83.39643903213114</v>
       </c>
     </row>
     <row r="7">
@@ -622,25 +622,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2534653366053905</v>
+        <v>1.796335253398112</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1637901373081837</v>
+        <v>1.835888857919282</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02787282315341413</v>
+        <v>1.568333562938725</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1921692184021017</v>
+        <v>7.859205212305826</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1333732543594781</v>
+        <v>0.1802476164720937</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08528544199611732</v>
+        <v>0.6760622715045581</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1426593686374476</v>
+        <v>2.3193454624231</v>
       </c>
     </row>
     <row r="8">
@@ -650,25 +650,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-10.50744871050458</v>
+        <v>4.894232972426587</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.400186545017229</v>
+        <v>5.964776409008447</v>
       </c>
       <c r="D8" t="n">
-        <v>-38.97168828561355</v>
+        <v>-14.74597323091107</v>
       </c>
       <c r="E8" t="n">
-        <v>-32.48113095111241</v>
+        <v>-10.3453779582679</v>
       </c>
       <c r="F8" t="n">
-        <v>-56.94548738764884</v>
+        <v>-49.07736246944695</v>
       </c>
       <c r="G8" t="n">
-        <v>-64.28190801819977</v>
+        <v>-40.91998271779411</v>
       </c>
       <c r="H8" t="n">
-        <v>-35.26464164968273</v>
+        <v>-17.37161449916416</v>
       </c>
     </row>
     <row r="9">
@@ -678,25 +678,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10.11299955583214</v>
+        <v>5.683131281771465</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.816667606561118</v>
+        <v>5.131814285920667</v>
       </c>
       <c r="D9" t="n">
-        <v>-39.38816934715744</v>
+        <v>-15.57893535399885</v>
       </c>
       <c r="E9" t="n">
-        <v>-32.8976120126563</v>
+        <v>-11.17834008135568</v>
       </c>
       <c r="F9" t="n">
-        <v>-55.81558867272577</v>
+        <v>-46.8175650396008</v>
       </c>
       <c r="G9" t="n">
-        <v>-63.00379335896925</v>
+        <v>-38.36375339933307</v>
       </c>
       <c r="H9" t="n">
-        <v>-35.005805092317</v>
+        <v>-16.85394138443271</v>
       </c>
     </row>
   </sheetData>
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.488095220001828</v>
+        <v>0.8645775807794492</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2402259383247827</v>
+        <v>0.0145033920544565</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4665040085421261</v>
+        <v>0.5002306138001882</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6109082663102046</v>
+        <v>0.6993296006313198</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1294250046635497</v>
+        <v>-0.04563390402976197</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7027788523564</v>
+        <v>-5.943254517206119</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1364508377423884</v>
+        <v>-0.6517078723284113</v>
       </c>
     </row>
     <row r="3">
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6889847572727756</v>
+        <v>0.2225774792433848</v>
       </c>
       <c r="C3" t="n">
-        <v>0.635799238869143</v>
+        <v>0.477841565447257</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06480390243071533</v>
+        <v>0.06488493665845484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02792728096938103</v>
+        <v>0.02455710357168324</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1151691143657734</v>
+        <v>0.1247830171227903</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08042367716403416</v>
+        <v>0.3845274058450479</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2688513285119705</v>
+        <v>0.216528584648103</v>
       </c>
     </row>
     <row r="4">
@@ -813,25 +813,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.850489289303232</v>
+        <v>0.07184371999426954</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6351123077582536</v>
+        <v>0.5046669365790332</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004714199641831041</v>
+        <v>0.004416176876949053</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001408693094854773</v>
+        <v>0.001088566727957179</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01908861913103812</v>
+        <v>0.02292703954449183</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008603133618190506</v>
+        <v>0.2009740788305421</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4199027070912333</v>
+        <v>0.1343194197588738</v>
       </c>
     </row>
     <row r="5">
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.360326905307409</v>
+        <v>0.2680367885090954</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7969393375648196</v>
+        <v>0.7103991389205319</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06866002943365988</v>
+        <v>0.06645432173266877</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03753256046228092</v>
+        <v>0.03299343461898411</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1381615689366552</v>
+        <v>0.1514167743167573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09275307875316326</v>
+        <v>0.4483013259299398</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4157289134096646</v>
+        <v>0.2796002973379962</v>
       </c>
     </row>
     <row r="6">
@@ -869,25 +869,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.44837753906288</v>
+        <v>49.20371617172356</v>
       </c>
       <c r="C6" t="n">
-        <v>70.64980401714233</v>
+        <v>43.42649148649638</v>
       </c>
       <c r="D6" t="n">
-        <v>29.704115806072</v>
+        <v>34.19214438966389</v>
       </c>
       <c r="E6" t="n">
-        <v>22.16247160807079</v>
+        <v>27.00796947102526</v>
       </c>
       <c r="F6" t="n">
-        <v>38.91621994962923</v>
+        <v>36.4310284267679</v>
       </c>
       <c r="G6" t="n">
-        <v>40.14059430531782</v>
+        <v>123.5655853845822</v>
       </c>
       <c r="H6" t="n">
-        <v>44.00359720421583</v>
+        <v>52.30448922170987</v>
       </c>
     </row>
     <row r="7">
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.689542137025622</v>
+        <v>0.09641732976215392</v>
       </c>
       <c r="C7" t="n">
-        <v>1.639292793856425</v>
+        <v>0.6544158379889863</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1663487371866439</v>
+        <v>0.1585221396738079</v>
       </c>
       <c r="E7" t="n">
-        <v>0.120713605273337</v>
+        <v>0.09646311652017411</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2775345319926618</v>
+        <v>0.6704781977801458</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09818853782581335</v>
+        <v>4.458316420686431</v>
       </c>
       <c r="H7" t="n">
-        <v>1.165270057193417</v>
+        <v>1.022435507068616</v>
       </c>
     </row>
     <row r="8">
@@ -925,25 +925,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.53905076343245</v>
+        <v>-1.699358672042507</v>
       </c>
       <c r="C8" t="n">
-        <v>9.276279401301778</v>
+        <v>17.89686040707978</v>
       </c>
       <c r="D8" t="n">
-        <v>-20.14305674718636</v>
+        <v>-10.53488550291517</v>
       </c>
       <c r="E8" t="n">
-        <v>-27.39055732497313</v>
+        <v>-18.93736025898675</v>
       </c>
       <c r="F8" t="n">
-        <v>-39.46261872097586</v>
+        <v>-27.08069788495903</v>
       </c>
       <c r="G8" t="n">
-        <v>-54.57880275035691</v>
+        <v>-0.4641107639386277</v>
       </c>
       <c r="H8" t="n">
-        <v>-19.12661756312634</v>
+        <v>-6.803258779293717</v>
       </c>
     </row>
     <row r="9">
@@ -953,25 +953,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.72239822744976</v>
+        <v>0.4701116786559076</v>
       </c>
       <c r="C9" t="n">
-        <v>8.026836216670109</v>
+        <v>15.60621456858838</v>
       </c>
       <c r="D9" t="n">
-        <v>-21.39249993181803</v>
+        <v>-12.82553134140656</v>
       </c>
       <c r="E9" t="n">
-        <v>-28.6400005096048</v>
+        <v>-21.22800609747815</v>
       </c>
       <c r="F9" t="n">
-        <v>-36.07292257620664</v>
+        <v>-20.86625495288213</v>
       </c>
       <c r="G9" t="n">
-        <v>-50.74445877266537</v>
+        <v>6.565519861829216</v>
       </c>
       <c r="H9" t="n">
-        <v>-18.35010789102916</v>
+        <v>-5.379657713782223</v>
       </c>
     </row>
   </sheetData>
@@ -1032,25 +1032,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6052280794998253</v>
+        <v>0.7405432174820235</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5790774219830688</v>
+        <v>0.6471650067547646</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5677417256944224</v>
+        <v>0.731204550218244</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01769191432656303</v>
+        <v>-0.06302308555359049</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8376498690226772</v>
+        <v>0.5479618073066959</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807447042214722</v>
+        <v>0.4583027866412372</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5646889524580049</v>
+        <v>0.5103590471415625</v>
       </c>
     </row>
     <row r="3">
@@ -1060,25 +1060,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2632665328889778</v>
+        <v>0.2345692996945325</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3312489000633217</v>
+        <v>0.2524332213241921</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05329152493131504</v>
+        <v>0.03923915209959859</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05497820442568521</v>
+        <v>0.0559289749324489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0477327252669988</v>
+        <v>0.0873315308920634</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06615235519177012</v>
+        <v>0.0903759974739993</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1361117071280114</v>
+        <v>0.1266463627361391</v>
       </c>
     </row>
     <row r="4">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2094327031023131</v>
+        <v>0.137645897489674</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2155519423122073</v>
+        <v>0.1806846961453938</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003819619705747618</v>
+        <v>0.002375192004019069</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003556412273747754</v>
+        <v>0.003848638124716426</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003559762033944685</v>
+        <v>0.009911592842923934</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006346394329721147</v>
+        <v>0.01567954886142583</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07371113895961362</v>
+        <v>0.05835759424469217</v>
       </c>
     </row>
     <row r="5">
@@ -1116,25 +1116,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4576381792446005</v>
+        <v>0.3710066003316841</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4642757179868525</v>
+        <v>0.4250702249574696</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06180307197662279</v>
+        <v>0.04873594160390327</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0596356627677412</v>
+        <v>0.06203739295551051</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0596637413673052</v>
+        <v>0.09955698289383791</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07966426005255522</v>
+        <v>0.1252180053403896</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1971134388992796</v>
+        <v>0.1886041913471325</v>
       </c>
     </row>
     <row r="6">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.94829537268154</v>
+        <v>39.9346520203627</v>
       </c>
       <c r="C6" t="n">
-        <v>40.56598790976194</v>
+        <v>25.12469609750132</v>
       </c>
       <c r="D6" t="n">
-        <v>27.61068391345197</v>
+        <v>15.11009883078349</v>
       </c>
       <c r="E6" t="n">
-        <v>35.52742004332647</v>
+        <v>45.84371018805089</v>
       </c>
       <c r="F6" t="n">
-        <v>14.4517148154561</v>
+        <v>27.41418990773307</v>
       </c>
       <c r="G6" t="n">
-        <v>29.17334306656272</v>
+        <v>29.3403572362446</v>
       </c>
       <c r="H6" t="n">
-        <v>29.37957418687346</v>
+        <v>30.46128404677934</v>
       </c>
     </row>
     <row r="7">
@@ -1172,25 +1172,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2660344683216716</v>
+        <v>0.1801891629981648</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2781631330236245</v>
+        <v>0.2383297852753463</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1333512160856966</v>
+        <v>0.08830126933734016</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2981819142936545</v>
+        <v>0.6552019447067574</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05219687271695812</v>
+        <v>0.148549572798038</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07121906476436314</v>
+        <v>0.1794848482106269</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1831911115343281</v>
+        <v>0.2483427638877123</v>
       </c>
     </row>
     <row r="8">
@@ -1200,25 +1200,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-10.07017535719479</v>
+        <v>6.15236233413275</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.207320201223693</v>
+        <v>13.73398933783794</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.40562648873183</v>
+        <v>-12.25606200579428</v>
       </c>
       <c r="E8" t="n">
-        <v>-29.83401818330805</v>
+        <v>-9.36021556260544</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.29480054974928</v>
+        <v>-35.98265276491589</v>
       </c>
       <c r="G8" t="n">
-        <v>-66.83815829216994</v>
+        <v>-34.17557250493136</v>
       </c>
       <c r="H8" t="n">
-        <v>-35.10834984539626</v>
+        <v>-11.98135852771271</v>
       </c>
     </row>
     <row r="9">
@@ -1228,25 +1228,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9.675726202522348</v>
+        <v>8.519057262167383</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.623801262767583</v>
+        <v>11.2351029685746</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.82210755027572</v>
+        <v>-14.75494837505762</v>
       </c>
       <c r="E9" t="n">
-        <v>-30.25049924485194</v>
+        <v>-11.85910193186878</v>
       </c>
       <c r="F9" t="n">
-        <v>-68.16490183482621</v>
+        <v>-29.20326047537745</v>
       </c>
       <c r="G9" t="n">
-        <v>-65.56004363293943</v>
+        <v>-26.50688454954826</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.84951328803054</v>
+        <v>-10.42833918351835</v>
       </c>
     </row>
   </sheetData>
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9335261790938426</v>
+        <v>0.8290640070150127</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8922469244370054</v>
+        <v>0.479712152925594</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.6038449789511797</v>
+        <v>0.7027359822243582</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.569127389893541</v>
+        <v>-2.669076648991513</v>
       </c>
       <c r="F2" t="n">
-        <v>0.610248094991808</v>
+        <v>-0.06706793888561369</v>
       </c>
       <c r="G2" t="n">
-        <v>0.23988402397355</v>
+        <v>-0.3536336141255922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08382214227524755</v>
+        <v>-0.1797110099729589</v>
       </c>
     </row>
     <row r="3">
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1157858503609138</v>
+        <v>0.2791451793308299</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1594110861604422</v>
+        <v>0.3197205514998337</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08909124622744267</v>
+        <v>0.04800919817145741</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06262015045502824</v>
+        <v>0.1041940817943792</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08100563478964189</v>
+        <v>0.1367067186721626</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1365338394808071</v>
+        <v>0.136044477751771</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1074079679123793</v>
+        <v>0.1706367012034057</v>
       </c>
     </row>
     <row r="4">
@@ -1363,25 +1363,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0352654058583415</v>
+        <v>0.09068422856156017</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05517970748241324</v>
+        <v>0.2664363040982178</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01417226285930057</v>
+        <v>0.002626752494049136</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009301436398108228</v>
+        <v>0.01328376445038515</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008545875668554736</v>
+        <v>0.02339701183866118</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02200172955027499</v>
+        <v>0.03918123237435578</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02407773630283222</v>
+        <v>0.0726015489695382</v>
       </c>
     </row>
     <row r="5">
@@ -1391,25 +1391,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1877908566952649</v>
+        <v>0.3011382216882476</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2349036131744534</v>
+        <v>0.5161746837052529</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1190473135324799</v>
+        <v>0.05125185356696025</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09644395469965045</v>
+        <v>0.1152552144173319</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09244390552413249</v>
+        <v>0.1529608179850683</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1483297999401165</v>
+        <v>0.1979424976460482</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1464932405943496</v>
+        <v>0.2224538815014848</v>
       </c>
     </row>
     <row r="6">
@@ -1419,25 +1419,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.92690569997862</v>
+        <v>65.29434905316566</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47601897550529</v>
+        <v>27.43520324822987</v>
       </c>
       <c r="D6" t="n">
-        <v>31.42189739741408</v>
+        <v>22.27793140781747</v>
       </c>
       <c r="E6" t="n">
-        <v>34.5774827264161</v>
+        <v>71.31512495550521</v>
       </c>
       <c r="F6" t="n">
-        <v>36.15824542523906</v>
+        <v>40.09414307038884</v>
       </c>
       <c r="G6" t="n">
-        <v>69.99409637989486</v>
+        <v>40.478593406481</v>
       </c>
       <c r="H6" t="n">
-        <v>34.259107767408</v>
+        <v>44.48255752359801</v>
       </c>
     </row>
     <row r="7">
@@ -1447,25 +1447,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04662793037268627</v>
+        <v>0.1167597578885883</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07295171790658767</v>
+        <v>0.3445917669910743</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9861481553737288</v>
+        <v>0.09301793207852696</v>
       </c>
       <c r="E7" t="n">
-        <v>1.558498444893476</v>
+        <v>2.224043259625447</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1249076844704459</v>
+        <v>0.6769965799054939</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2454360034931275</v>
+        <v>0.8710338937994535</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5057616560850088</v>
+        <v>0.7210738650480972</v>
       </c>
     </row>
     <row r="8">
@@ -1475,25 +1475,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-22.10367519616395</v>
+        <v>-13.60334640466913</v>
       </c>
       <c r="C8" t="n">
-        <v>-9.382960068156397</v>
+        <v>0.06427956226544218</v>
       </c>
       <c r="D8" t="n">
-        <v>-17.53881126615676</v>
+        <v>-27.65204193348923</v>
       </c>
       <c r="E8" t="n">
-        <v>-20.06551863603899</v>
+        <v>-17.92727624472236</v>
       </c>
       <c r="F8" t="n">
-        <v>-53.90998437470538</v>
+        <v>-40.81691053167802</v>
       </c>
       <c r="G8" t="n">
-        <v>-45.4328789790922</v>
+        <v>-37.35380377907467</v>
       </c>
       <c r="H8" t="n">
-        <v>-28.07230475338561</v>
+        <v>-22.88151655522799</v>
       </c>
     </row>
     <row r="9">
@@ -1503,25 +1503,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.31477688681908</v>
+        <v>-12.81444809532425</v>
       </c>
       <c r="C9" t="n">
-        <v>-10.21592219124418</v>
+        <v>-0.768682560822338</v>
       </c>
       <c r="D9" t="n">
-        <v>-18.37177338924454</v>
+        <v>-28.48500405657701</v>
       </c>
       <c r="E9" t="n">
-        <v>-20.89848075912677</v>
+        <v>-18.76023836781015</v>
       </c>
       <c r="F9" t="n">
-        <v>-51.65018694485924</v>
+        <v>-38.55711310183187</v>
       </c>
       <c r="G9" t="n">
-        <v>-42.87664966063117</v>
+        <v>-34.79757446061364</v>
       </c>
       <c r="H9" t="n">
-        <v>-27.55463163865416</v>
+        <v>-22.36384344049654</v>
       </c>
     </row>
   </sheetData>
@@ -1857,25 +1857,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6258371036729562</v>
+        <v>-0.4909968017002182</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7121808913493878</v>
+        <v>-0.6045568886952402</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9209392636757794</v>
+        <v>-6.446034458120704</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4740787887493597</v>
+        <v>-48.04565869474698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6083057412178591</v>
+        <v>0.5906494128096049</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7417391379388518</v>
+        <v>0.7081035296740632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6805134877673655</v>
+        <v>-9.048082316796579</v>
       </c>
     </row>
     <row r="3">
@@ -1885,25 +1885,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2589324105380315</v>
+        <v>0.6392269354572233</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2728884861657859</v>
+        <v>0.6098780236276239</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02049192249945866</v>
+        <v>0.2554900584247046</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04121087603777812</v>
+        <v>0.4194621888309931</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0653267665092315</v>
+        <v>0.07798636798035362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05945350332914929</v>
+        <v>0.05325324603374652</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1197173275132392</v>
+        <v>0.3425494700591075</v>
       </c>
     </row>
     <row r="4">
@@ -1913,25 +1913,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1984992921459029</v>
+        <v>0.7909972170800379</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1473904493232297</v>
+        <v>0.8216840149990223</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006986146116000743</v>
+        <v>0.06579635749391748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001904079461418446</v>
+        <v>0.1775681022074256</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008588464591516298</v>
+        <v>0.008975605194041227</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007475419304030695</v>
+        <v>0.008449009623983556</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06075938657294968</v>
+        <v>0.312245051099738</v>
       </c>
     </row>
     <row r="5">
@@ -1941,25 +1941,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4455325938086942</v>
+        <v>0.8893802432480935</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3839146380684509</v>
+        <v>0.906467878636095</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02643131876392236</v>
+        <v>0.2565080066857904</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04363575897607885</v>
+        <v>0.4213883033585835</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09267396933074734</v>
+        <v>0.09473967064562357</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08646050719276804</v>
+        <v>0.09191849446103627</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1797747976901103</v>
+        <v>0.4434004328392037</v>
       </c>
     </row>
     <row r="6">
@@ -1969,25 +1969,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.92359674413855</v>
+        <v>63.27236070016351</v>
       </c>
       <c r="C6" t="n">
-        <v>31.39278549921732</v>
+        <v>53.59802582409917</v>
       </c>
       <c r="D6" t="n">
-        <v>8.948626839180527</v>
+        <v>140.1932884906262</v>
       </c>
       <c r="E6" t="n">
-        <v>28.88206055423365</v>
+        <v>306.7503648740001</v>
       </c>
       <c r="F6" t="n">
-        <v>18.07352254167058</v>
+        <v>33.37810148350586</v>
       </c>
       <c r="G6" t="n">
-        <v>24.51366763750172</v>
+        <v>30.90701506874792</v>
       </c>
       <c r="H6" t="n">
-        <v>23.28904330265705</v>
+        <v>104.6831927401904</v>
       </c>
     </row>
     <row r="7">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2521983734002451</v>
+        <v>2.004994184932184</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1905190471214444</v>
+        <v>2.116091754215776</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02520725112538624</v>
+        <v>4.562735575363908</v>
       </c>
       <c r="E7" t="n">
-        <v>0.160109218998185</v>
+        <v>29.67899055993859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1245202028487037</v>
+        <v>0.1305880997929474</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08371105213116595</v>
+        <v>0.09498324783456955</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1393775242708551</v>
+        <v>6.431397237012995</v>
       </c>
     </row>
     <row r="8">
@@ -2025,25 +2025,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-10.55272770389167</v>
+        <v>3.889852534943585</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.488020573632706</v>
+        <v>4.821603793156373</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.59846786158872</v>
+        <v>-10.32714479651058</v>
       </c>
       <c r="E8" t="n">
-        <v>-33.58253965727324</v>
+        <v>-4.370406415457039</v>
       </c>
       <c r="F8" t="n">
-        <v>-57.84535893476535</v>
+        <v>-55.27218390527291</v>
       </c>
       <c r="G8" t="n">
-        <v>-64.54589093931457</v>
+        <v>-60.83188468242037</v>
       </c>
       <c r="H8" t="n">
-        <v>-35.60216761174438</v>
+        <v>-20.34836057859349</v>
       </c>
     </row>
     <row r="9">
@@ -2053,25 +2053,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10.15827854921924</v>
+        <v>4.481526266952244</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.904501635176596</v>
+        <v>4.196882200840538</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.01494892313261</v>
+        <v>-10.95186638882642</v>
       </c>
       <c r="E9" t="n">
-        <v>-33.99902071881714</v>
+        <v>-4.995128007772873</v>
       </c>
       <c r="F9" t="n">
-        <v>-56.71546021984228</v>
+        <v>-53.5773358328883</v>
       </c>
       <c r="G9" t="n">
-        <v>-63.26777628008406</v>
+        <v>-58.91471269357459</v>
       </c>
       <c r="H9" t="n">
-        <v>-35.34333105437865</v>
+        <v>-19.9601057425449</v>
       </c>
     </row>
   </sheetData>
@@ -2132,25 +2132,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.623954367248333</v>
+        <v>-0.4742830406263603</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7080626571527329</v>
+        <v>-0.5478158573263705</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8904598475850932</v>
+        <v>-3.125790015442175</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2047989963051596</v>
+        <v>-16.75355245554382</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5928556392671358</v>
+        <v>0.5093187862143554</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7169770015842996</v>
+        <v>0.4438329319164874</v>
       </c>
       <c r="H2" t="n">
-        <v>0.622851418190459</v>
+        <v>-3.324714941801313</v>
       </c>
     </row>
     <row r="3">
@@ -2160,25 +2160,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2594266950671338</v>
+        <v>0.6325660181227728</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2715995493533347</v>
+        <v>0.5942147210138986</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02421471417999809</v>
+        <v>0.1896968096883741</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05208931720228325</v>
+        <v>0.2509963249591765</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06708321012268993</v>
+        <v>0.07572181594400468</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06722177442570623</v>
+        <v>0.07117553151596119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.123605876725191</v>
+        <v>0.302395203540698</v>
       </c>
     </row>
     <row r="4">
@@ -2188,25 +2188,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.199498113384603</v>
+        <v>0.7821303043668204</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1494993724990015</v>
+        <v>0.792627271172214</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009679438187892123</v>
+        <v>0.03645725202155223</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002878997588315727</v>
+        <v>0.06427611945414731</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008927230479869304</v>
+        <v>0.01075889711384351</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008192164964354685</v>
+        <v>0.01609838209257296</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06166063712248892</v>
+        <v>0.2837247043701917</v>
       </c>
     </row>
     <row r="5">
@@ -2216,25 +2216,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4466521167358362</v>
+        <v>0.8843813116336303</v>
       </c>
       <c r="C5" t="n">
-        <v>0.386651487128915</v>
+        <v>0.8902961704804834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03111179549285467</v>
+        <v>0.1909378223965913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.053656291227737</v>
+        <v>0.2535273544494702</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09448402235229671</v>
+        <v>0.1037251035856003</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09051057929521103</v>
+        <v>0.1268793997959203</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1838443820388084</v>
+        <v>0.4082911937236159</v>
       </c>
     </row>
     <row r="6">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.9339861064911</v>
+        <v>62.16150914730942</v>
       </c>
       <c r="C6" t="n">
-        <v>29.87878308302649</v>
+        <v>52.07429461705536</v>
       </c>
       <c r="D6" t="n">
-        <v>12.305888213546</v>
+        <v>104.6742999708249</v>
       </c>
       <c r="E6" t="n">
-        <v>37.87694649649026</v>
+        <v>182.0593185092567</v>
       </c>
       <c r="F6" t="n">
-        <v>19.71652942658077</v>
+        <v>35.41286255547853</v>
       </c>
       <c r="G6" t="n">
-        <v>29.89553574823712</v>
+        <v>34.01134011992583</v>
       </c>
       <c r="H6" t="n">
-        <v>26.26794484572862</v>
+        <v>78.39893748664178</v>
       </c>
     </row>
     <row r="7">
@@ -2272,25 +2272,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2534623691947222</v>
+        <v>1.987552250489365</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1932307636034812</v>
+        <v>2.046367694036922</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03453960639762449</v>
+        <v>2.534514162095478</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2415755994202732</v>
+        <v>10.7501180405621</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1293923695557678</v>
+        <v>0.1587355921153838</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09164141499975842</v>
+        <v>0.1821189878898549</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1573070205286045</v>
+        <v>2.943234454531517</v>
       </c>
     </row>
     <row r="8">
@@ -2300,25 +2300,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-10.50755449474144</v>
+        <v>13.78839469576381</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.40277850094779</v>
+        <v>14.60558685048668</v>
       </c>
       <c r="D8" t="n">
-        <v>-37.64201906487733</v>
+        <v>-3.86968929349835</v>
       </c>
       <c r="E8" t="n">
-        <v>-31.10187863020209</v>
+        <v>-0.4674026560873941</v>
       </c>
       <c r="F8" t="n">
-        <v>-57.34243789477463</v>
+        <v>-42.91628896679864</v>
       </c>
       <c r="G8" t="n">
-        <v>-63.26407903092372</v>
+        <v>-41.80651104460161</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.54345793607784</v>
+        <v>-10.11098506912258</v>
       </c>
     </row>
     <row r="9">
@@ -2328,25 +2328,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10.113105340069</v>
+        <v>15.36619131445357</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.81925956249168</v>
+        <v>12.93966260431112</v>
       </c>
       <c r="D9" t="n">
-        <v>-38.05850012642122</v>
+        <v>-5.535613539673911</v>
       </c>
       <c r="E9" t="n">
-        <v>-31.51835969174599</v>
+        <v>-2.133326902262954</v>
       </c>
       <c r="F9" t="n">
-        <v>-56.21253917985155</v>
+        <v>-38.39669410710634</v>
       </c>
       <c r="G9" t="n">
-        <v>-61.98596437169321</v>
+        <v>-36.69405240767954</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.28462137871211</v>
+        <v>-9.075638839659675</v>
       </c>
     </row>
   </sheetData>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6248287174786535</v>
+        <v>-0.4742024174035977</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7252676491373158</v>
+        <v>-0.5688925816549919</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9092055114398102</v>
+        <v>-3.688151556830552</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3503386968833492</v>
+        <v>-29.70497912103557</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6142027152119751</v>
+        <v>0.5108115267531983</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7315454253698592</v>
+        <v>0.4479453218181846</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6592314525868271</v>
+        <v>-5.579578138058888</v>
       </c>
     </row>
     <row r="3">
@@ -2435,25 +2435,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2591781588396749</v>
+        <v>0.6355477330734451</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2656457957144873</v>
+        <v>0.5999473283507916</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0213255549467852</v>
+        <v>0.2022170011074444</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04648444856154271</v>
+        <v>0.3306383612313323</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06204724799466634</v>
+        <v>0.08090928564085684</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06350837312022103</v>
+        <v>0.07022922234302212</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1196982631962296</v>
+        <v>0.3199148219578154</v>
       </c>
     </row>
     <row r="4">
@@ -2463,25 +2463,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.199034256857112</v>
+        <v>0.782087532481083</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1406887986941588</v>
+        <v>0.8034205360239525</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008022990843493095</v>
+        <v>0.04142652005625306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002352076162133026</v>
+        <v>0.111166309433721</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008459164885916765</v>
+        <v>0.01072616661301351</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007770478629357138</v>
+        <v>0.01597934803293458</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05985117905217117</v>
+        <v>0.2941344021068262</v>
       </c>
     </row>
     <row r="5">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4461325552536062</v>
+        <v>0.8843571294907295</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3750850552796777</v>
+        <v>0.8963372892075574</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02832488454255921</v>
+        <v>0.20353505854337</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04849820782392918</v>
+        <v>0.3334161205366666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09197371845215765</v>
+        <v>0.1035672081935856</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08815031837354383</v>
+        <v>0.1264094459798578</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1796941232875789</v>
+        <v>0.4246037086586278</v>
       </c>
     </row>
     <row r="6">
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.9166044834691</v>
+        <v>62.34836127887306</v>
       </c>
       <c r="C6" t="n">
-        <v>30.20161986734976</v>
+        <v>52.84790951938115</v>
       </c>
       <c r="D6" t="n">
-        <v>9.858394777088513</v>
+        <v>106.2169534433297</v>
       </c>
       <c r="E6" t="n">
-        <v>33.12101958397747</v>
+        <v>238.8233755610779</v>
       </c>
       <c r="F6" t="n">
-        <v>18.27528452537481</v>
+        <v>35.22879162794211</v>
       </c>
       <c r="G6" t="n">
-        <v>27.12283858251672</v>
+        <v>19.55616015745132</v>
       </c>
       <c r="H6" t="n">
-        <v>24.41596030329606</v>
+        <v>85.83692526467588</v>
       </c>
     </row>
     <row r="7">
@@ -2547,25 +2547,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2528753645563823</v>
+        <v>1.986443995915675</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1819018643447164</v>
+        <v>2.073124299426529</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02879995592710146</v>
+        <v>2.877888062177086</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1975448442484884</v>
+        <v>18.58562030582856</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1226606008565492</v>
+        <v>0.15776485860315</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08697570742959224</v>
+        <v>0.1803019470775989</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1451263895604717</v>
+        <v>4.310190578171432</v>
       </c>
     </row>
     <row r="8">
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-10.52850491656055</v>
+        <v>11.78790250476245</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.767229575812124</v>
+        <v>12.68673802406224</v>
       </c>
       <c r="D8" t="n">
-        <v>-38.76817457892496</v>
+        <v>-5.103004132998574</v>
       </c>
       <c r="E8" t="n">
-        <v>-32.31474120566455</v>
+        <v>0.819632505263014</v>
       </c>
       <c r="F8" t="n">
-        <v>-58.04256270530614</v>
+        <v>-44.9558975847073</v>
       </c>
       <c r="G8" t="n">
-        <v>-64.00392923575858</v>
+        <v>-43.910413937832</v>
       </c>
       <c r="H8" t="n">
-        <v>-35.23752370300448</v>
+        <v>-11.44584043690836</v>
       </c>
     </row>
     <row r="9">
@@ -2603,25 +2603,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10.13405576188811</v>
+        <v>13.16847454611599</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.183710637356015</v>
+        <v>11.22905430865863</v>
       </c>
       <c r="D9" t="n">
-        <v>-39.18465564046885</v>
+        <v>-6.560687848402189</v>
       </c>
       <c r="E9" t="n">
-        <v>-32.73122226720844</v>
+        <v>-0.6380512101406008</v>
       </c>
       <c r="F9" t="n">
-        <v>-56.91266399038307</v>
+        <v>-41.00125208247654</v>
       </c>
       <c r="G9" t="n">
-        <v>-62.72581457652806</v>
+        <v>-39.4370126305252</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.97868714563875</v>
+        <v>-10.53991248612832</v>
       </c>
     </row>
   </sheetData>
@@ -2682,25 +2682,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8685678318370699</v>
+        <v>0.3277686086247772</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6986293261865306</v>
+        <v>0.2760376358262634</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4126901534395658</v>
+        <v>0.8113152392860703</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5209892718759563</v>
+        <v>-2.114152072346265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08861459281888762</v>
+        <v>0.5176042677548718</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6925776404901107</v>
+        <v>0.3881096861358225</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3733483788160348</v>
+        <v>0.0344472275469234</v>
       </c>
     </row>
     <row r="3">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1750876146413242</v>
+        <v>0.3504722069681389</v>
       </c>
       <c r="C3" t="n">
-        <v>0.31309808885334</v>
+        <v>0.417212187081936</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06344321100702473</v>
+        <v>0.03191046092134913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06410168510749435</v>
+        <v>0.09731069962948319</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1076346311514207</v>
+        <v>0.09275156808853072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07545303858804472</v>
+        <v>0.1138849839688397</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1331363782247748</v>
+        <v>0.1839236844430463</v>
       </c>
     </row>
     <row r="4">
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0697268291475357</v>
+        <v>0.356629309469541</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1543301250374338</v>
+        <v>0.3707368098280284</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005189721970980668</v>
+        <v>0.001667299559169827</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005506688780872554</v>
+        <v>0.01127467931287207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01998344658698003</v>
+        <v>0.01057722591688587</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008898410012380311</v>
+        <v>0.01771130409657914</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04393920358936384</v>
+        <v>0.1280994380305127</v>
       </c>
     </row>
     <row r="5">
@@ -2766,25 +2766,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2640583820815687</v>
+        <v>0.5971844852887096</v>
       </c>
       <c r="C5" t="n">
-        <v>0.392848730477055</v>
+        <v>0.6088816057560192</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07203972495075664</v>
+        <v>0.04083257962913717</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07420706692002153</v>
+        <v>0.10618229284053</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1413628189694165</v>
+        <v>0.1028456412148121</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09433138402663406</v>
+        <v>0.1330838235721349</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1731413512375754</v>
+        <v>0.2648350713835572</v>
       </c>
     </row>
     <row r="6">
@@ -2794,25 +2794,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.34577571975767</v>
+        <v>29.13037842759058</v>
       </c>
       <c r="C6" t="n">
-        <v>42.65378767894514</v>
+        <v>41.39317999795678</v>
       </c>
       <c r="D6" t="n">
-        <v>35.24985622128856</v>
+        <v>13.80682368489973</v>
       </c>
       <c r="E6" t="n">
-        <v>44.01882111465301</v>
+        <v>60.75125563962567</v>
       </c>
       <c r="F6" t="n">
-        <v>33.35944508208592</v>
+        <v>24.78723260207323</v>
       </c>
       <c r="G6" t="n">
-        <v>29.79165501554208</v>
+        <v>40.00760538910419</v>
       </c>
       <c r="H6" t="n">
-        <v>35.9032234720454</v>
+        <v>34.9794126235417</v>
       </c>
     </row>
     <row r="7">
@@ -2822,25 +2822,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08873843085215402</v>
+        <v>0.4528099340412455</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1989422896702445</v>
+        <v>0.4782044761317409</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1803257593478167</v>
+        <v>0.0592725379055978</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9213029274187955</v>
+        <v>1.88727579444578</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2879040347652198</v>
+        <v>0.1536227778153586</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09895559486163302</v>
+        <v>0.1974650070268587</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2960281728193106</v>
+        <v>0.5381084212277636</v>
       </c>
     </row>
     <row r="8">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.96853100865231</v>
+        <v>-3.279525469364248</v>
       </c>
       <c r="C8" t="n">
-        <v>-9.211967811246815</v>
+        <v>0.04642274643076583</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.56645092026722</v>
+        <v>-32.37929995077317</v>
       </c>
       <c r="E8" t="n">
-        <v>-29.21075070201115</v>
+        <v>-20.91117501789131</v>
       </c>
       <c r="F8" t="n">
-        <v>-48.86706324423893</v>
+        <v>-53.13767713886504</v>
       </c>
       <c r="G8" t="n">
-        <v>-64.10635735897557</v>
+        <v>-50.46973071219099</v>
       </c>
       <c r="H8" t="n">
-        <v>-33.82185350756533</v>
+        <v>-26.68849759044233</v>
       </c>
     </row>
     <row r="9">
@@ -2878,25 +2878,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.77130643131609</v>
+        <v>-2.68785173735559</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.420208342018761</v>
+        <v>-0.5782988458850689</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.77469145103917</v>
+        <v>-33.00402154308901</v>
       </c>
       <c r="E9" t="n">
-        <v>-29.4189912327831</v>
+        <v>-21.53589661020715</v>
       </c>
       <c r="F9" t="n">
-        <v>-48.3021138867774</v>
+        <v>-51.44282906648043</v>
       </c>
       <c r="G9" t="n">
-        <v>-63.46730002936032</v>
+        <v>-48.55255872334522</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.69243522888247</v>
+        <v>-26.30024275439375</v>
       </c>
     </row>
   </sheetData>
@@ -2957,25 +2957,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8763164901305321</v>
+        <v>0.04816807796755396</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7335847922737466</v>
+        <v>0.02397563792941282</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8897989646310563</v>
+        <v>-1.277023431119883</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8159001480919044</v>
+        <v>-5.523654133549165</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6114763337745661</v>
+        <v>0.5888369132872135</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7436396702000752</v>
+        <v>0.05144187779013509</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7784527331836467</v>
+        <v>-1.014709176282455</v>
       </c>
     </row>
     <row r="3">
@@ -2985,25 +2985,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1502569241408714</v>
+        <v>0.4722917721766684</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2656699490904884</v>
+        <v>0.440825513521497</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02850780216096743</v>
+        <v>0.13350607261929</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02216297679425426</v>
+        <v>0.1514551031083642</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06024931334651434</v>
+        <v>0.07559704298348544</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04399972732622922</v>
+        <v>0.1296207212228465</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09514111547655418</v>
+        <v>0.2338827042720252</v>
       </c>
     </row>
     <row r="4">
@@ -3013,25 +3013,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06561604424226725</v>
+        <v>0.5049617816732157</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1364296392877129</v>
+        <v>0.4998162559478709</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009737836643271305</v>
+        <v>0.02012075669789517</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000666527113509639</v>
+        <v>0.02361866299240919</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008518944752261904</v>
+        <v>0.009015346874245064</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007420407966114081</v>
+        <v>0.02745623026722429</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03660422450436548</v>
+        <v>0.1808315057421434</v>
       </c>
     </row>
     <row r="5">
@@ -3041,25 +3041,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2561562887033368</v>
+        <v>0.7106066293479225</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3693638305082306</v>
+        <v>0.7069768425824646</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03120550695513743</v>
+        <v>0.1418476531279075</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0258171863980109</v>
+        <v>0.153683645819616</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09229812973328282</v>
+        <v>0.09494918048221936</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08614178989383771</v>
+        <v>0.1656992162541039</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1434971220319727</v>
+        <v>0.3289605279357057</v>
       </c>
     </row>
     <row r="6">
@@ -3069,25 +3069,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.8428537674006</v>
+        <v>59.25666201428961</v>
       </c>
       <c r="C6" t="n">
-        <v>32.17900588432645</v>
+        <v>47.3865512705325</v>
       </c>
       <c r="D6" t="n">
-        <v>13.74677476019102</v>
+        <v>83.33480786919245</v>
       </c>
       <c r="E6" t="n">
-        <v>15.178555471334</v>
+        <v>111.9917775120955</v>
       </c>
       <c r="F6" t="n">
-        <v>15.51375779697422</v>
+        <v>33.98933014939521</v>
       </c>
       <c r="G6" t="n">
-        <v>15.64904565898547</v>
+        <v>45.09438711480063</v>
       </c>
       <c r="H6" t="n">
-        <v>17.35166555653529</v>
+        <v>63.50891932171763</v>
       </c>
     </row>
     <row r="7">
@@ -3097,25 +3097,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08403628393042743</v>
+        <v>0.6450228237809847</v>
       </c>
       <c r="C7" t="n">
-        <v>0.176425309819275</v>
+        <v>0.6486786877846858</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03474195917571209</v>
+        <v>1.406383118048983</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05669652455188545</v>
+        <v>3.959258608318872</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1235203611942135</v>
+        <v>0.1356596688258075</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08310238451625732</v>
+        <v>0.3097867978500165</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0930871371979618</v>
+        <v>1.184131617434892</v>
       </c>
     </row>
     <row r="8">
@@ -3125,25 +3125,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-20.51541532465078</v>
+        <v>17.85054720816906</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.951677562085436</v>
+        <v>19.83891158277297</v>
       </c>
       <c r="D8" t="n">
-        <v>-37.6059283372342</v>
+        <v>0.5639800486890856</v>
       </c>
       <c r="E8" t="n">
-        <v>-39.88057843243022</v>
+        <v>1.525691551747158</v>
       </c>
       <c r="F8" t="n">
-        <v>-57.95101641533926</v>
+        <v>-37.21475029297419</v>
       </c>
       <c r="G8" t="n">
-        <v>-64.64929737901514</v>
+        <v>-26.33227036515031</v>
       </c>
       <c r="H8" t="n">
-        <v>-38.09231890845917</v>
+        <v>-3.961315044457704</v>
       </c>
     </row>
     <row r="9">
@@ -3153,25 +3153,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-20.12096616997834</v>
+        <v>20.21724213620369</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.368158623629327</v>
+        <v>17.34002521350963</v>
       </c>
       <c r="D9" t="n">
-        <v>-38.02240939877809</v>
+        <v>-1.934906320574253</v>
       </c>
       <c r="E9" t="n">
-        <v>-40.29705949397411</v>
+        <v>-0.9731948175161804</v>
       </c>
       <c r="F9" t="n">
-        <v>-56.82111770041619</v>
+        <v>-30.43535800343574</v>
       </c>
       <c r="G9" t="n">
-        <v>-63.37118271978462</v>
+        <v>-18.66358240976721</v>
       </c>
       <c r="H9" t="n">
-        <v>-37.83348235109344</v>
+        <v>-2.408295700263344</v>
       </c>
     </row>
   </sheetData>
@@ -3232,25 +3232,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8436242274262216</v>
+        <v>-0.3393562671117369</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6341135575690567</v>
+        <v>0.1334077646307407</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8621672544670789</v>
+        <v>-0.1736160572066336</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5028149324824145</v>
+        <v>-0.09553889238147018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3262595186737904</v>
+        <v>-0.4016881575371958</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7231904098508483</v>
+        <v>-1.933051775019947</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6486949834115684</v>
+        <v>-0.4683072307710405</v>
       </c>
     </row>
     <row r="3">
@@ -3260,25 +3260,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1757332759837784</v>
+        <v>0.5898934951703412</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3016175729325269</v>
+        <v>0.4694666714192655</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03148628326002361</v>
+        <v>0.08519587469594352</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03663500059252107</v>
+        <v>0.04713059046339321</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1026830521888454</v>
+        <v>0.1479474183611203</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07920405583566012</v>
+        <v>0.2554558645306542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1212265401322259</v>
+        <v>0.2658483191067863</v>
       </c>
     </row>
     <row r="4">
@@ -3288,25 +3288,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08295980298787352</v>
+        <v>0.7105495322028877</v>
       </c>
       <c r="C4" t="n">
-        <v>0.187368265449807</v>
+        <v>0.4437767163894157</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00121794931925968</v>
+        <v>0.01037057538410304</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001800041252059361</v>
+        <v>0.003966360472908443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01477273699576912</v>
+        <v>0.03073404534134777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008012316450999282</v>
+        <v>0.08489784973115384</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04935518540929465</v>
+        <v>0.2140491799203028</v>
       </c>
     </row>
     <row r="5">
@@ -3316,25 +3316,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2880274344361549</v>
+        <v>0.8429410016145186</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4328605612085802</v>
+        <v>0.6661656823864583</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03489913063759154</v>
+        <v>0.101836022035933</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04242689302858932</v>
+        <v>0.06297904788823377</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1215431486994192</v>
+        <v>0.175311281272335</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08951154367454112</v>
+        <v>0.291372355811518</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1682114519474794</v>
+        <v>0.3567675651681661</v>
       </c>
     </row>
     <row r="6">
@@ -3344,25 +3344,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.64462793629973</v>
+        <v>58.86535938730673</v>
       </c>
       <c r="C6" t="n">
-        <v>31.1953459722528</v>
+        <v>47.28820402521066</v>
       </c>
       <c r="D6" t="n">
-        <v>19.51698787411599</v>
+        <v>35.91053219588825</v>
       </c>
       <c r="E6" t="n">
-        <v>32.83445299734411</v>
+        <v>27.73430205252467</v>
       </c>
       <c r="F6" t="n">
-        <v>27.52854123009909</v>
+        <v>47.08690271122896</v>
       </c>
       <c r="G6" t="n">
-        <v>28.35884204783627</v>
+        <v>83.83729996863104</v>
       </c>
       <c r="H6" t="n">
-        <v>25.84646634299133</v>
+        <v>50.12043339013172</v>
       </c>
     </row>
     <row r="7">
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.106484593863645</v>
+        <v>1.802383105351085</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2424237185441478</v>
+        <v>0.5726213720833688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04370238818335812</v>
+        <v>0.7226884398617245</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1519155491317172</v>
+        <v>0.666876240090954</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2139630602949013</v>
+        <v>0.8880405580002045</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09015149856044502</v>
+        <v>1.882688054635584</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1414401347630358</v>
+        <v>1.08921629500382</v>
       </c>
     </row>
     <row r="8">
@@ -3400,25 +3400,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-16.40459180863414</v>
+        <v>4.92455042626707</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.048075588604158</v>
+        <v>3.125397595658973</v>
       </c>
       <c r="D8" t="n">
-        <v>-34.26352032218017</v>
+        <v>-19.41269663698756</v>
       </c>
       <c r="E8" t="n">
-        <v>-31.91967417919123</v>
+        <v>-25.1794381732957</v>
       </c>
       <c r="F8" t="n">
-        <v>-48.79463459386528</v>
+        <v>-37.27099551087208</v>
       </c>
       <c r="G8" t="n">
-        <v>-61.57485510761076</v>
+        <v>-26.52829118287746</v>
       </c>
       <c r="H8" t="n">
-        <v>-32.83422526668095</v>
+        <v>-16.72357891368446</v>
       </c>
     </row>
     <row r="9">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-15.81291807662548</v>
+        <v>5.713448735611948</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.672797180919993</v>
+        <v>2.292435472571193</v>
       </c>
       <c r="D9" t="n">
-        <v>-34.88824191449601</v>
+        <v>-20.24565876007534</v>
       </c>
       <c r="E9" t="n">
-        <v>-32.54439577150706</v>
+        <v>-26.01240029638348</v>
       </c>
       <c r="F9" t="n">
-        <v>-47.09978652148067</v>
+        <v>-35.01119808102594</v>
       </c>
       <c r="G9" t="n">
-        <v>-59.65768311876499</v>
+        <v>-23.97206186441642</v>
       </c>
       <c r="H9" t="n">
-        <v>-32.44597043063236</v>
+        <v>-16.20590579895301</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/global_ind/metrics_summary.xlsx
+++ b/results/cross_validation/global_ind/metrics_summary.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8645775807794492</v>
+        <v>0.9307216193376199</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0145033920544565</v>
+        <v>-0.113546152323984</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5002306138001882</v>
+        <v>0.4858128212819773</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6993296006313198</v>
+        <v>0.7475602372657608</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.04563390402976197</v>
+        <v>-0.3326028335021165</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.943254517206119</v>
+        <v>0.88293397979138</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6517078723284113</v>
+        <v>0.4334799453084395</v>
       </c>
     </row>
     <row r="3">
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2225774792433848</v>
+        <v>0.148454894607697</v>
       </c>
       <c r="C3" t="n">
-        <v>0.477841565447257</v>
+        <v>0.557592833272092</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06488493665845484</v>
+        <v>0.0578417699186328</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02455710357168324</v>
+        <v>0.02781615989491391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1247830171227903</v>
+        <v>0.1469780547576257</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3845274058450479</v>
+        <v>0.04967070865465885</v>
       </c>
       <c r="H3" t="n">
-        <v>0.216528584648103</v>
+        <v>0.1647257368509367</v>
       </c>
     </row>
     <row r="4">
@@ -813,25 +813,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07184371999426954</v>
+        <v>0.03675326885025213</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5046669365790332</v>
+        <v>0.5702403447174197</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004416176876949053</v>
+        <v>0.004543578682049047</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001088566727957179</v>
+        <v>0.0009139493847844408</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02292703954449183</v>
+        <v>0.02921924943621115</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2009740788305421</v>
+        <v>0.003388502540916808</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1343194197588738</v>
+        <v>0.1075098156019389</v>
       </c>
     </row>
     <row r="5">
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2680367885090954</v>
+        <v>0.1917114207611329</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7103991389205319</v>
+        <v>0.7551425989291159</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06645432173266877</v>
+        <v>0.06740607303536564</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03299343461898411</v>
+        <v>0.03023159580280936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1514167743167573</v>
+        <v>0.1709363900291894</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4483013259299398</v>
+        <v>0.05821084556091595</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2796002973379962</v>
+        <v>0.2122731540197549</v>
       </c>
     </row>
     <row r="6">
@@ -869,25 +869,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.20371617172356</v>
+        <v>20.23576997367782</v>
       </c>
       <c r="C6" t="n">
-        <v>43.42649148649638</v>
+        <v>60.98797633233774</v>
       </c>
       <c r="D6" t="n">
-        <v>34.19214438966389</v>
+        <v>23.87777011117193</v>
       </c>
       <c r="E6" t="n">
-        <v>27.00796947102526</v>
+        <v>22.53066428260665</v>
       </c>
       <c r="F6" t="n">
-        <v>36.4310284267679</v>
+        <v>43.8213453518174</v>
       </c>
       <c r="G6" t="n">
-        <v>123.5655853845822</v>
+        <v>20.68535333756011</v>
       </c>
       <c r="H6" t="n">
-        <v>52.30448922170987</v>
+        <v>32.02314656486194</v>
       </c>
     </row>
     <row r="7">
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09641732976215392</v>
+        <v>0.04851080239389054</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6544158379889863</v>
+        <v>1.470464173998778</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1585221396738079</v>
+        <v>0.1594366586928412</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09646311652017411</v>
+        <v>0.07837169338962088</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6704781977801458</v>
+        <v>0.8444686493119656</v>
       </c>
       <c r="G7" t="n">
-        <v>4.458316420686431</v>
+        <v>0.03949175784122778</v>
       </c>
       <c r="H7" t="n">
-        <v>1.022435507068616</v>
+        <v>0.440123955938054</v>
       </c>
     </row>
     <row r="8">
@@ -925,25 +925,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.699358672042507</v>
+        <v>-21.73175298075499</v>
       </c>
       <c r="C8" t="n">
-        <v>17.89686040707978</v>
+        <v>4.629815902237647</v>
       </c>
       <c r="D8" t="n">
-        <v>-10.53488550291517</v>
+        <v>-24.36424192888902</v>
       </c>
       <c r="E8" t="n">
-        <v>-18.93736025898675</v>
+        <v>-33.98641219444644</v>
       </c>
       <c r="F8" t="n">
-        <v>-27.08069788495903</v>
+        <v>-37.92805827525815</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4641107639386277</v>
+        <v>-71.6231405693305</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.803258779293717</v>
+        <v>-30.83396500774024</v>
       </c>
     </row>
     <row r="9">
@@ -953,25 +953,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4701116786559076</v>
+        <v>-20.94285467141012</v>
       </c>
       <c r="C9" t="n">
-        <v>15.60621456858838</v>
+        <v>3.796853779149867</v>
       </c>
       <c r="D9" t="n">
-        <v>-12.82553134140656</v>
+        <v>-25.1972040519768</v>
       </c>
       <c r="E9" t="n">
-        <v>-21.22800609747815</v>
+        <v>-34.81937431753423</v>
       </c>
       <c r="F9" t="n">
-        <v>-20.86625495288213</v>
+        <v>-35.66826084541201</v>
       </c>
       <c r="G9" t="n">
-        <v>6.565519861829216</v>
+        <v>-69.06691125086947</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.379657713782223</v>
+        <v>-30.31629189300879</v>
       </c>
     </row>
   </sheetData>
@@ -1032,25 +1032,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7405432174820235</v>
+        <v>0.5322122403418451</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6471650067547646</v>
+        <v>0.3959891612370473</v>
       </c>
       <c r="D2" t="n">
-        <v>0.731204550218244</v>
+        <v>0.6766252994135792</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.06302308555359049</v>
+        <v>-0.04948809935183918</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5479618073066959</v>
+        <v>0.519212269072604</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4583027866412372</v>
+        <v>0.2510753883468199</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5103590471415625</v>
+        <v>0.3876043765100094</v>
       </c>
     </row>
     <row r="3">
@@ -1060,25 +1060,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2345692996945325</v>
+        <v>0.2867453324907351</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2524332213241921</v>
+        <v>0.363634190858969</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03923915209959859</v>
+        <v>0.04449466390879434</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0559289749324489</v>
+        <v>0.05468549709840365</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0873315308920634</v>
+        <v>0.08852912492028278</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0903759974739993</v>
+        <v>0.09697121517464972</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1266463627361391</v>
+        <v>0.1558433374086391</v>
       </c>
     </row>
     <row r="4">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.137645897489674</v>
+        <v>0.2481687523754344</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1806846961453938</v>
+        <v>0.3093103489158591</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002375192004019069</v>
+        <v>0.00285747769822203</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003848638124716426</v>
+        <v>0.003799635177723564</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009911592842923934</v>
+        <v>0.01054196815634735</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01567954886142583</v>
+        <v>0.02167779296690459</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05835759424469217</v>
+        <v>0.09939266254841517</v>
       </c>
     </row>
     <row r="5">
@@ -1116,25 +1116,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3710066003316841</v>
+        <v>0.4981653865689932</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4250702249574696</v>
+        <v>0.5561567664929189</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04873594160390327</v>
+        <v>0.05345538044221582</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06203739295551051</v>
+        <v>0.06164118085925645</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09955698289383791</v>
+        <v>0.1026740870733572</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1252180053403896</v>
+        <v>0.1472338037507168</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1886041913471325</v>
+        <v>0.2365544341979098</v>
       </c>
     </row>
     <row r="6">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.9346520203627</v>
+        <v>33.61708222650574</v>
       </c>
       <c r="C6" t="n">
-        <v>25.12469609750132</v>
+        <v>37.23577359772289</v>
       </c>
       <c r="D6" t="n">
-        <v>15.11009883078349</v>
+        <v>17.0957858288949</v>
       </c>
       <c r="E6" t="n">
-        <v>45.84371018805089</v>
+        <v>46.42077192124482</v>
       </c>
       <c r="F6" t="n">
-        <v>27.41418990773307</v>
+        <v>27.18313057827408</v>
       </c>
       <c r="G6" t="n">
-        <v>29.3403572362446</v>
+        <v>36.51270556128613</v>
       </c>
       <c r="H6" t="n">
-        <v>30.46128404677934</v>
+        <v>33.01087495232143</v>
       </c>
     </row>
     <row r="7">
@@ -1172,25 +1172,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1801891629981648</v>
+        <v>0.3195544545602506</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2383297852753463</v>
+        <v>0.4032204958699873</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08830126933734016</v>
+        <v>0.1045126445646817</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6552019447067574</v>
+        <v>0.6460123488599165</v>
       </c>
       <c r="F7" t="n">
-        <v>0.148549572798038</v>
+        <v>0.157115696987662</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1794848482106269</v>
+        <v>0.2453518385727873</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2483427638877123</v>
+        <v>0.3126279132358808</v>
       </c>
     </row>
     <row r="8">
@@ -1200,25 +1200,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.15236233413275</v>
+        <v>9.457183200157013</v>
       </c>
       <c r="C8" t="n">
-        <v>13.73398933783794</v>
+        <v>14.95953915580967</v>
       </c>
       <c r="D8" t="n">
-        <v>-12.25606200579428</v>
+        <v>-13.14689580183484</v>
       </c>
       <c r="E8" t="n">
-        <v>-9.36021556260544</v>
+        <v>-11.43710133632525</v>
       </c>
       <c r="F8" t="n">
-        <v>-35.98265276491589</v>
+        <v>-37.18108327559901</v>
       </c>
       <c r="G8" t="n">
-        <v>-34.17557250493136</v>
+        <v>-31.6405367121713</v>
       </c>
       <c r="H8" t="n">
-        <v>-11.98135852771271</v>
+        <v>-11.49814912832728</v>
       </c>
     </row>
     <row r="9">
@@ -1228,25 +1228,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.519057262167383</v>
+        <v>11.62665355085543</v>
       </c>
       <c r="C9" t="n">
-        <v>11.2351029685746</v>
+        <v>12.66889331731828</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.75494837505762</v>
+        <v>-15.43754164032623</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.85910193186878</v>
+        <v>-13.72774717481665</v>
       </c>
       <c r="F9" t="n">
-        <v>-29.20326047537745</v>
+        <v>-30.9666403435221</v>
       </c>
       <c r="G9" t="n">
-        <v>-26.50688454954826</v>
+        <v>-24.61090608640346</v>
       </c>
       <c r="H9" t="n">
-        <v>-10.42833918351835</v>
+        <v>-10.07454806281579</v>
       </c>
     </row>
   </sheetData>
@@ -1582,25 +1582,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5038892464581608</v>
+        <v>0.8289733721003293</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4813254593126435</v>
+        <v>0.5054415124767873</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5168962693519259</v>
+        <v>0.7187638459105679</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6452623963277524</v>
+        <v>-2.477248867299485</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5854856098601107</v>
+        <v>-0.1697669484088691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2231123687019424</v>
+        <v>-38.61995438444821</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3322200718978748</v>
+        <v>-6.535631911611479</v>
       </c>
     </row>
     <row r="3">
@@ -1610,25 +1610,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3504042502542233</v>
+        <v>0.2683601799359722</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6366603083969438</v>
+        <v>0.3137170916038851</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04935130587157693</v>
+        <v>0.04688022651039043</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03012394228008801</v>
+        <v>0.1016540690866198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08133218674224739</v>
+        <v>0.1426809489857602</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1375071729345135</v>
+        <v>0.6033379246683938</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2142298610799321</v>
+        <v>0.2461050734651703</v>
       </c>
     </row>
     <row r="4">
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2631945453991498</v>
+        <v>0.09073231180707962</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7585779348204014</v>
+        <v>0.2532604524918786</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004268911988944575</v>
+        <v>0.002485123408810146</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001284315161464789</v>
+        <v>0.01258925863575814</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009088829061368743</v>
+        <v>0.02564883653891765</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02248718892099543</v>
+        <v>1.146808577445988</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1764836208920541</v>
+        <v>0.255254093388072</v>
       </c>
     </row>
     <row r="5">
@@ -1666,25 +1666,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5130248974456794</v>
+        <v>0.3012180469478541</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8709637965038509</v>
+        <v>0.5032498907023017</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0653369113820402</v>
+        <v>0.04985101211420032</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03583734311391944</v>
+        <v>0.1122018655627354</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09533535053362285</v>
+        <v>0.1601525414688061</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1499572903229297</v>
+        <v>1.070891487241349</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2884092648836737</v>
+        <v>0.366260807339541</v>
       </c>
     </row>
     <row r="6">
@@ -1694,25 +1694,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.03035492739448</v>
+        <v>60.93203374060686</v>
       </c>
       <c r="C6" t="n">
-        <v>63.83928815220064</v>
+        <v>26.93214292304248</v>
       </c>
       <c r="D6" t="n">
-        <v>17.30374009568751</v>
+        <v>22.01827361111813</v>
       </c>
       <c r="E6" t="n">
-        <v>18.81808878259936</v>
+        <v>70.03515391047065</v>
       </c>
       <c r="F6" t="n">
-        <v>36.30767886611383</v>
+        <v>40.98121627305381</v>
       </c>
       <c r="G6" t="n">
-        <v>69.38172398020255</v>
+        <v>137.0433970371868</v>
       </c>
       <c r="H6" t="n">
-        <v>39.94681246736641</v>
+        <v>59.65703624924645</v>
       </c>
     </row>
     <row r="7">
@@ -1722,25 +1722,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3360694078419567</v>
+        <v>0.116820606634857</v>
       </c>
       <c r="C7" t="n">
-        <v>1.956804384336148</v>
+        <v>0.3276498630012789</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1509193575866835</v>
+        <v>0.08811043261299675</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1103203017146997</v>
+        <v>2.107974282469753</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1337164973849249</v>
+        <v>0.7417685401998063</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2518073216341141</v>
+        <v>25.38150463909331</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4899395450830878</v>
+        <v>4.793971394002001</v>
       </c>
     </row>
     <row r="8">
@@ -1750,25 +1750,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01375623521778557</v>
+        <v>-13.59857562446431</v>
       </c>
       <c r="C8" t="n">
-        <v>10.34214157882679</v>
+        <v>-0.2400211797515475</v>
       </c>
       <c r="D8" t="n">
-        <v>-20.73837772641239</v>
+        <v>-27.98459775504172</v>
       </c>
       <c r="E8" t="n">
-        <v>-27.94517790587276</v>
+        <v>-18.249467906955</v>
       </c>
       <c r="F8" t="n">
-        <v>-49.10921953787704</v>
+        <v>-39.6223418775083</v>
       </c>
       <c r="G8" t="n">
-        <v>-41.12733318507912</v>
+        <v>9.917761082442869</v>
       </c>
       <c r="H8" t="n">
-        <v>-21.43195383527205</v>
+        <v>-14.96287387687967</v>
       </c>
     </row>
     <row r="9">
@@ -1778,25 +1778,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.169591228799531</v>
+        <v>-12.80967731511944</v>
       </c>
       <c r="C9" t="n">
-        <v>9.092698394195125</v>
+        <v>-1.072983302839328</v>
       </c>
       <c r="D9" t="n">
-        <v>-21.98782091104406</v>
+        <v>-28.8175598781295</v>
       </c>
       <c r="E9" t="n">
-        <v>-29.19462109050443</v>
+        <v>-19.08243003004278</v>
       </c>
       <c r="F9" t="n">
-        <v>-45.71952339310782</v>
+        <v>-37.36254444766215</v>
       </c>
       <c r="G9" t="n">
-        <v>-37.29298920738756</v>
+        <v>12.4739904009039</v>
       </c>
       <c r="H9" t="n">
-        <v>-20.65544416317487</v>
+        <v>-14.44520076214822</v>
       </c>
     </row>
   </sheetData>
@@ -1857,25 +1857,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.4909968017002182</v>
+        <v>-0.1339382503343978</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6045568886952402</v>
+        <v>-0.604556897658223</v>
       </c>
       <c r="D2" t="n">
-        <v>-6.446034458120704</v>
+        <v>-3.503431092908371</v>
       </c>
       <c r="E2" t="n">
-        <v>-48.04565869474698</v>
+        <v>-32.7996700086531</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5906494128096049</v>
+        <v>0.580481387442407</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7081035296740632</v>
+        <v>0.7425027960852767</v>
       </c>
       <c r="H2" t="n">
-        <v>-9.048082316796579</v>
+        <v>-5.953102011004401</v>
       </c>
     </row>
     <row r="3">
@@ -1885,25 +1885,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6392269354572233</v>
+        <v>0.5553688959234085</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6098780236276239</v>
+        <v>0.6098780255670923</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2554900584247046</v>
+        <v>0.1979448078146765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4194621888309931</v>
+        <v>0.3476471281780953</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07798636798035362</v>
+        <v>0.08271422952952527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05325324603374652</v>
+        <v>0.07057101513755379</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3425494700591075</v>
+        <v>0.310687350358392</v>
       </c>
     </row>
     <row r="4">
@@ -1913,25 +1913,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7909972170800379</v>
+        <v>0.6015720485331104</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8216840149990223</v>
+        <v>0.8216840195889125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06579635749391748</v>
+        <v>0.03979425072564167</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1775681022074256</v>
+        <v>0.1223705302038606</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008975605194041227</v>
+        <v>0.009198553894140484</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008449009623983556</v>
+        <v>0.007453315045553803</v>
       </c>
       <c r="H4" t="n">
-        <v>0.312245051099738</v>
+        <v>0.2670121196652033</v>
       </c>
     </row>
     <row r="5">
@@ -1941,25 +1941,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8893802432480935</v>
+        <v>0.7756107583918047</v>
       </c>
       <c r="C5" t="n">
-        <v>0.906467878636095</v>
+        <v>0.9064678811678395</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2565080066857904</v>
+        <v>0.1994849636580203</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4213883033585835</v>
+        <v>0.3498149942524771</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09473967064562357</v>
+        <v>0.09590909182210247</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09191849446103627</v>
+        <v>0.08633258391565611</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4434004328392037</v>
+        <v>0.40227004553465</v>
       </c>
     </row>
     <row r="6">
@@ -1969,25 +1969,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.27236070016351</v>
+        <v>60.17452671466674</v>
       </c>
       <c r="C6" t="n">
-        <v>53.59802582409917</v>
+        <v>53.59802624836117</v>
       </c>
       <c r="D6" t="n">
-        <v>140.1932884906262</v>
+        <v>110.1035117226935</v>
       </c>
       <c r="E6" t="n">
-        <v>306.7503648740001</v>
+        <v>253.3520462355196</v>
       </c>
       <c r="F6" t="n">
-        <v>33.37810148350586</v>
+        <v>30.04532273720684</v>
       </c>
       <c r="G6" t="n">
-        <v>30.90701506874792</v>
+        <v>39.29983366502063</v>
       </c>
       <c r="H6" t="n">
-        <v>104.6831927401904</v>
+        <v>91.0955445539114</v>
       </c>
     </row>
     <row r="7">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.004994184932184</v>
+        <v>1.527563818146993</v>
       </c>
       <c r="C7" t="n">
-        <v>2.116091754215776</v>
+        <v>2.118091766019411</v>
       </c>
       <c r="D7" t="n">
-        <v>4.562735575363908</v>
+        <v>2.762770606760921</v>
       </c>
       <c r="E7" t="n">
-        <v>29.67899055993859</v>
+        <v>20.45612074747727</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1305880997929474</v>
+        <v>0.1347945714931763</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09498324783456955</v>
+        <v>0.08496648170630466</v>
       </c>
       <c r="H7" t="n">
-        <v>6.431397237012995</v>
+        <v>4.514051331934012</v>
       </c>
     </row>
     <row r="8">
@@ -2025,25 +2025,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.889852534943585</v>
+        <v>5.42611927624873</v>
       </c>
       <c r="C8" t="n">
-        <v>4.821603793156373</v>
+        <v>8.821603826672105</v>
       </c>
       <c r="D8" t="n">
-        <v>-10.32714479651058</v>
+        <v>-9.344196987535124</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.370406415457039</v>
+        <v>-2.604210225206606</v>
       </c>
       <c r="F8" t="n">
-        <v>-55.27218390527291</v>
+        <v>-50.95321690512051</v>
       </c>
       <c r="G8" t="n">
-        <v>-60.83188468242037</v>
+        <v>-58.58734922205657</v>
       </c>
       <c r="H8" t="n">
-        <v>-20.34836057859349</v>
+        <v>-17.87354170616633</v>
       </c>
     </row>
     <row r="9">
@@ -2053,25 +2053,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.481526266952244</v>
+        <v>6.412242162929828</v>
       </c>
       <c r="C9" t="n">
-        <v>4.196882200840538</v>
+        <v>7.780401172812379</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.95186638882642</v>
+        <v>-10.38539964139485</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.995128007772873</v>
+        <v>-3.645412879066331</v>
       </c>
       <c r="F9" t="n">
-        <v>-53.5773358328883</v>
+        <v>-48.12847011781283</v>
       </c>
       <c r="G9" t="n">
-        <v>-58.91471269357459</v>
+        <v>-55.39206257398028</v>
       </c>
       <c r="H9" t="n">
-        <v>-19.9601057425449</v>
+        <v>-17.22645031275201</v>
       </c>
     </row>
   </sheetData>
@@ -2132,25 +2132,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.4742830406263603</v>
+        <v>-0.393799003667721</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.5478158573263705</v>
+        <v>-0.4347059001531748</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.125790015442175</v>
+        <v>-3.515455544421928</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.75355245554382</v>
+        <v>-30.62129494392837</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5093187862143554</v>
+        <v>0.4921711139280971</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4438329319164874</v>
+        <v>0.7307148775945349</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.324714941801313</v>
+        <v>-5.623728233441427</v>
       </c>
     </row>
     <row r="3">
@@ -2160,25 +2160,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6325660181227728</v>
+        <v>0.6140462329543629</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5942147210138986</v>
+        <v>0.5630692372949559</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1896968096883741</v>
+        <v>0.19844444147301</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2509963249591765</v>
+        <v>0.3364207849036255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07572181594400468</v>
+        <v>0.08696783476347357</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07117553151596119</v>
+        <v>0.06442271345354411</v>
       </c>
       <c r="H3" t="n">
-        <v>0.302395203540698</v>
+        <v>0.3105618741404954</v>
       </c>
     </row>
     <row r="4">
@@ -2188,25 +2188,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7821303043668204</v>
+        <v>0.7394322588840571</v>
       </c>
       <c r="C4" t="n">
-        <v>0.792627271172214</v>
+        <v>0.7347043365593974</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03645725202155223</v>
+        <v>0.03990050394202203</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06427611945414731</v>
+        <v>0.1144837990143256</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01075889711384351</v>
+        <v>0.01113488469332796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01609838209257296</v>
+        <v>0.00779451902333332</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2837247043701917</v>
+        <v>0.2745750503527438</v>
       </c>
     </row>
     <row r="5">
@@ -2216,25 +2216,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8843813116336303</v>
+        <v>0.8599024705651549</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8902961704804834</v>
+        <v>0.8571489582093637</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1909378223965913</v>
+        <v>0.1997511049832316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2535273544494702</v>
+        <v>0.338354546318393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1037251035856003</v>
+        <v>0.1055219630850751</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1268793997959203</v>
+        <v>0.08828657329024227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4082911937236159</v>
+        <v>0.4081609360752436</v>
       </c>
     </row>
     <row r="6">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.16150914730942</v>
+        <v>60.53575614858531</v>
       </c>
       <c r="C6" t="n">
-        <v>52.07429461705536</v>
+        <v>49.12510756111656</v>
       </c>
       <c r="D6" t="n">
-        <v>104.6742999708249</v>
+        <v>107.3769949792334</v>
       </c>
       <c r="E6" t="n">
-        <v>182.0593185092567</v>
+        <v>245.9886535338695</v>
       </c>
       <c r="F6" t="n">
-        <v>35.41286255547853</v>
+        <v>30.89250539451482</v>
       </c>
       <c r="G6" t="n">
-        <v>34.01134011992583</v>
+        <v>30.98390363332208</v>
       </c>
       <c r="H6" t="n">
-        <v>78.39893748664178</v>
+        <v>87.48382020844026</v>
       </c>
     </row>
     <row r="7">
@@ -2272,25 +2272,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.987552250489365</v>
+        <v>1.876484564638313</v>
       </c>
       <c r="C7" t="n">
-        <v>2.046367694036922</v>
+        <v>1.894409611275061</v>
       </c>
       <c r="D7" t="n">
-        <v>2.534514162095478</v>
+        <v>2.770134032171988</v>
       </c>
       <c r="E7" t="n">
-        <v>10.7501180405621</v>
+        <v>19.13805428497708</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1587355921153838</v>
+        <v>0.1626430851069005</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1821189878898549</v>
+        <v>0.08874170003797287</v>
       </c>
       <c r="H7" t="n">
-        <v>2.943234454531517</v>
+        <v>4.321744546367886</v>
       </c>
     </row>
     <row r="8">
@@ -2300,25 +2300,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.78839469576381</v>
+        <v>7.283146555267231</v>
       </c>
       <c r="C8" t="n">
-        <v>14.60558685048668</v>
+        <v>8.150277256700004</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.86968929349835</v>
+        <v>-9.328197950241279</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4674026560873941</v>
+        <v>-3.00393175594181</v>
       </c>
       <c r="F8" t="n">
-        <v>-42.91628896679864</v>
+        <v>-48.46974033761813</v>
       </c>
       <c r="G8" t="n">
-        <v>-41.80651104460161</v>
+        <v>-57.96068274246561</v>
       </c>
       <c r="H8" t="n">
-        <v>-10.11098506912258</v>
+        <v>-17.2215214957166</v>
       </c>
     </row>
     <row r="9">
@@ -2328,25 +2328,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.36619131445357</v>
+        <v>8.269269441948328</v>
       </c>
       <c r="C9" t="n">
-        <v>12.93966260431112</v>
+        <v>7.109074602840279</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.535613539673911</v>
+        <v>-10.369400604101</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.133326902262954</v>
+        <v>-4.045134409801536</v>
       </c>
       <c r="F9" t="n">
-        <v>-38.39669410710634</v>
+        <v>-45.64499355031045</v>
       </c>
       <c r="G9" t="n">
-        <v>-36.69405240767954</v>
+        <v>-54.76539609438932</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.075638839659675</v>
+        <v>-16.57443010230228</v>
       </c>
     </row>
   </sheetData>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.4742024174035977</v>
+        <v>-0.1437404602458008</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.5688925816549919</v>
+        <v>-0.5688960135984944</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.688151556830552</v>
+        <v>-3.516378487428696</v>
       </c>
       <c r="E2" t="n">
-        <v>-29.70497912103557</v>
+        <v>-30.62322918742803</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5108115267531983</v>
+        <v>0.492791523558557</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4479453218181846</v>
+        <v>0.7304932593628033</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.579578138058888</v>
+        <v>-5.604826560963276</v>
       </c>
     </row>
     <row r="3">
@@ -2435,25 +2435,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6355477330734451</v>
+        <v>0.5550566579123023</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5999473283507916</v>
+        <v>0.5999480745668823</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2022170011074444</v>
+        <v>0.1984639000192299</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3306383612313323</v>
+        <v>0.3364345424106267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08090928564085684</v>
+        <v>0.08692893515153161</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07022922234302212</v>
+        <v>0.06448396150158356</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3199148219578154</v>
+        <v>0.3068860119270261</v>
       </c>
     </row>
     <row r="4">
@@ -2463,25 +2463,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.782087532481083</v>
+        <v>0.60677227481952</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8034205360239525</v>
+        <v>0.803422293501756</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04142652005625306</v>
+        <v>0.03990865946270371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.111166309433721</v>
+        <v>0.1144908018756711</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01072616661301351</v>
+        <v>0.01112128131256867</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01597934803293458</v>
+        <v>0.007800933813380834</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2941344021068262</v>
+        <v>0.2639193741309334</v>
       </c>
     </row>
     <row r="5">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8843571294907295</v>
+        <v>0.7789558875953888</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8963372892075574</v>
+        <v>0.8963382695733547</v>
       </c>
       <c r="D5" t="n">
-        <v>0.20353505854337</v>
+        <v>0.1997715181468663</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3334161205366666</v>
+        <v>0.3383648945674937</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1035672081935856</v>
+        <v>0.105457485806218</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1264094459798578</v>
+        <v>0.0883228951822846</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4246037086586278</v>
+        <v>0.4012018251452676</v>
       </c>
     </row>
     <row r="6">
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.34836127887306</v>
+        <v>60.09567885971909</v>
       </c>
       <c r="C6" t="n">
-        <v>52.84790951938115</v>
+        <v>52.84807222503062</v>
       </c>
       <c r="D6" t="n">
-        <v>106.2169534433297</v>
+        <v>107.405405091929</v>
       </c>
       <c r="E6" t="n">
-        <v>238.8233755610779</v>
+        <v>246.012347479582</v>
       </c>
       <c r="F6" t="n">
-        <v>35.22879162794211</v>
+        <v>30.90460543714447</v>
       </c>
       <c r="G6" t="n">
-        <v>19.55616015745132</v>
+        <v>31.04123668331636</v>
       </c>
       <c r="H6" t="n">
-        <v>85.83692526467588</v>
+        <v>88.05122429612027</v>
       </c>
     </row>
     <row r="7">
@@ -2547,25 +2547,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.986443995915675</v>
+        <v>1.540725460894808</v>
       </c>
       <c r="C7" t="n">
-        <v>2.073124299426529</v>
+        <v>2.071128819061555</v>
       </c>
       <c r="D7" t="n">
-        <v>2.877888062177086</v>
+        <v>2.770699215705003</v>
       </c>
       <c r="E7" t="n">
-        <v>18.58562030582856</v>
+        <v>19.13922463508275</v>
       </c>
       <c r="F7" t="n">
-        <v>0.15776485860315</v>
+        <v>0.162447439851231</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1803019470775989</v>
+        <v>0.08881267586052562</v>
       </c>
       <c r="H7" t="n">
-        <v>4.310190578171432</v>
+        <v>4.295506374409313</v>
       </c>
     </row>
     <row r="8">
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.78790250476245</v>
+        <v>5.503584489790362</v>
       </c>
       <c r="C8" t="n">
-        <v>12.68673802406224</v>
+        <v>8.686751149013393</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.103004132998574</v>
+        <v>-9.326971696959752</v>
       </c>
       <c r="E8" t="n">
-        <v>0.819632505263014</v>
+        <v>-3.003564753069671</v>
       </c>
       <c r="F8" t="n">
-        <v>-44.9558975847073</v>
+        <v>-48.48563202101464</v>
       </c>
       <c r="G8" t="n">
-        <v>-43.910413937832</v>
+        <v>-57.94916565903492</v>
       </c>
       <c r="H8" t="n">
-        <v>-11.44584043690836</v>
+        <v>-17.42916641521254</v>
       </c>
     </row>
     <row r="9">
@@ -2603,25 +2603,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.16847454611599</v>
+        <v>6.48970737647146</v>
       </c>
       <c r="C9" t="n">
-        <v>11.22905430865863</v>
+        <v>7.645548495153667</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.560687848402189</v>
+        <v>-10.36817435081948</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6380512101406008</v>
+        <v>-4.044767406929397</v>
       </c>
       <c r="F9" t="n">
-        <v>-41.00125208247654</v>
+        <v>-45.66088523370696</v>
       </c>
       <c r="G9" t="n">
-        <v>-39.4370126305252</v>
+        <v>-54.75387901095863</v>
       </c>
       <c r="H9" t="n">
-        <v>-10.53991248612832</v>
+        <v>-16.78207502179822</v>
       </c>
     </row>
   </sheetData>
@@ -2682,25 +2682,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3277686086247772</v>
+        <v>0.365783384987858</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2760376358262634</v>
+        <v>0.6104318708285223</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8113152392860703</v>
+        <v>0.6888372838972741</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.114152072346265</v>
+        <v>-0.5744732901503353</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5176042677548718</v>
+        <v>-0.6963306575101522</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3881096861358225</v>
+        <v>0.04867373913701267</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0344472275469234</v>
+        <v>0.07382038853169659</v>
       </c>
     </row>
     <row r="3">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3504722069681389</v>
+        <v>0.4539420558233967</v>
       </c>
       <c r="C3" t="n">
-        <v>0.417212187081936</v>
+        <v>0.3913081396880673</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03191046092134913</v>
+        <v>0.04616930910718053</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09731069962948319</v>
+        <v>0.05476375561925004</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09275156808853072</v>
+        <v>0.167091168245418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1138849839688397</v>
+        <v>0.1306721954668457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1839236844430463</v>
+        <v>0.2073244373250264</v>
       </c>
     </row>
     <row r="4">
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.356629309469541</v>
+        <v>0.3364618736461859</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3707368098280284</v>
+        <v>0.1994955160197351</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001667299559169827</v>
+        <v>0.002749567359998568</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01127467931287207</v>
+        <v>0.005700325809636243</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01057722591688587</v>
+        <v>0.03719450939318635</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01771130409657914</v>
+        <v>0.02753635466918994</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1280994380305127</v>
+        <v>0.1015230244829887</v>
       </c>
     </row>
     <row r="5">
@@ -2766,25 +2766,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5971844852887096</v>
+        <v>0.5800533368977252</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6088816057560192</v>
+        <v>0.4466492091336725</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04083257962913717</v>
+        <v>0.05243631718569267</v>
       </c>
       <c r="E5" t="n">
-        <v>0.10618229284053</v>
+        <v>0.07550050204890192</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1028456412148121</v>
+        <v>0.192858780959505</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1330838235721349</v>
+        <v>0.1659408167666712</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2648350713835572</v>
+        <v>0.2522398271653614</v>
       </c>
     </row>
     <row r="6">
@@ -2794,25 +2794,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.13037842759058</v>
+        <v>61.37547214048929</v>
       </c>
       <c r="C6" t="n">
-        <v>41.39317999795678</v>
+        <v>54.37081003899185</v>
       </c>
       <c r="D6" t="n">
-        <v>13.80682368489973</v>
+        <v>23.72881194179946</v>
       </c>
       <c r="E6" t="n">
-        <v>60.75125563962567</v>
+        <v>31.65012472768436</v>
       </c>
       <c r="F6" t="n">
-        <v>24.78723260207323</v>
+        <v>54.98476519264089</v>
       </c>
       <c r="G6" t="n">
-        <v>40.00760538910419</v>
+        <v>45.17860209115435</v>
       </c>
       <c r="H6" t="n">
-        <v>34.9794126235417</v>
+        <v>45.21476435546003</v>
       </c>
     </row>
     <row r="7">
@@ -2822,25 +2822,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4528099340412455</v>
+        <v>0.4262882960559727</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4782044761317409</v>
+        <v>0.2570172999652579</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0592725379055978</v>
+        <v>0.09577351198281679</v>
       </c>
       <c r="E7" t="n">
-        <v>1.88727579444578</v>
+        <v>0.9536644302236921</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1536227778153586</v>
+        <v>1.070870707656552</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1974650070268587</v>
+        <v>0.3051733265273292</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5381084212277636</v>
+        <v>0.5181312620686035</v>
       </c>
     </row>
     <row r="8">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.279525469364248</v>
+        <v>-7.803433951022633</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04642274643076583</v>
+        <v>-7.671781113978183</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.37929995077317</v>
+        <v>-33.37787021990322</v>
       </c>
       <c r="E8" t="n">
-        <v>-20.91117501789131</v>
+        <v>-29.00339167713924</v>
       </c>
       <c r="F8" t="n">
-        <v>-53.13767713886504</v>
+        <v>-40.79072363220064</v>
       </c>
       <c r="G8" t="n">
-        <v>-50.46973071219099</v>
+        <v>-48.29147423154124</v>
       </c>
       <c r="H8" t="n">
-        <v>-26.68849759044233</v>
+        <v>-27.82311247096419</v>
       </c>
     </row>
     <row r="9">
@@ -2878,25 +2878,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.68785173735559</v>
+        <v>-7.606209373686413</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.5782988458850689</v>
+        <v>-7.880021644750128</v>
       </c>
       <c r="D9" t="n">
-        <v>-33.00402154308901</v>
+        <v>-33.58611075067516</v>
       </c>
       <c r="E9" t="n">
-        <v>-21.53589661020715</v>
+        <v>-29.21163220791119</v>
       </c>
       <c r="F9" t="n">
-        <v>-51.44282906648043</v>
+        <v>-40.2257742747391</v>
       </c>
       <c r="G9" t="n">
-        <v>-48.55255872334522</v>
+        <v>-47.65241690192599</v>
       </c>
       <c r="H9" t="n">
-        <v>-26.30024275439375</v>
+        <v>-27.69369419228133</v>
       </c>
     </row>
   </sheetData>
@@ -2957,25 +2957,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04816807796755396</v>
+        <v>-0.205979260580377</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02397563792941282</v>
+        <v>-0.4029164179288041</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.277023431119883</v>
+        <v>-0.3981097194974563</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.523654133549165</v>
+        <v>-16.1565585651214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5888369132872135</v>
+        <v>-0.02234964220393176</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05144187779013509</v>
+        <v>0.6316582722186486</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.014709176282455</v>
+        <v>-2.759042555518887</v>
       </c>
     </row>
     <row r="3">
@@ -2985,25 +2985,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4722917721766684</v>
+        <v>0.5708438180860372</v>
       </c>
       <c r="C3" t="n">
-        <v>0.440825513521497</v>
+        <v>0.557365152506311</v>
       </c>
       <c r="D3" t="n">
-        <v>0.13350607261929</v>
+        <v>0.1009018822008189</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1514551031083642</v>
+        <v>0.2483563712451899</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07559704298348544</v>
+        <v>0.124519651362172</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1296207212228465</v>
+        <v>0.05397140142150834</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2338827042720252</v>
+        <v>0.2759930461370062</v>
       </c>
     </row>
     <row r="4">
@@ -3013,25 +3013,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5049617816732157</v>
+        <v>0.6397909357602484</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4998162559478709</v>
+        <v>0.7184251322676122</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02012075669789517</v>
+        <v>0.01235429777248072</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02361866299240919</v>
+        <v>0.06211472382866478</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009015346874245064</v>
+        <v>0.02241649834112443</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02745623026722429</v>
+        <v>0.01066173496193468</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1808315057421434</v>
+        <v>0.2442938871553442</v>
       </c>
     </row>
     <row r="5">
@@ -3041,25 +3041,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7106066293479225</v>
+        <v>0.7998693241775486</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7069768425824646</v>
+        <v>0.8475996297000207</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1418476531279075</v>
+        <v>0.1111498887650398</v>
       </c>
       <c r="E5" t="n">
-        <v>0.153683645819616</v>
+        <v>0.249228256481212</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09494918048221936</v>
+        <v>0.1497214024150336</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1656992162541039</v>
+        <v>0.1032556776256622</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3289605279357057</v>
+        <v>0.3768040298607528</v>
       </c>
     </row>
     <row r="6">
@@ -3069,25 +3069,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.25666201428961</v>
+        <v>59.66570776838789</v>
       </c>
       <c r="C6" t="n">
-        <v>47.3865512705325</v>
+        <v>46.96341866664856</v>
       </c>
       <c r="D6" t="n">
-        <v>83.33480786919245</v>
+        <v>64.39092256056641</v>
       </c>
       <c r="E6" t="n">
-        <v>111.9917775120955</v>
+        <v>187.6873322912452</v>
       </c>
       <c r="F6" t="n">
-        <v>33.98933014939521</v>
+        <v>38.22989719035569</v>
       </c>
       <c r="G6" t="n">
-        <v>45.09438711480063</v>
+        <v>30.32919993525522</v>
       </c>
       <c r="H6" t="n">
-        <v>63.50891932171763</v>
+        <v>71.21107973540983</v>
       </c>
     </row>
     <row r="7">
@@ -3097,25 +3097,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6450228237809847</v>
+        <v>1.624294866412574</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6486786877846858</v>
+        <v>1.852545035931939</v>
       </c>
       <c r="D7" t="n">
-        <v>1.406383118048983</v>
+        <v>0.8611618485799469</v>
       </c>
       <c r="E7" t="n">
-        <v>3.959258608318872</v>
+        <v>10.38589575243297</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1356596688258075</v>
+        <v>0.6497928829999333</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3097867978500165</v>
+        <v>0.1204657328077597</v>
       </c>
       <c r="H7" t="n">
-        <v>1.184131617434892</v>
+        <v>2.582359353194188</v>
       </c>
     </row>
     <row r="8">
@@ -3125,25 +3125,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.85054720816906</v>
+        <v>5.980475630179267</v>
       </c>
       <c r="C8" t="n">
-        <v>19.83891158277297</v>
+        <v>8.015837326375983</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5639800486890856</v>
+        <v>-16.36250767204168</v>
       </c>
       <c r="E8" t="n">
-        <v>1.525691551747158</v>
+        <v>-6.672633316735414</v>
       </c>
       <c r="F8" t="n">
-        <v>-37.21475029297419</v>
+        <v>-39.37345475585397</v>
       </c>
       <c r="G8" t="n">
-        <v>-26.33227036515031</v>
+        <v>-53.5753176671847</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.961315044457704</v>
+        <v>-16.99793340921009</v>
       </c>
     </row>
     <row r="9">
@@ -3153,25 +3153,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.21724213620369</v>
+        <v>6.966598516860365</v>
       </c>
       <c r="C9" t="n">
-        <v>17.34002521350963</v>
+        <v>6.974634672516257</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.934906320574253</v>
+        <v>-17.40371032590141</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9731948175161804</v>
+        <v>-7.71383597059514</v>
       </c>
       <c r="F9" t="n">
-        <v>-30.43535800343574</v>
+        <v>-36.54870796854629</v>
       </c>
       <c r="G9" t="n">
-        <v>-18.66358240976721</v>
+        <v>-50.38003101910841</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.408295700263344</v>
+        <v>-16.35084201579577</v>
       </c>
     </row>
   </sheetData>
@@ -3232,25 +3232,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3393562671117369</v>
+        <v>-0.3744395701864245</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1334077646307407</v>
+        <v>-0.6498506974641116</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1736160572066336</v>
+        <v>-1.98636787503421</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.09553889238147018</v>
+        <v>-0.5979164120466416</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4016881575371958</v>
+        <v>-2.876855628417361</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.933051775019947</v>
+        <v>-2.140220980664422</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4683072307710405</v>
+        <v>-1.437608527302195</v>
       </c>
     </row>
     <row r="3">
@@ -3260,25 +3260,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5898934951703412</v>
+        <v>0.5996248276171328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4694666714192655</v>
+        <v>0.6791196733585282</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08519587469594352</v>
+        <v>0.1550759492092912</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04713059046339321</v>
+        <v>0.0672275087719983</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1479474183611203</v>
+        <v>0.2463445664385754</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2554558645306542</v>
+        <v>0.2681144656690697</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2658483191067863</v>
+        <v>0.3359178318440992</v>
       </c>
     </row>
     <row r="4">
@@ -3288,25 +3288,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7105495322028877</v>
+        <v>0.7291617754125368</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4437767163894157</v>
+        <v>0.8448787043902272</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01037057538410304</v>
+        <v>0.02638882876774841</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003966360472908443</v>
+        <v>0.005785200817449937</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03073404534134777</v>
+        <v>0.08500568120300797</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08489784973115384</v>
+        <v>0.09089440943716434</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2140491799203028</v>
+        <v>0.2970191000046891</v>
       </c>
     </row>
     <row r="5">
@@ -3316,25 +3316,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8429410016145186</v>
+        <v>0.8539096998000063</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6661656823864583</v>
+        <v>0.919172837060706</v>
       </c>
       <c r="D5" t="n">
-        <v>0.101836022035933</v>
+        <v>0.1624463873644114</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06297904788823377</v>
+        <v>0.07606050760710145</v>
       </c>
       <c r="F5" t="n">
-        <v>0.175311281272335</v>
+        <v>0.2915573377622453</v>
       </c>
       <c r="G5" t="n">
-        <v>0.291372355811518</v>
+        <v>0.3014869971278435</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3567675651681661</v>
+        <v>0.4341056277870524</v>
       </c>
     </row>
     <row r="6">
@@ -3344,25 +3344,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.86535938730673</v>
+        <v>60.42690621145799</v>
       </c>
       <c r="C6" t="n">
-        <v>47.28820402521066</v>
+        <v>70.68629393654709</v>
       </c>
       <c r="D6" t="n">
-        <v>35.91053219588825</v>
+        <v>73.27258179703509</v>
       </c>
       <c r="E6" t="n">
-        <v>27.73430205252467</v>
+        <v>62.62648844059918</v>
       </c>
       <c r="F6" t="n">
-        <v>47.08690271122896</v>
+        <v>75.48283294142118</v>
       </c>
       <c r="G6" t="n">
-        <v>83.83729996863104</v>
+        <v>89.37115329579187</v>
       </c>
       <c r="H6" t="n">
-        <v>50.12043339013172</v>
+        <v>71.97770943714207</v>
       </c>
     </row>
     <row r="7">
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.802383105351085</v>
+        <v>1.848490227689406</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5726213720833688</v>
+        <v>2.175740604624785</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7226884398617245</v>
+        <v>1.831765085295374</v>
       </c>
       <c r="E7" t="n">
-        <v>0.666876240090954</v>
+        <v>0.969849128372415</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8880405580002045</v>
+        <v>2.448121330734628</v>
       </c>
       <c r="G7" t="n">
-        <v>1.882688054635584</v>
+        <v>2.014384761610684</v>
       </c>
       <c r="H7" t="n">
-        <v>1.08921629500382</v>
+        <v>1.881391856387882</v>
       </c>
     </row>
     <row r="8">
@@ -3400,25 +3400,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.92455042626707</v>
+        <v>3.157263082980241</v>
       </c>
       <c r="C8" t="n">
-        <v>3.125397595658973</v>
+        <v>4.98862675782678</v>
       </c>
       <c r="D8" t="n">
-        <v>-19.41269663698756</v>
+        <v>-15.80888706672632</v>
       </c>
       <c r="E8" t="n">
-        <v>-25.1794381732957</v>
+        <v>-24.91471323278702</v>
       </c>
       <c r="F8" t="n">
-        <v>-37.27099551087208</v>
+        <v>-26.04548343155786</v>
       </c>
       <c r="G8" t="n">
-        <v>-26.52829118287746</v>
+        <v>-27.57279494844067</v>
       </c>
       <c r="H8" t="n">
-        <v>-16.72357891368446</v>
+        <v>-14.36599813978414</v>
       </c>
     </row>
     <row r="9">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.713448735611948</v>
+        <v>3.7489368149889</v>
       </c>
       <c r="C9" t="n">
-        <v>2.292435472571193</v>
+        <v>4.363905165510945</v>
       </c>
       <c r="D9" t="n">
-        <v>-20.24565876007534</v>
+        <v>-16.43360865904215</v>
       </c>
       <c r="E9" t="n">
-        <v>-26.01240029638348</v>
+        <v>-25.53943482510286</v>
       </c>
       <c r="F9" t="n">
-        <v>-35.01119808102594</v>
+        <v>-24.35063535917325</v>
       </c>
       <c r="G9" t="n">
-        <v>-23.97206186441642</v>
+        <v>-25.6556229595949</v>
       </c>
       <c r="H9" t="n">
-        <v>-16.20590579895301</v>
+        <v>-13.97774330373555</v>
       </c>
     </row>
   </sheetData>
